--- a/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_Pre12.xlsx
+++ b/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_Pre12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="85">
   <si>
     <t>Scenario</t>
   </si>
@@ -82,199 +82,190 @@
     <t>Haryana</t>
   </si>
   <si>
+    <t>AMRITSAR</t>
+  </si>
+  <si>
+    <t>FAZILKA</t>
+  </si>
+  <si>
     <t>JALANDHAR</t>
   </si>
   <si>
-    <t>FAZILKA</t>
+    <t>SRI MUKTSAR SAHIB</t>
+  </si>
+  <si>
+    <t>TARN TARAN</t>
+  </si>
+  <si>
+    <t>Stor</t>
+  </si>
+  <si>
+    <t>CHAK SAKANDAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BHILOWAL GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>ABOHAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BAHADUR KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BAHAAW WALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BUKENWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BALLUANA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BHAAGU GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>CHANNAN KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>CHURHI WALA DHANNA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DEEWAN KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DHABA KOKARIYA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DHARANGWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DHINGANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DODHEWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DUTARANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>GHALLU GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>GOBINDGARH GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JANDWALA MEERA SANGLA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JHUMIYANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JHURAD KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHUPAYA SARWAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KULAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KUNDAL GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MALOOKPURA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MAUJGARH GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>NIHAL KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>PANJKOSI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>PATRE WALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>RUKANPURA KHUI KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>SAIDANWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>WAREYAM KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>Bhadoo Waxing Plant</t>
+  </si>
+  <si>
+    <t>P.S. Waxing Plant</t>
+  </si>
+  <si>
+    <t>Sandhu waxing plant</t>
+  </si>
+  <si>
+    <t>Sri Ram cotton &amp; oil mill</t>
+  </si>
+  <si>
+    <t>Near Mandir</t>
+  </si>
+  <si>
+    <t>Near Gurdwara Sahib</t>
+  </si>
+  <si>
+    <t>Dera Jhangi wala</t>
+  </si>
+  <si>
+    <t>Near Jandwala Meera Sangla purchase center</t>
+  </si>
+  <si>
+    <t>GHARHIANA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MAMMU KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MURADWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KUHADIANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHIUWALA DHAB GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>RAMKOT GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KANDHWALA HAZARKHAN GRAIN MARKET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAMPUR  </t>
+  </si>
+  <si>
+    <t>BHAGSAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MAHABADAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>sri muktsar sahib grain market</t>
+  </si>
+  <si>
+    <t>KARAM PATTI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHALRA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>Depot</t>
+  </si>
+  <si>
+    <t>agah</t>
   </si>
   <si>
     <t>MALERKOTLA</t>
-  </si>
-  <si>
-    <t>ADAMPUR</t>
-  </si>
-  <si>
-    <t>Abohar</t>
-  </si>
-  <si>
-    <t>AHMEDGARH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAMPUR  </t>
-  </si>
-  <si>
-    <t>ABOHAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BAHADUR KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BAHAAW WALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BUKENWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BALLUANA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BHAAGU GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>CHANNAN KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>CHURHI WALA DHANNA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DEEWAN KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DHABA KOKARIYA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DHARANGWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DHINGANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DODHEWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DUTARANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>GADA DOB GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>GHALLU GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>GOBINDGARH GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JANDWALA MEERA SANGLA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JHUMIYANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JHURAD KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KALAR KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KHUMBAN GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KHUPAYA SARWAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KULAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KUNDAL GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MALOOKPURA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MAUJGARH GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>NARAINPURA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>NIHAL KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>PANJKOSI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>PATRE WALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>RUKANPURA KHUI KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>SAIDANWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>SITO GUNO GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>VAJIDPUR BHOMA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>WAREYAM KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>Bhadoo Waxing Plant</t>
-  </si>
-  <si>
-    <t>P.S. Waxing Plant</t>
-  </si>
-  <si>
-    <t>Sandhu waxing plant</t>
-  </si>
-  <si>
-    <t>Sri Ram cotton &amp; oil mill</t>
-  </si>
-  <si>
-    <t>Near Mandir</t>
-  </si>
-  <si>
-    <t>Near Gurdwara Sahib</t>
-  </si>
-  <si>
-    <t>Dera Jhangi wala</t>
-  </si>
-  <si>
-    <t>Near Jandwala Meera Sangla purchase center</t>
-  </si>
-  <si>
-    <t>GHARHIANA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MAMMU KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MURADWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KUHADIANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BHIKHAMPUR BEGOWAL</t>
-  </si>
-  <si>
-    <t>DHALER KHURD</t>
-  </si>
-  <si>
-    <t>KANGANWAL</t>
-  </si>
-  <si>
-    <t>KUP</t>
-  </si>
-  <si>
-    <t>MAHOLI KALAN</t>
-  </si>
-  <si>
-    <t>MANAK HERI</t>
-  </si>
-  <si>
-    <t>MOMNA BAD</t>
-  </si>
-  <si>
-    <t>UMARPURA (NATHUMAJRA)</t>
-  </si>
-  <si>
-    <t>Depot</t>
-  </si>
-  <si>
-    <t>agah</t>
   </si>
   <si>
     <t>Paddy</t>
@@ -635,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S88"/>
+  <dimension ref="A1:S84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -711,28 +702,28 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F2">
-        <v>1046</v>
+        <v>3</v>
       </c>
       <c r="G2" t="s">
         <v>28</v>
       </c>
       <c r="H2">
-        <v>31.425406</v>
+        <v>31.84430551</v>
       </c>
       <c r="I2">
-        <v>75.719528</v>
+        <v>74.91208039999999</v>
       </c>
       <c r="J2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K2">
-        <v>625</v>
+        <v>3</v>
       </c>
       <c r="L2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M2" t="s">
         <v>21</v>
@@ -741,19 +732,19 @@
         <v>22</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P2">
-        <v>31.408658</v>
+        <v>31.8529346</v>
       </c>
       <c r="Q2">
-        <v>75.685958</v>
+        <v>74.91584450000001</v>
       </c>
       <c r="R2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S2">
-        <v>21500</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -767,52 +758,52 @@
         <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>501</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
         <v>29</v>
       </c>
       <c r="H3">
-        <v>30.156605</v>
+        <v>31.7398221</v>
       </c>
       <c r="I3">
-        <v>74.19572100000001</v>
+        <v>74.6072853</v>
       </c>
       <c r="J3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K3">
-        <v>396</v>
+        <v>5</v>
       </c>
       <c r="L3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M3" t="s">
         <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P3">
-        <v>30.15881226</v>
+        <v>31.800077</v>
       </c>
       <c r="Q3">
-        <v>74.18214294000001</v>
+        <v>74.588493</v>
       </c>
       <c r="R3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S3">
-        <v>90000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -829,13 +820,13 @@
         <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4">
         <v>501</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H4">
         <v>30.156605</v>
@@ -844,13 +835,13 @@
         <v>74.19572100000001</v>
       </c>
       <c r="J4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K4">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M4" t="s">
         <v>21</v>
@@ -859,19 +850,19 @@
         <v>23</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P4">
-        <v>30.15894356</v>
+        <v>30.15881226</v>
       </c>
       <c r="Q4">
-        <v>74.18094151</v>
+        <v>74.18214294000001</v>
       </c>
       <c r="R4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S4">
-        <v>60000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -888,13 +879,13 @@
         <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5">
         <v>501</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H5">
         <v>30.156605</v>
@@ -903,13 +894,13 @@
         <v>74.19572100000001</v>
       </c>
       <c r="J5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K5">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M5" t="s">
         <v>21</v>
@@ -918,19 +909,19 @@
         <v>23</v>
       </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P5">
-        <v>30.15848535</v>
+        <v>30.15894356</v>
       </c>
       <c r="Q5">
-        <v>74.18085842000001</v>
+        <v>74.18094151</v>
       </c>
       <c r="R5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S5">
-        <v>120000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -947,13 +938,13 @@
         <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6">
         <v>501</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H6">
         <v>30.156605</v>
@@ -962,13 +953,13 @@
         <v>74.19572100000001</v>
       </c>
       <c r="J6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K6">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M6" t="s">
         <v>21</v>
@@ -977,19 +968,19 @@
         <v>23</v>
       </c>
       <c r="O6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P6">
-        <v>30.15809938</v>
+        <v>30.15848535</v>
       </c>
       <c r="Q6">
-        <v>74.16401603</v>
+        <v>74.18085842000001</v>
       </c>
       <c r="R6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S6">
-        <v>145397</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1006,13 +997,13 @@
         <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7">
         <v>501</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H7">
         <v>30.156605</v>
@@ -1021,13 +1012,13 @@
         <v>74.19572100000001</v>
       </c>
       <c r="J7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K7">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="L7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M7" t="s">
         <v>21</v>
@@ -1036,19 +1027,19 @@
         <v>23</v>
       </c>
       <c r="O7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P7">
-        <v>30.1689126</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q7">
-        <v>74.183232</v>
+        <v>74.16401603</v>
       </c>
       <c r="R7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S7">
-        <v>31477</v>
+        <v>33610</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1065,13 +1056,13 @@
         <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8">
         <v>501</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H8">
         <v>30.156605</v>
@@ -1080,13 +1071,13 @@
         <v>74.19572100000001</v>
       </c>
       <c r="J8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K8">
         <v>405</v>
       </c>
       <c r="L8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M8" t="s">
         <v>21</v>
@@ -1095,7 +1086,7 @@
         <v>23</v>
       </c>
       <c r="O8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P8">
         <v>30.15857797</v>
@@ -1104,7 +1095,7 @@
         <v>74.18315728</v>
       </c>
       <c r="R8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S8">
         <v>150000</v>
@@ -1124,28 +1115,28 @@
         <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G9" t="s">
         <v>30</v>
       </c>
       <c r="H9">
-        <v>30.099748</v>
+        <v>30.156605</v>
       </c>
       <c r="I9">
-        <v>74.34759699999999</v>
+        <v>74.19572100000001</v>
       </c>
       <c r="J9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K9">
         <v>407</v>
       </c>
       <c r="L9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M9" t="s">
         <v>21</v>
@@ -1154,7 +1145,7 @@
         <v>23</v>
       </c>
       <c r="O9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P9">
         <v>30.126927</v>
@@ -1163,10 +1154,10 @@
         <v>74.161942</v>
       </c>
       <c r="R9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S9">
-        <v>71835.5</v>
+        <v>143264</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1183,28 +1174,28 @@
         <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G10" t="s">
         <v>31</v>
       </c>
       <c r="H10">
-        <v>30.028699</v>
+        <v>30.099748</v>
       </c>
       <c r="I10">
-        <v>74.197309</v>
+        <v>74.34759699999999</v>
       </c>
       <c r="J10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K10">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="L10" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M10" t="s">
         <v>21</v>
@@ -1213,19 +1204,19 @@
         <v>23</v>
       </c>
       <c r="O10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P10">
-        <v>30.10552983</v>
+        <v>30.08793156</v>
       </c>
       <c r="Q10">
-        <v>74.18014506</v>
+        <v>74.20908439</v>
       </c>
       <c r="R10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S10">
-        <v>73538.5</v>
+        <v>48247.5</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1242,28 +1233,28 @@
         <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F11">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G11" t="s">
         <v>31</v>
       </c>
       <c r="H11">
-        <v>30.028699</v>
+        <v>30.099748</v>
       </c>
       <c r="I11">
-        <v>74.197309</v>
+        <v>74.34759699999999</v>
       </c>
       <c r="J11" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K11">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="L11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M11" t="s">
         <v>21</v>
@@ -1272,19 +1263,19 @@
         <v>23</v>
       </c>
       <c r="O11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P11">
-        <v>30.126927</v>
+        <v>30.0974593</v>
       </c>
       <c r="Q11">
-        <v>74.161942</v>
+        <v>74.206666</v>
       </c>
       <c r="R11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S11">
-        <v>322</v>
+        <v>23588</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1301,28 +1292,28 @@
         <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F12">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G12" t="s">
         <v>32</v>
       </c>
       <c r="H12">
-        <v>30.162859</v>
+        <v>30.028699</v>
       </c>
       <c r="I12">
-        <v>73.991192</v>
+        <v>74.197309</v>
       </c>
       <c r="J12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K12">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="L12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M12" t="s">
         <v>21</v>
@@ -1331,19 +1322,19 @@
         <v>23</v>
       </c>
       <c r="O12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P12">
-        <v>30.126927</v>
+        <v>30.10552983</v>
       </c>
       <c r="Q12">
-        <v>74.161942</v>
+        <v>74.18014506</v>
       </c>
       <c r="R12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S12">
-        <v>37309</v>
+        <v>73860.5</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1360,28 +1351,28 @@
         <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F13">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G13" t="s">
         <v>33</v>
       </c>
       <c r="H13">
-        <v>30.16948</v>
+        <v>30.162859</v>
       </c>
       <c r="I13">
-        <v>74.28432100000001</v>
+        <v>73.991192</v>
       </c>
       <c r="J13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K13">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="L13" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M13" t="s">
         <v>21</v>
@@ -1390,19 +1381,19 @@
         <v>23</v>
       </c>
       <c r="O13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P13">
-        <v>30.1689126</v>
+        <v>30.126927</v>
       </c>
       <c r="Q13">
-        <v>74.183232</v>
+        <v>74.161942</v>
       </c>
       <c r="R13" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S13">
-        <v>2823</v>
+        <v>37309</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1419,13 +1410,13 @@
         <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14">
         <v>506</v>
       </c>
       <c r="G14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H14">
         <v>30.16948</v>
@@ -1434,13 +1425,13 @@
         <v>74.28432100000001</v>
       </c>
       <c r="J14" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K14">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L14" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M14" t="s">
         <v>21</v>
@@ -1449,19 +1440,19 @@
         <v>23</v>
       </c>
       <c r="O14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P14">
-        <v>30.16991135</v>
+        <v>30.126927</v>
       </c>
       <c r="Q14">
-        <v>74.18230296</v>
+        <v>74.161942</v>
       </c>
       <c r="R14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S14">
-        <v>15202.5</v>
+        <v>18025.5</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -1478,13 +1469,13 @@
         <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F15">
         <v>507</v>
       </c>
       <c r="G15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H15">
         <v>30.034436</v>
@@ -1493,13 +1484,13 @@
         <v>74.233859</v>
       </c>
       <c r="J15" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K15">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L15" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M15" t="s">
         <v>21</v>
@@ -1508,19 +1499,19 @@
         <v>23</v>
       </c>
       <c r="O15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P15">
-        <v>30.08675444</v>
+        <v>30.08793156</v>
       </c>
       <c r="Q15">
-        <v>74.20888524</v>
+        <v>74.20908439</v>
       </c>
       <c r="R15" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S15">
-        <v>49766</v>
+        <v>16177.5</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -1537,28 +1528,28 @@
         <v>23</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F16">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G16" t="s">
         <v>35</v>
       </c>
       <c r="H16">
-        <v>30.182524</v>
+        <v>30.034436</v>
       </c>
       <c r="I16">
-        <v>74.326095</v>
+        <v>74.233859</v>
       </c>
       <c r="J16" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K16">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="L16" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M16" t="s">
         <v>21</v>
@@ -1567,19 +1558,19 @@
         <v>23</v>
       </c>
       <c r="O16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P16">
-        <v>30.16991135</v>
+        <v>30.08675444</v>
       </c>
       <c r="Q16">
-        <v>74.18230296</v>
+        <v>74.20888524</v>
       </c>
       <c r="R16" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S16">
-        <v>41707.5</v>
+        <v>33588.5</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -1596,28 +1587,28 @@
         <v>23</v>
       </c>
       <c r="E17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F17">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G17" t="s">
         <v>36</v>
       </c>
       <c r="H17">
-        <v>30.199756</v>
+        <v>30.182524</v>
       </c>
       <c r="I17">
-        <v>74.108656</v>
+        <v>74.326095</v>
       </c>
       <c r="J17" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K17">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L17" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M17" t="s">
         <v>21</v>
@@ -1626,19 +1617,19 @@
         <v>23</v>
       </c>
       <c r="O17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P17">
-        <v>30.15809938</v>
+        <v>30.1689126</v>
       </c>
       <c r="Q17">
-        <v>74.16401603</v>
+        <v>74.183232</v>
       </c>
       <c r="R17" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S17">
-        <v>18038</v>
+        <v>13129</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -1655,28 +1646,28 @@
         <v>23</v>
       </c>
       <c r="E18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F18">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H18">
-        <v>30.113508</v>
+        <v>30.182524</v>
       </c>
       <c r="I18">
-        <v>73.989543</v>
+        <v>74.326095</v>
       </c>
       <c r="J18" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K18">
         <v>407</v>
       </c>
       <c r="L18" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M18" t="s">
         <v>21</v>
@@ -1685,7 +1676,7 @@
         <v>23</v>
       </c>
       <c r="O18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P18">
         <v>30.126927</v>
@@ -1694,10 +1685,10 @@
         <v>74.161942</v>
       </c>
       <c r="R18" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S18">
-        <v>44568.5</v>
+        <v>28578.5</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -1714,28 +1705,28 @@
         <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F19">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H19">
-        <v>30.122605</v>
+        <v>30.199756</v>
       </c>
       <c r="I19">
-        <v>74.328892</v>
+        <v>74.108656</v>
       </c>
       <c r="J19" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K19">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="L19" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M19" t="s">
         <v>21</v>
@@ -1744,19 +1735,19 @@
         <v>23</v>
       </c>
       <c r="O19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P19">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q19">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="R19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S19">
-        <v>25216</v>
+        <v>18038</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -1773,28 +1764,28 @@
         <v>23</v>
       </c>
       <c r="E20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F20">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H20">
-        <v>30.237206</v>
+        <v>30.113508</v>
       </c>
       <c r="I20">
-        <v>74.23982700000001</v>
+        <v>73.989543</v>
       </c>
       <c r="J20" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K20">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="L20" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M20" t="s">
         <v>21</v>
@@ -1803,19 +1794,19 @@
         <v>23</v>
       </c>
       <c r="O20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P20">
-        <v>30.17081207</v>
+        <v>30.126927</v>
       </c>
       <c r="Q20">
-        <v>74.18179719</v>
+        <v>74.161942</v>
       </c>
       <c r="R20" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S20">
-        <v>44802</v>
+        <v>44568.5</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -1832,28 +1823,28 @@
         <v>23</v>
       </c>
       <c r="E21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F21">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H21">
-        <v>30.023582</v>
+        <v>30.122605</v>
       </c>
       <c r="I21">
-        <v>74.04262799999999</v>
+        <v>74.328892</v>
       </c>
       <c r="J21" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K21">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="L21" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M21" t="s">
         <v>21</v>
@@ -1862,19 +1853,19 @@
         <v>23</v>
       </c>
       <c r="O21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P21">
-        <v>30.126927</v>
+        <v>30.0974593</v>
       </c>
       <c r="Q21">
-        <v>74.161942</v>
+        <v>74.206666</v>
       </c>
       <c r="R21" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S21">
-        <v>30276.5</v>
+        <v>25216</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -1891,28 +1882,28 @@
         <v>23</v>
       </c>
       <c r="E22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F22">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="G22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H22">
-        <v>29.960526</v>
+        <v>30.237206</v>
       </c>
       <c r="I22">
-        <v>74.219824</v>
+        <v>74.23982700000001</v>
       </c>
       <c r="J22" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K22">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="L22" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M22" t="s">
         <v>21</v>
@@ -1921,19 +1912,19 @@
         <v>23</v>
       </c>
       <c r="O22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P22">
-        <v>30.10552983</v>
+        <v>30.17081207</v>
       </c>
       <c r="Q22">
-        <v>74.18014506</v>
+        <v>74.18179719</v>
       </c>
       <c r="R22" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S22">
-        <v>19961.5</v>
+        <v>44802</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -1950,28 +1941,28 @@
         <v>23</v>
       </c>
       <c r="E23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F23">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="G23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H23">
-        <v>30.082625</v>
+        <v>30.023582</v>
       </c>
       <c r="I23">
-        <v>74.288794</v>
+        <v>74.04262799999999</v>
       </c>
       <c r="J23" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K23">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="L23" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M23" t="s">
         <v>21</v>
@@ -1980,19 +1971,19 @@
         <v>23</v>
       </c>
       <c r="O23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P23">
-        <v>30.0974593</v>
+        <v>30.126927</v>
       </c>
       <c r="Q23">
-        <v>74.206666</v>
+        <v>74.161942</v>
       </c>
       <c r="R23" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S23">
-        <v>9709</v>
+        <v>30276.5</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -2009,28 +2000,28 @@
         <v>23</v>
       </c>
       <c r="E24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F24">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G24" t="s">
         <v>42</v>
       </c>
       <c r="H24">
-        <v>30.082625</v>
+        <v>29.960526</v>
       </c>
       <c r="I24">
-        <v>74.288794</v>
+        <v>74.219824</v>
       </c>
       <c r="J24" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K24">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="L24" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M24" t="s">
         <v>21</v>
@@ -2039,19 +2030,19 @@
         <v>23</v>
       </c>
       <c r="O24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P24">
-        <v>30.126927</v>
+        <v>30.08675444</v>
       </c>
       <c r="Q24">
-        <v>74.161942</v>
+        <v>74.20888524</v>
       </c>
       <c r="R24" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S24">
-        <v>54672</v>
+        <v>19961.5</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -2068,28 +2059,28 @@
         <v>23</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F25">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G25" t="s">
         <v>43</v>
       </c>
       <c r="H25">
-        <v>30.221432</v>
+        <v>30.082625</v>
       </c>
       <c r="I25">
-        <v>74.35153099999999</v>
+        <v>74.288794</v>
       </c>
       <c r="J25" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K25">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="L25" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M25" t="s">
         <v>21</v>
@@ -2098,19 +2089,19 @@
         <v>23</v>
       </c>
       <c r="O25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P25">
-        <v>30.17081207</v>
+        <v>30.08793156</v>
       </c>
       <c r="Q25">
-        <v>74.18179719</v>
+        <v>74.20908439</v>
       </c>
       <c r="R25" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S25">
-        <v>13755.5</v>
+        <v>64381</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -2127,28 +2118,28 @@
         <v>23</v>
       </c>
       <c r="E26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F26">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H26">
-        <v>30.221432</v>
+        <v>30.254598</v>
       </c>
       <c r="I26">
-        <v>74.35153099999999</v>
+        <v>74.124285</v>
       </c>
       <c r="J26" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K26">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="L26" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M26" t="s">
         <v>21</v>
@@ -2157,19 +2148,19 @@
         <v>23</v>
       </c>
       <c r="O26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P26">
-        <v>30.16991135</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q26">
-        <v>74.18230296</v>
+        <v>74.16401603</v>
       </c>
       <c r="R26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S26">
-        <v>6714.5</v>
+        <v>39817.5</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -2186,28 +2177,28 @@
         <v>23</v>
       </c>
       <c r="E27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F27">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H27">
-        <v>30.254598</v>
+        <v>30.173582</v>
       </c>
       <c r="I27">
-        <v>74.124285</v>
+        <v>74.250483</v>
       </c>
       <c r="J27" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K27">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L27" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M27" t="s">
         <v>21</v>
@@ -2216,19 +2207,19 @@
         <v>23</v>
       </c>
       <c r="O27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P27">
-        <v>30.15809938</v>
+        <v>30.1689126</v>
       </c>
       <c r="Q27">
-        <v>74.16401603</v>
+        <v>74.183232</v>
       </c>
       <c r="R27" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S27">
-        <v>39817.5</v>
+        <v>10375.5</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -2245,28 +2236,28 @@
         <v>23</v>
       </c>
       <c r="E28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F28">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H28">
-        <v>30.173582</v>
+        <v>30.21019</v>
       </c>
       <c r="I28">
-        <v>74.250483</v>
+        <v>74.024728</v>
       </c>
       <c r="J28" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K28">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L28" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M28" t="s">
         <v>21</v>
@@ -2275,19 +2266,19 @@
         <v>23</v>
       </c>
       <c r="O28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P28">
-        <v>30.16991135</v>
+        <v>30.126927</v>
       </c>
       <c r="Q28">
-        <v>74.18230296</v>
+        <v>74.161942</v>
       </c>
       <c r="R28" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S28">
-        <v>10375.5</v>
+        <v>100949.5</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -2304,28 +2295,28 @@
         <v>23</v>
       </c>
       <c r="E29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F29">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H29">
-        <v>30.21019</v>
+        <v>30.257887</v>
       </c>
       <c r="I29">
-        <v>74.024728</v>
+        <v>74.185624</v>
       </c>
       <c r="J29" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K29">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L29" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M29" t="s">
         <v>21</v>
@@ -2334,19 +2325,19 @@
         <v>23</v>
       </c>
       <c r="O29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P29">
-        <v>30.15809938</v>
+        <v>30.17767461</v>
       </c>
       <c r="Q29">
-        <v>74.16401603</v>
+        <v>74.17723581</v>
       </c>
       <c r="R29" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S29">
-        <v>72343</v>
+        <v>36622.5</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -2363,28 +2354,28 @@
         <v>23</v>
       </c>
       <c r="E30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F30">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H30">
-        <v>30.21019</v>
+        <v>30.007285</v>
       </c>
       <c r="I30">
-        <v>74.024728</v>
+        <v>74.126166</v>
       </c>
       <c r="J30" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K30">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="L30" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M30" t="s">
         <v>21</v>
@@ -2393,19 +2384,19 @@
         <v>23</v>
       </c>
       <c r="O30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P30">
-        <v>30.126927</v>
+        <v>30.10552983</v>
       </c>
       <c r="Q30">
-        <v>74.161942</v>
+        <v>74.18014506</v>
       </c>
       <c r="R30" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S30">
-        <v>28606.5</v>
+        <v>11652.5</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -2422,28 +2413,28 @@
         <v>23</v>
       </c>
       <c r="E31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F31">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H31">
-        <v>30.257887</v>
+        <v>30.007285</v>
       </c>
       <c r="I31">
-        <v>74.185624</v>
+        <v>74.126166</v>
       </c>
       <c r="J31" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K31">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="L31" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M31" t="s">
         <v>21</v>
@@ -2452,19 +2443,19 @@
         <v>23</v>
       </c>
       <c r="O31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P31">
-        <v>30.17081207</v>
+        <v>30.126927</v>
       </c>
       <c r="Q31">
-        <v>74.18179719</v>
+        <v>74.161942</v>
       </c>
       <c r="R31" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S31">
-        <v>2347.5</v>
+        <v>16592.5</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -2481,28 +2472,28 @@
         <v>23</v>
       </c>
       <c r="E32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F32">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="G32" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H32">
-        <v>30.257887</v>
+        <v>30.127701</v>
       </c>
       <c r="I32">
-        <v>74.185624</v>
+        <v>74.06368999999999</v>
       </c>
       <c r="J32" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K32">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="L32" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M32" t="s">
         <v>21</v>
@@ -2511,19 +2502,19 @@
         <v>23</v>
       </c>
       <c r="O32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P32">
-        <v>30.17767461</v>
+        <v>30.126927</v>
       </c>
       <c r="Q32">
-        <v>74.17723581</v>
+        <v>74.161942</v>
       </c>
       <c r="R32" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S32">
-        <v>34275</v>
+        <v>21311</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -2540,28 +2531,28 @@
         <v>23</v>
       </c>
       <c r="E33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F33">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="G33" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H33">
-        <v>30.007285</v>
+        <v>29.98347</v>
       </c>
       <c r="I33">
-        <v>74.126166</v>
+        <v>74.283652</v>
       </c>
       <c r="J33" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K33">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="L33" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M33" t="s">
         <v>21</v>
@@ -2570,19 +2561,19 @@
         <v>23</v>
       </c>
       <c r="O33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P33">
-        <v>30.126927</v>
+        <v>30.08793156</v>
       </c>
       <c r="Q33">
-        <v>74.161942</v>
+        <v>74.20908439</v>
       </c>
       <c r="R33" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S33">
-        <v>28245</v>
+        <v>34094</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -2599,28 +2590,28 @@
         <v>23</v>
       </c>
       <c r="E34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F34">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="G34" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H34">
-        <v>30.039412</v>
+        <v>30.216512</v>
       </c>
       <c r="I34">
-        <v>73.954567</v>
+        <v>74.269492</v>
       </c>
       <c r="J34" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K34">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="L34" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M34" t="s">
         <v>21</v>
@@ -2629,19 +2620,19 @@
         <v>23</v>
       </c>
       <c r="O34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P34">
-        <v>30.126927</v>
+        <v>30.1689126</v>
       </c>
       <c r="Q34">
-        <v>74.161942</v>
+        <v>74.183232</v>
       </c>
       <c r="R34" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S34">
-        <v>12854</v>
+        <v>10795.5</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -2658,28 +2649,28 @@
         <v>23</v>
       </c>
       <c r="E35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F35">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="G35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H35">
-        <v>30.012837</v>
+        <v>30.216512</v>
       </c>
       <c r="I35">
-        <v>74.432883</v>
+        <v>74.269492</v>
       </c>
       <c r="J35" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K35">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="L35" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M35" t="s">
         <v>21</v>
@@ -2688,19 +2679,19 @@
         <v>23</v>
       </c>
       <c r="O35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P35">
-        <v>30.0974593</v>
+        <v>30.16991135</v>
       </c>
       <c r="Q35">
-        <v>74.206666</v>
+        <v>74.18230296</v>
       </c>
       <c r="R35" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S35">
-        <v>74081</v>
+        <v>21605.5</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -2717,28 +2708,28 @@
         <v>23</v>
       </c>
       <c r="E36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F36">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="G36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H36">
-        <v>30.127701</v>
+        <v>30.132598</v>
       </c>
       <c r="I36">
-        <v>74.06368999999999</v>
+        <v>74.343463</v>
       </c>
       <c r="J36" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K36">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="L36" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M36" t="s">
         <v>21</v>
@@ -2747,19 +2738,19 @@
         <v>23</v>
       </c>
       <c r="O36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P36">
-        <v>30.126927</v>
+        <v>30.0974593</v>
       </c>
       <c r="Q36">
-        <v>74.161942</v>
+        <v>74.206666</v>
       </c>
       <c r="R36" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S36">
-        <v>21311</v>
+        <v>71196</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -2776,28 +2767,28 @@
         <v>23</v>
       </c>
       <c r="E37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F37">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="G37" t="s">
         <v>52</v>
       </c>
       <c r="H37">
-        <v>29.98347</v>
+        <v>30.132598</v>
       </c>
       <c r="I37">
-        <v>74.283652</v>
+        <v>74.343463</v>
       </c>
       <c r="J37" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K37">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="L37" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M37" t="s">
         <v>21</v>
@@ -2806,19 +2797,19 @@
         <v>23</v>
       </c>
       <c r="O37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P37">
-        <v>30.08793156</v>
+        <v>30.126927</v>
       </c>
       <c r="Q37">
-        <v>74.20908439</v>
+        <v>74.161942</v>
       </c>
       <c r="R37" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S37">
-        <v>30310</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -2835,28 +2826,28 @@
         <v>23</v>
       </c>
       <c r="E38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F38">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="G38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H38">
-        <v>29.98347</v>
+        <v>30.065633</v>
       </c>
       <c r="I38">
-        <v>74.283652</v>
+        <v>73.98462499999999</v>
       </c>
       <c r="J38" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K38">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="L38" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M38" t="s">
         <v>21</v>
@@ -2865,19 +2856,19 @@
         <v>23</v>
       </c>
       <c r="O38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P38">
-        <v>30.08675444</v>
+        <v>30.126927</v>
       </c>
       <c r="Q38">
-        <v>74.20888524</v>
+        <v>74.161942</v>
       </c>
       <c r="R38" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S38">
-        <v>3784</v>
+        <v>34208</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -2894,28 +2885,28 @@
         <v>23</v>
       </c>
       <c r="E39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F39">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="G39" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H39">
-        <v>30.216512</v>
+        <v>30.224829</v>
       </c>
       <c r="I39">
-        <v>74.269492</v>
+        <v>74.12361199999999</v>
       </c>
       <c r="J39" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K39">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L39" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M39" t="s">
         <v>21</v>
@@ -2924,19 +2915,19 @@
         <v>23</v>
       </c>
       <c r="O39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P39">
-        <v>30.17081207</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q39">
-        <v>74.18179719</v>
+        <v>74.16401603</v>
       </c>
       <c r="R39" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S39">
-        <v>32401</v>
+        <v>54819.5</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -2953,28 +2944,28 @@
         <v>23</v>
       </c>
       <c r="E40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F40">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="G40" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H40">
-        <v>30.132598</v>
+        <v>30.178444</v>
       </c>
       <c r="I40">
-        <v>74.343463</v>
+        <v>74.065141</v>
       </c>
       <c r="J40" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K40">
         <v>407</v>
       </c>
       <c r="L40" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M40" t="s">
         <v>21</v>
@@ -2983,7 +2974,7 @@
         <v>23</v>
       </c>
       <c r="O40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P40">
         <v>30.126927</v>
@@ -2992,10 +2983,10 @@
         <v>74.161942</v>
       </c>
       <c r="R40" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S40">
-        <v>73685</v>
+        <v>37768</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -3012,28 +3003,28 @@
         <v>23</v>
       </c>
       <c r="E41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F41">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="G41" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H41">
-        <v>30.065633</v>
+        <v>30.196706</v>
       </c>
       <c r="I41">
-        <v>73.98462499999999</v>
+        <v>74.04839699999999</v>
       </c>
       <c r="J41" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K41">
         <v>407</v>
       </c>
       <c r="L41" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M41" t="s">
         <v>21</v>
@@ -3042,7 +3033,7 @@
         <v>23</v>
       </c>
       <c r="O41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P41">
         <v>30.126927</v>
@@ -3051,10 +3042,10 @@
         <v>74.161942</v>
       </c>
       <c r="R41" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S41">
-        <v>34208</v>
+        <v>29874.5</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -3071,28 +3062,28 @@
         <v>23</v>
       </c>
       <c r="E42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F42">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="G42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H42">
-        <v>29.956267</v>
+        <v>30.035803</v>
       </c>
       <c r="I42">
-        <v>74.332578</v>
+        <v>74.111367</v>
       </c>
       <c r="J42" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K42">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="L42" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M42" t="s">
         <v>21</v>
@@ -3101,19 +3092,19 @@
         <v>23</v>
       </c>
       <c r="O42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P42">
-        <v>30.08793156</v>
+        <v>30.126927</v>
       </c>
       <c r="Q42">
-        <v>74.20908439</v>
+        <v>74.161942</v>
       </c>
       <c r="R42" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S42">
-        <v>17701</v>
+        <v>56983.5</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -3130,28 +3121,28 @@
         <v>23</v>
       </c>
       <c r="E43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F43">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="G43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H43">
-        <v>30.224829</v>
+        <v>30.131281</v>
       </c>
       <c r="I43">
-        <v>74.12361199999999</v>
+        <v>74.103374</v>
       </c>
       <c r="J43" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K43">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="L43" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M43" t="s">
         <v>21</v>
@@ -3160,19 +3151,19 @@
         <v>23</v>
       </c>
       <c r="O43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P43">
-        <v>30.15809938</v>
+        <v>30.126927</v>
       </c>
       <c r="Q43">
-        <v>74.16401603</v>
+        <v>74.161942</v>
       </c>
       <c r="R43" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S43">
-        <v>54819.5</v>
+        <v>23195.5</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -3189,28 +3180,28 @@
         <v>23</v>
       </c>
       <c r="E44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F44">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="G44" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H44">
-        <v>30.178444</v>
+        <v>30.029455</v>
       </c>
       <c r="I44">
-        <v>74.065141</v>
+        <v>74.077962</v>
       </c>
       <c r="J44" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K44">
         <v>407</v>
       </c>
       <c r="L44" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M44" t="s">
         <v>21</v>
@@ -3219,7 +3210,7 @@
         <v>23</v>
       </c>
       <c r="O44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P44">
         <v>30.126927</v>
@@ -3228,10 +3219,10 @@
         <v>74.161942</v>
       </c>
       <c r="R44" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S44">
-        <v>37768</v>
+        <v>57368</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -3248,28 +3239,28 @@
         <v>23</v>
       </c>
       <c r="E45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F45">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="G45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H45">
-        <v>30.196706</v>
+        <v>29.983545</v>
       </c>
       <c r="I45">
-        <v>74.04839699999999</v>
+        <v>74.173574</v>
       </c>
       <c r="J45" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K45">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="L45" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M45" t="s">
         <v>21</v>
@@ -3278,19 +3269,19 @@
         <v>23</v>
       </c>
       <c r="O45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P45">
-        <v>30.126927</v>
+        <v>30.10552983</v>
       </c>
       <c r="Q45">
-        <v>74.161942</v>
+        <v>74.18014506</v>
       </c>
       <c r="R45" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S45">
-        <v>29874.5</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="46" spans="1:19">
@@ -3307,28 +3298,28 @@
         <v>23</v>
       </c>
       <c r="E46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F46">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="G46" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H46">
-        <v>30.035803</v>
+        <v>30.254422</v>
       </c>
       <c r="I46">
-        <v>74.111367</v>
+        <v>74.126414</v>
       </c>
       <c r="J46" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K46">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="L46" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M46" t="s">
         <v>21</v>
@@ -3337,19 +3328,19 @@
         <v>23</v>
       </c>
       <c r="O46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P46">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q46">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="R46" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S46">
-        <v>56983.5</v>
+        <v>29195</v>
       </c>
     </row>
     <row r="47" spans="1:19">
@@ -3366,28 +3357,28 @@
         <v>23</v>
       </c>
       <c r="E47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F47">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="G47" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H47">
-        <v>30.131281</v>
+        <v>30.247905</v>
       </c>
       <c r="I47">
-        <v>74.103374</v>
+        <v>74.129536</v>
       </c>
       <c r="J47" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K47">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="L47" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M47" t="s">
         <v>21</v>
@@ -3396,19 +3387,19 @@
         <v>23</v>
       </c>
       <c r="O47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P47">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q47">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="R47" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S47">
-        <v>23195.5</v>
+        <v>26795</v>
       </c>
     </row>
     <row r="48" spans="1:19">
@@ -3425,28 +3416,28 @@
         <v>23</v>
       </c>
       <c r="E48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F48">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="G48" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H48">
-        <v>30.027734</v>
+        <v>30.25374</v>
       </c>
       <c r="I48">
-        <v>74.36728100000001</v>
+        <v>74.122122</v>
       </c>
       <c r="J48" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K48">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="L48" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M48" t="s">
         <v>21</v>
@@ -3455,19 +3446,19 @@
         <v>23</v>
       </c>
       <c r="O48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P48">
-        <v>30.08793156</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q48">
-        <v>74.20908439</v>
+        <v>74.16401603</v>
       </c>
       <c r="R48" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S48">
-        <v>71340</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="49" spans="1:19">
@@ -3484,28 +3475,28 @@
         <v>23</v>
       </c>
       <c r="E49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F49">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="G49" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H49">
-        <v>30.027734</v>
+        <v>29.975306</v>
       </c>
       <c r="I49">
-        <v>74.36728100000001</v>
+        <v>74.164011</v>
       </c>
       <c r="J49" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K49">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="L49" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M49" t="s">
         <v>21</v>
@@ -3514,19 +3505,19 @@
         <v>23</v>
       </c>
       <c r="O49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P49">
-        <v>30.0974593</v>
+        <v>30.10552983</v>
       </c>
       <c r="Q49">
-        <v>74.206666</v>
+        <v>74.18014506</v>
       </c>
       <c r="R49" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S49">
-        <v>36210</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="50" spans="1:19">
@@ -3543,28 +3534,28 @@
         <v>23</v>
       </c>
       <c r="E50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F50">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="G50" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H50">
-        <v>29.951208</v>
+        <v>30.144184</v>
       </c>
       <c r="I50">
-        <v>74.380385</v>
+        <v>74.122771</v>
       </c>
       <c r="J50" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K50">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="L50" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M50" t="s">
         <v>21</v>
@@ -3573,19 +3564,19 @@
         <v>23</v>
       </c>
       <c r="O50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P50">
-        <v>30.08793156</v>
+        <v>30.126927</v>
       </c>
       <c r="Q50">
-        <v>74.20908439</v>
+        <v>74.161942</v>
       </c>
       <c r="R50" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S50">
-        <v>43549</v>
+        <v>12630.5</v>
       </c>
     </row>
     <row r="51" spans="1:19">
@@ -3602,28 +3593,28 @@
         <v>23</v>
       </c>
       <c r="E51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F51">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="G51" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H51">
-        <v>30.029455</v>
+        <v>30.161715</v>
       </c>
       <c r="I51">
-        <v>74.077962</v>
+        <v>73.987483</v>
       </c>
       <c r="J51" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K51">
         <v>407</v>
       </c>
       <c r="L51" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M51" t="s">
         <v>21</v>
@@ -3632,7 +3623,7 @@
         <v>23</v>
       </c>
       <c r="O51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P51">
         <v>30.126927</v>
@@ -3641,10 +3632,10 @@
         <v>74.161942</v>
       </c>
       <c r="R51" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S51">
-        <v>57368</v>
+        <v>13803</v>
       </c>
     </row>
     <row r="52" spans="1:19">
@@ -3661,28 +3652,28 @@
         <v>23</v>
       </c>
       <c r="E52" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F52">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="G52" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H52">
-        <v>29.983545</v>
+        <v>30.21135</v>
       </c>
       <c r="I52">
-        <v>74.173574</v>
+        <v>74.02397999999999</v>
       </c>
       <c r="J52" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K52">
         <v>407</v>
       </c>
       <c r="L52" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M52" t="s">
         <v>21</v>
@@ -3691,7 +3682,7 @@
         <v>23</v>
       </c>
       <c r="O52" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P52">
         <v>30.126927</v>
@@ -3700,10 +3691,10 @@
         <v>74.161942</v>
       </c>
       <c r="R52" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S52">
-        <v>2487</v>
+        <v>9145</v>
       </c>
     </row>
     <row r="53" spans="1:19">
@@ -3720,28 +3711,28 @@
         <v>23</v>
       </c>
       <c r="E53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F53">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="G53" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H53">
-        <v>30.254422</v>
+        <v>30.296726</v>
       </c>
       <c r="I53">
-        <v>74.126414</v>
+        <v>74.263169</v>
       </c>
       <c r="J53" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K53">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L53" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M53" t="s">
         <v>21</v>
@@ -3750,19 +3741,19 @@
         <v>23</v>
       </c>
       <c r="O53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P53">
-        <v>30.15809938</v>
+        <v>30.17081207</v>
       </c>
       <c r="Q53">
-        <v>74.16401603</v>
+        <v>74.18179719</v>
       </c>
       <c r="R53" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S53">
-        <v>29195</v>
+        <v>17622.5</v>
       </c>
     </row>
     <row r="54" spans="1:19">
@@ -3779,28 +3770,28 @@
         <v>23</v>
       </c>
       <c r="E54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F54">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="G54" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H54">
-        <v>30.247905</v>
+        <v>30.285139</v>
       </c>
       <c r="I54">
-        <v>74.129536</v>
+        <v>74.172681</v>
       </c>
       <c r="J54" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K54">
         <v>400</v>
       </c>
       <c r="L54" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M54" t="s">
         <v>21</v>
@@ -3809,7 +3800,7 @@
         <v>23</v>
       </c>
       <c r="O54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P54">
         <v>30.15809938</v>
@@ -3818,10 +3809,10 @@
         <v>74.16401603</v>
       </c>
       <c r="R54" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S54">
-        <v>26795</v>
+        <v>2347.5</v>
       </c>
     </row>
     <row r="55" spans="1:19">
@@ -3838,28 +3829,28 @@
         <v>23</v>
       </c>
       <c r="E55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F55">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="G55" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H55">
-        <v>30.25374</v>
+        <v>30.285139</v>
       </c>
       <c r="I55">
-        <v>74.122122</v>
+        <v>74.172681</v>
       </c>
       <c r="J55" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K55">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L55" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M55" t="s">
         <v>21</v>
@@ -3868,19 +3859,19 @@
         <v>23</v>
       </c>
       <c r="O55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P55">
-        <v>30.15809938</v>
+        <v>30.17767461</v>
       </c>
       <c r="Q55">
-        <v>74.16401603</v>
+        <v>74.17723581</v>
       </c>
       <c r="R55" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S55">
-        <v>7950</v>
+        <v>40337.5</v>
       </c>
     </row>
     <row r="56" spans="1:19">
@@ -3897,28 +3888,28 @@
         <v>23</v>
       </c>
       <c r="E56" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F56">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="G56" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H56">
-        <v>29.975306</v>
+        <v>30.260814</v>
       </c>
       <c r="I56">
-        <v>74.164011</v>
+        <v>74.269329</v>
       </c>
       <c r="J56" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K56">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="L56" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M56" t="s">
         <v>21</v>
@@ -3927,19 +3918,19 @@
         <v>23</v>
       </c>
       <c r="O56" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P56">
-        <v>30.126927</v>
+        <v>30.17081207</v>
       </c>
       <c r="Q56">
-        <v>74.161942</v>
+        <v>74.18179719</v>
       </c>
       <c r="R56" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S56">
-        <v>5500</v>
+        <v>56502.5</v>
       </c>
     </row>
     <row r="57" spans="1:19">
@@ -3956,28 +3947,28 @@
         <v>23</v>
       </c>
       <c r="E57" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F57">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="G57" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H57">
-        <v>30.144184</v>
+        <v>30.290503</v>
       </c>
       <c r="I57">
-        <v>74.122771</v>
+        <v>74.220803</v>
       </c>
       <c r="J57" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K57">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="L57" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M57" t="s">
         <v>21</v>
@@ -3986,19 +3977,19 @@
         <v>23</v>
       </c>
       <c r="O57" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P57">
-        <v>30.126927</v>
+        <v>30.17081207</v>
       </c>
       <c r="Q57">
-        <v>74.161942</v>
+        <v>74.18179719</v>
       </c>
       <c r="R57" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S57">
-        <v>12630.5</v>
+        <v>43110</v>
       </c>
     </row>
     <row r="58" spans="1:19">
@@ -4015,28 +4006,28 @@
         <v>23</v>
       </c>
       <c r="E58" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F58">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="G58" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H58">
-        <v>30.161715</v>
+        <v>30.251211</v>
       </c>
       <c r="I58">
-        <v>73.987483</v>
+        <v>74.011872</v>
       </c>
       <c r="J58" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K58">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="L58" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M58" t="s">
         <v>21</v>
@@ -4045,19 +4036,19 @@
         <v>23</v>
       </c>
       <c r="O58" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P58">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q58">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="R58" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S58">
-        <v>13803</v>
+        <v>128218</v>
       </c>
     </row>
     <row r="59" spans="1:19">
@@ -4074,28 +4065,28 @@
         <v>23</v>
       </c>
       <c r="E59" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F59">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="G59" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H59">
-        <v>30.21135</v>
+        <v>30.280985</v>
       </c>
       <c r="I59">
-        <v>74.02397999999999</v>
+        <v>74.057811</v>
       </c>
       <c r="J59" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K59">
         <v>400</v>
       </c>
       <c r="L59" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M59" t="s">
         <v>21</v>
@@ -4104,7 +4095,7 @@
         <v>23</v>
       </c>
       <c r="O59" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P59">
         <v>30.15809938</v>
@@ -4113,10 +4104,10 @@
         <v>74.16401603</v>
       </c>
       <c r="R59" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S59">
-        <v>9145</v>
+        <v>62709.5</v>
       </c>
     </row>
     <row r="60" spans="1:19">
@@ -4133,28 +4124,28 @@
         <v>23</v>
       </c>
       <c r="E60" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F60">
-        <v>549</v>
+        <v>612</v>
       </c>
       <c r="G60" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H60">
-        <v>30.296726</v>
+        <v>30.3064</v>
       </c>
       <c r="I60">
-        <v>74.263169</v>
+        <v>74.22073899999999</v>
       </c>
       <c r="J60" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K60">
         <v>401</v>
       </c>
       <c r="L60" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M60" t="s">
         <v>21</v>
@@ -4163,7 +4154,7 @@
         <v>23</v>
       </c>
       <c r="O60" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P60">
         <v>30.17081207</v>
@@ -4172,10 +4163,10 @@
         <v>74.18179719</v>
       </c>
       <c r="R60" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S60">
-        <v>17622.5</v>
+        <v>47189.5</v>
       </c>
     </row>
     <row r="61" spans="1:19">
@@ -4189,52 +4180,52 @@
         <v>21</v>
       </c>
       <c r="D61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F61">
-        <v>550</v>
+        <v>1046</v>
       </c>
       <c r="G61" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H61">
-        <v>30.285139</v>
+        <v>31.425406</v>
       </c>
       <c r="I61">
-        <v>74.172681</v>
+        <v>75.719528</v>
       </c>
       <c r="J61" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K61">
-        <v>402</v>
+        <v>625</v>
       </c>
       <c r="L61" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M61" t="s">
         <v>21</v>
       </c>
       <c r="N61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P61">
-        <v>30.17767461</v>
+        <v>31.408658</v>
       </c>
       <c r="Q61">
-        <v>74.17723581</v>
+        <v>75.685958</v>
       </c>
       <c r="R61" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S61">
-        <v>42685</v>
+        <v>21500</v>
       </c>
     </row>
     <row r="62" spans="1:19">
@@ -4248,52 +4239,52 @@
         <v>21</v>
       </c>
       <c r="D62" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E62" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F62">
-        <v>551</v>
+        <v>1577</v>
       </c>
       <c r="G62" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H62">
-        <v>30.260814</v>
+        <v>30.4426709</v>
       </c>
       <c r="I62">
-        <v>74.269329</v>
+        <v>74.4101264</v>
       </c>
       <c r="J62" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K62">
-        <v>401</v>
+        <v>866</v>
       </c>
       <c r="L62" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M62" t="s">
         <v>21</v>
       </c>
       <c r="N62" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="O62" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P62">
-        <v>30.17081207</v>
+        <v>30.458388</v>
       </c>
       <c r="Q62">
-        <v>74.18179719</v>
+        <v>74.453514</v>
       </c>
       <c r="R62" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S62">
-        <v>56502.5</v>
+        <v>88594</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4307,52 +4298,52 @@
         <v>21</v>
       </c>
       <c r="D63" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F63">
-        <v>552</v>
+        <v>1577</v>
       </c>
       <c r="G63" t="s">
         <v>76</v>
       </c>
       <c r="H63">
-        <v>30.290503</v>
+        <v>30.4426709</v>
       </c>
       <c r="I63">
-        <v>74.220803</v>
+        <v>74.4101264</v>
       </c>
       <c r="J63" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K63">
-        <v>401</v>
+        <v>870</v>
       </c>
       <c r="L63" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M63" t="s">
         <v>21</v>
       </c>
       <c r="N63" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="O63" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P63">
-        <v>30.17081207</v>
+        <v>30.458388</v>
       </c>
       <c r="Q63">
-        <v>74.18179719</v>
+        <v>74.453514</v>
       </c>
       <c r="R63" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S63">
-        <v>43110</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="64" spans="1:19">
@@ -4366,37 +4357,37 @@
         <v>21</v>
       </c>
       <c r="D64" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E64" t="s">
         <v>27</v>
       </c>
       <c r="F64">
-        <v>1322</v>
+        <v>1577</v>
       </c>
       <c r="G64" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="H64">
-        <v>30.67924</v>
+        <v>30.4426709</v>
       </c>
       <c r="I64">
-        <v>75.84139999999999</v>
+        <v>74.4101264</v>
       </c>
       <c r="J64" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K64">
-        <v>864</v>
+        <v>875</v>
       </c>
       <c r="L64" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M64" t="s">
         <v>21</v>
       </c>
       <c r="N64" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="O64" t="s">
         <v>27</v>
@@ -4408,10 +4399,10 @@
         <v>74.453514</v>
       </c>
       <c r="R64" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S64">
-        <v>197630</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="65" spans="1:19">
@@ -4425,37 +4416,37 @@
         <v>21</v>
       </c>
       <c r="D65" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E65" t="s">
         <v>27</v>
       </c>
       <c r="F65">
-        <v>1322</v>
+        <v>1577</v>
       </c>
       <c r="G65" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="H65">
-        <v>30.67924</v>
+        <v>30.4426709</v>
       </c>
       <c r="I65">
-        <v>75.84139999999999</v>
+        <v>74.4101264</v>
       </c>
       <c r="J65" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K65">
-        <v>865</v>
+        <v>876</v>
       </c>
       <c r="L65" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M65" t="s">
         <v>21</v>
       </c>
       <c r="N65" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="O65" t="s">
         <v>27</v>
@@ -4467,10 +4458,10 @@
         <v>74.453514</v>
       </c>
       <c r="R65" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S65">
-        <v>16680</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="66" spans="1:19">
@@ -4484,37 +4475,37 @@
         <v>21</v>
       </c>
       <c r="D66" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E66" t="s">
         <v>27</v>
       </c>
       <c r="F66">
-        <v>1322</v>
+        <v>1597</v>
       </c>
       <c r="G66" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="H66">
-        <v>30.67924</v>
+        <v>30.419565</v>
       </c>
       <c r="I66">
-        <v>75.84139999999999</v>
+        <v>74.44302166999999</v>
       </c>
       <c r="J66" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K66">
         <v>866</v>
       </c>
       <c r="L66" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M66" t="s">
         <v>21</v>
       </c>
       <c r="N66" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="O66" t="s">
         <v>27</v>
@@ -4526,10 +4517,10 @@
         <v>74.453514</v>
       </c>
       <c r="R66" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S66">
-        <v>42630</v>
+        <v>38086</v>
       </c>
     </row>
     <row r="67" spans="1:19">
@@ -4543,37 +4534,37 @@
         <v>21</v>
       </c>
       <c r="D67" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E67" t="s">
         <v>27</v>
       </c>
       <c r="F67">
-        <v>1322</v>
+        <v>1597</v>
       </c>
       <c r="G67" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="H67">
-        <v>30.67924</v>
+        <v>30.419565</v>
       </c>
       <c r="I67">
-        <v>75.84139999999999</v>
+        <v>74.44302166999999</v>
       </c>
       <c r="J67" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K67">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="L67" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M67" t="s">
         <v>21</v>
       </c>
       <c r="N67" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="O67" t="s">
         <v>27</v>
@@ -4585,10 +4576,10 @@
         <v>74.453514</v>
       </c>
       <c r="R67" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S67">
-        <v>10000</v>
+        <v>30720</v>
       </c>
     </row>
     <row r="68" spans="1:19">
@@ -4602,37 +4593,37 @@
         <v>21</v>
       </c>
       <c r="D68" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E68" t="s">
         <v>27</v>
       </c>
       <c r="F68">
-        <v>1322</v>
+        <v>1597</v>
       </c>
       <c r="G68" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="H68">
-        <v>30.67924</v>
+        <v>30.419565</v>
       </c>
       <c r="I68">
-        <v>75.84139999999999</v>
+        <v>74.44302166999999</v>
       </c>
       <c r="J68" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K68">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="L68" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M68" t="s">
         <v>21</v>
       </c>
       <c r="N68" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="O68" t="s">
         <v>27</v>
@@ -4644,10 +4635,10 @@
         <v>74.453514</v>
       </c>
       <c r="R68" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S68">
-        <v>10000</v>
+        <v>5127</v>
       </c>
     </row>
     <row r="69" spans="1:19">
@@ -4661,37 +4652,37 @@
         <v>21</v>
       </c>
       <c r="D69" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E69" t="s">
         <v>27</v>
       </c>
       <c r="F69">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G69" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="H69">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I69">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J69" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K69">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="L69" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M69" t="s">
         <v>21</v>
       </c>
       <c r="N69" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="O69" t="s">
         <v>27</v>
@@ -4703,10 +4694,10 @@
         <v>74.453514</v>
       </c>
       <c r="R69" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S69">
-        <v>10000</v>
+        <v>294680</v>
       </c>
     </row>
     <row r="70" spans="1:19">
@@ -4720,37 +4711,37 @@
         <v>21</v>
       </c>
       <c r="D70" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E70" t="s">
         <v>27</v>
       </c>
       <c r="F70">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G70" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="H70">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I70">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J70" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K70">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="L70" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M70" t="s">
         <v>21</v>
       </c>
       <c r="N70" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="O70" t="s">
         <v>27</v>
@@ -4762,10 +4753,10 @@
         <v>74.453514</v>
       </c>
       <c r="R70" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S70">
-        <v>30720</v>
+        <v>16680</v>
       </c>
     </row>
     <row r="71" spans="1:19">
@@ -4779,37 +4770,37 @@
         <v>21</v>
       </c>
       <c r="D71" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E71" t="s">
         <v>27</v>
       </c>
       <c r="F71">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G71" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="H71">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I71">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J71" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K71">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="L71" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M71" t="s">
         <v>21</v>
       </c>
       <c r="N71" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="O71" t="s">
         <v>27</v>
@@ -4821,10 +4812,10 @@
         <v>74.453514</v>
       </c>
       <c r="R71" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S71">
-        <v>1080</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="72" spans="1:19">
@@ -4838,37 +4829,37 @@
         <v>21</v>
       </c>
       <c r="D72" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E72" t="s">
         <v>27</v>
       </c>
       <c r="F72">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G72" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="H72">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I72">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J72" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K72">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="L72" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M72" t="s">
         <v>21</v>
       </c>
       <c r="N72" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="O72" t="s">
         <v>27</v>
@@ -4880,10 +4871,10 @@
         <v>74.453514</v>
       </c>
       <c r="R72" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S72">
-        <v>29640</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="73" spans="1:19">
@@ -4897,37 +4888,37 @@
         <v>21</v>
       </c>
       <c r="D73" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E73" t="s">
         <v>27</v>
       </c>
       <c r="F73">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G73" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="H73">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I73">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J73" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K73">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="L73" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M73" t="s">
         <v>21</v>
       </c>
       <c r="N73" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="O73" t="s">
         <v>27</v>
@@ -4939,10 +4930,10 @@
         <v>74.453514</v>
       </c>
       <c r="R73" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S73">
-        <v>9950</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="74" spans="1:19">
@@ -4956,37 +4947,37 @@
         <v>21</v>
       </c>
       <c r="D74" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E74" t="s">
         <v>27</v>
       </c>
       <c r="F74">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G74" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H74">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I74">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J74" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K74">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="L74" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M74" t="s">
         <v>21</v>
       </c>
       <c r="N74" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="O74" t="s">
         <v>27</v>
@@ -4998,10 +4989,10 @@
         <v>74.453514</v>
       </c>
       <c r="R74" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S74">
-        <v>10000</v>
+        <v>30720</v>
       </c>
     </row>
     <row r="75" spans="1:19">
@@ -5015,37 +5006,37 @@
         <v>21</v>
       </c>
       <c r="D75" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E75" t="s">
         <v>27</v>
       </c>
       <c r="F75">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G75" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H75">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I75">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J75" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K75">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="L75" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M75" t="s">
         <v>21</v>
       </c>
       <c r="N75" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="O75" t="s">
         <v>27</v>
@@ -5057,10 +5048,10 @@
         <v>74.453514</v>
       </c>
       <c r="R75" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S75">
-        <v>5000</v>
+        <v>29640</v>
       </c>
     </row>
     <row r="76" spans="1:19">
@@ -5074,37 +5065,37 @@
         <v>21</v>
       </c>
       <c r="D76" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E76" t="s">
         <v>27</v>
       </c>
       <c r="F76">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G76" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H76">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I76">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J76" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K76">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="L76" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M76" t="s">
         <v>21</v>
       </c>
       <c r="N76" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="O76" t="s">
         <v>27</v>
@@ -5116,10 +5107,10 @@
         <v>74.453514</v>
       </c>
       <c r="R76" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S76">
-        <v>5000</v>
+        <v>28460</v>
       </c>
     </row>
     <row r="77" spans="1:19">
@@ -5133,37 +5124,37 @@
         <v>21</v>
       </c>
       <c r="D77" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E77" t="s">
         <v>27</v>
       </c>
       <c r="F77">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G77" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H77">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I77">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J77" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K77">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="L77" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M77" t="s">
         <v>21</v>
       </c>
       <c r="N77" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="O77" t="s">
         <v>27</v>
@@ -5175,10 +5166,10 @@
         <v>74.453514</v>
       </c>
       <c r="R77" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S77">
-        <v>20480</v>
+        <v>15353</v>
       </c>
     </row>
     <row r="78" spans="1:19">
@@ -5192,37 +5183,37 @@
         <v>21</v>
       </c>
       <c r="D78" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E78" t="s">
         <v>27</v>
       </c>
       <c r="F78">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G78" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H78">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I78">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J78" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K78">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="L78" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M78" t="s">
         <v>21</v>
       </c>
       <c r="N78" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="O78" t="s">
         <v>27</v>
@@ -5234,10 +5225,10 @@
         <v>74.453514</v>
       </c>
       <c r="R78" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S78">
-        <v>18000</v>
+        <v>20480</v>
       </c>
     </row>
     <row r="79" spans="1:19">
@@ -5251,37 +5242,37 @@
         <v>21</v>
       </c>
       <c r="D79" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E79" t="s">
         <v>27</v>
       </c>
       <c r="F79">
-        <v>1324</v>
+        <v>1607</v>
       </c>
       <c r="G79" t="s">
         <v>78</v>
       </c>
       <c r="H79">
-        <v>30.59296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I79">
-        <v>75.78903</v>
+        <v>74.5049465</v>
       </c>
       <c r="J79" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K79">
-        <v>864</v>
+        <v>879</v>
       </c>
       <c r="L79" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M79" t="s">
         <v>21</v>
       </c>
       <c r="N79" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="O79" t="s">
         <v>27</v>
@@ -5293,10 +5284,10 @@
         <v>74.453514</v>
       </c>
       <c r="R79" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S79">
-        <v>41830</v>
+        <v>20480</v>
       </c>
     </row>
     <row r="80" spans="1:19">
@@ -5310,37 +5301,37 @@
         <v>21</v>
       </c>
       <c r="D80" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E80" t="s">
         <v>27</v>
       </c>
       <c r="F80">
-        <v>1325</v>
+        <v>1607</v>
       </c>
       <c r="G80" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H80">
-        <v>30.61907</v>
+        <v>30.4726737</v>
       </c>
       <c r="I80">
-        <v>75.8098</v>
+        <v>74.5049465</v>
       </c>
       <c r="J80" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K80">
-        <v>864</v>
+        <v>880</v>
       </c>
       <c r="L80" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M80" t="s">
         <v>21</v>
       </c>
       <c r="N80" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="O80" t="s">
         <v>27</v>
@@ -5352,10 +5343,10 @@
         <v>74.453514</v>
       </c>
       <c r="R80" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S80">
-        <v>55220</v>
+        <v>15360</v>
       </c>
     </row>
     <row r="81" spans="1:19">
@@ -5369,52 +5360,52 @@
         <v>21</v>
       </c>
       <c r="D81" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E81" t="s">
         <v>27</v>
       </c>
       <c r="F81">
-        <v>1326</v>
+        <v>1660</v>
       </c>
       <c r="G81" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H81">
-        <v>30.60582</v>
+        <v>30.2397029</v>
       </c>
       <c r="I81">
-        <v>75.87558</v>
+        <v>74.2953411</v>
       </c>
       <c r="J81" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K81">
-        <v>866</v>
+        <v>401</v>
       </c>
       <c r="L81" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M81" t="s">
         <v>21</v>
       </c>
       <c r="N81" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O81" t="s">
         <v>27</v>
       </c>
       <c r="P81">
-        <v>30.458388</v>
+        <v>30.17081207</v>
       </c>
       <c r="Q81">
-        <v>74.453514</v>
+        <v>74.18179719</v>
       </c>
       <c r="R81" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S81">
-        <v>13140</v>
+        <v>1314.5</v>
       </c>
     </row>
     <row r="82" spans="1:19">
@@ -5428,52 +5419,52 @@
         <v>21</v>
       </c>
       <c r="D82" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E82" t="s">
         <v>27</v>
       </c>
       <c r="F82">
-        <v>1326</v>
+        <v>1660</v>
       </c>
       <c r="G82" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H82">
-        <v>30.60582</v>
+        <v>30.2397029</v>
       </c>
       <c r="I82">
-        <v>75.87558</v>
+        <v>74.2953411</v>
       </c>
       <c r="J82" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K82">
-        <v>874</v>
+        <v>406</v>
       </c>
       <c r="L82" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M82" t="s">
         <v>21</v>
       </c>
       <c r="N82" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O82" t="s">
         <v>27</v>
       </c>
       <c r="P82">
-        <v>30.458388</v>
+        <v>30.16991135</v>
       </c>
       <c r="Q82">
-        <v>74.453514</v>
+        <v>74.18230296</v>
       </c>
       <c r="R82" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S82">
-        <v>28460</v>
+        <v>52394.5</v>
       </c>
     </row>
     <row r="83" spans="1:19">
@@ -5487,52 +5478,52 @@
         <v>21</v>
       </c>
       <c r="D83" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E83" t="s">
         <v>27</v>
       </c>
       <c r="F83">
-        <v>1326</v>
+        <v>2153</v>
       </c>
       <c r="G83" t="s">
         <v>80</v>
       </c>
       <c r="H83">
-        <v>30.60582</v>
+        <v>31.3953454</v>
       </c>
       <c r="I83">
-        <v>75.87558</v>
+        <v>74.6222925</v>
       </c>
       <c r="J83" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K83">
-        <v>879</v>
+        <v>2</v>
       </c>
       <c r="L83" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M83" t="s">
         <v>21</v>
       </c>
       <c r="N83" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O83" t="s">
         <v>27</v>
       </c>
       <c r="P83">
-        <v>30.458388</v>
+        <v>31.45335</v>
       </c>
       <c r="Q83">
-        <v>74.453514</v>
+        <v>74.46541999999999</v>
       </c>
       <c r="R83" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S83">
-        <v>2480</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="84" spans="1:19">
@@ -5546,288 +5537,52 @@
         <v>21</v>
       </c>
       <c r="D84" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E84" t="s">
         <v>27</v>
       </c>
       <c r="F84">
-        <v>1327</v>
+        <v>2153</v>
       </c>
       <c r="G84" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H84">
-        <v>30.62411</v>
+        <v>31.3953454</v>
       </c>
       <c r="I84">
-        <v>75.75073</v>
+        <v>74.6222925</v>
       </c>
       <c r="J84" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K84">
-        <v>866</v>
+        <v>4</v>
       </c>
       <c r="L84" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M84" t="s">
         <v>21</v>
       </c>
       <c r="N84" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O84" t="s">
         <v>27</v>
       </c>
       <c r="P84">
-        <v>30.458388</v>
+        <v>31.45335</v>
       </c>
       <c r="Q84">
-        <v>74.453514</v>
+        <v>74.46541999999999</v>
       </c>
       <c r="R84" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S84">
-        <v>59240</v>
-      </c>
-    </row>
-    <row r="85" spans="1:19">
-      <c r="A85" t="s">
-        <v>19</v>
-      </c>
-      <c r="B85" t="s">
-        <v>20</v>
-      </c>
-      <c r="C85" t="s">
-        <v>21</v>
-      </c>
-      <c r="D85" t="s">
-        <v>24</v>
-      </c>
-      <c r="E85" t="s">
-        <v>27</v>
-      </c>
-      <c r="F85">
-        <v>1328</v>
-      </c>
-      <c r="G85" t="s">
-        <v>82</v>
-      </c>
-      <c r="H85">
-        <v>30.58776</v>
-      </c>
-      <c r="I85">
-        <v>75.81787</v>
-      </c>
-      <c r="J85" t="s">
-        <v>85</v>
-      </c>
-      <c r="K85">
-        <v>866</v>
-      </c>
-      <c r="L85" t="s">
-        <v>86</v>
-      </c>
-      <c r="M85" t="s">
-        <v>21</v>
-      </c>
-      <c r="N85" t="s">
-        <v>24</v>
-      </c>
-      <c r="O85" t="s">
-        <v>27</v>
-      </c>
-      <c r="P85">
-        <v>30.458388</v>
-      </c>
-      <c r="Q85">
-        <v>74.453514</v>
-      </c>
-      <c r="R85" t="s">
-        <v>87</v>
-      </c>
-      <c r="S85">
-        <v>11670</v>
-      </c>
-    </row>
-    <row r="86" spans="1:19">
-      <c r="A86" t="s">
-        <v>19</v>
-      </c>
-      <c r="B86" t="s">
-        <v>20</v>
-      </c>
-      <c r="C86" t="s">
-        <v>21</v>
-      </c>
-      <c r="D86" t="s">
-        <v>24</v>
-      </c>
-      <c r="E86" t="s">
-        <v>27</v>
-      </c>
-      <c r="F86">
-        <v>1328</v>
-      </c>
-      <c r="G86" t="s">
-        <v>82</v>
-      </c>
-      <c r="H86">
-        <v>30.58776</v>
-      </c>
-      <c r="I86">
-        <v>75.81787</v>
-      </c>
-      <c r="J86" t="s">
-        <v>85</v>
-      </c>
-      <c r="K86">
-        <v>880</v>
-      </c>
-      <c r="L86" t="s">
-        <v>86</v>
-      </c>
-      <c r="M86" t="s">
-        <v>21</v>
-      </c>
-      <c r="N86" t="s">
-        <v>24</v>
-      </c>
-      <c r="O86" t="s">
-        <v>27</v>
-      </c>
-      <c r="P86">
-        <v>30.458388</v>
-      </c>
-      <c r="Q86">
-        <v>74.453514</v>
-      </c>
-      <c r="R86" t="s">
-        <v>87</v>
-      </c>
-      <c r="S86">
-        <v>15360</v>
-      </c>
-    </row>
-    <row r="87" spans="1:19">
-      <c r="A87" t="s">
-        <v>19</v>
-      </c>
-      <c r="B87" t="s">
-        <v>20</v>
-      </c>
-      <c r="C87" t="s">
-        <v>21</v>
-      </c>
-      <c r="D87" t="s">
-        <v>24</v>
-      </c>
-      <c r="E87" t="s">
-        <v>27</v>
-      </c>
-      <c r="F87">
-        <v>1329</v>
-      </c>
-      <c r="G87" t="s">
-        <v>83</v>
-      </c>
-      <c r="H87">
-        <v>30.669134</v>
-      </c>
-      <c r="I87">
-        <v>75.877723</v>
-      </c>
-      <c r="J87" t="s">
-        <v>85</v>
-      </c>
-      <c r="K87">
-        <v>877</v>
-      </c>
-      <c r="L87" t="s">
-        <v>86</v>
-      </c>
-      <c r="M87" t="s">
-        <v>21</v>
-      </c>
-      <c r="N87" t="s">
-        <v>24</v>
-      </c>
-      <c r="O87" t="s">
-        <v>27</v>
-      </c>
-      <c r="P87">
-        <v>30.458388</v>
-      </c>
-      <c r="Q87">
-        <v>74.453514</v>
-      </c>
-      <c r="R87" t="s">
-        <v>87</v>
-      </c>
-      <c r="S87">
-        <v>10530</v>
-      </c>
-    </row>
-    <row r="88" spans="1:19">
-      <c r="A88" t="s">
-        <v>19</v>
-      </c>
-      <c r="B88" t="s">
-        <v>20</v>
-      </c>
-      <c r="C88" t="s">
-        <v>21</v>
-      </c>
-      <c r="D88" t="s">
-        <v>24</v>
-      </c>
-      <c r="E88" t="s">
-        <v>27</v>
-      </c>
-      <c r="F88">
-        <v>1330</v>
-      </c>
-      <c r="G88" t="s">
-        <v>84</v>
-      </c>
-      <c r="H88">
-        <v>30.651445</v>
-      </c>
-      <c r="I88">
-        <v>75.890028</v>
-      </c>
-      <c r="J88" t="s">
-        <v>85</v>
-      </c>
-      <c r="K88">
-        <v>872</v>
-      </c>
-      <c r="L88" t="s">
-        <v>86</v>
-      </c>
-      <c r="M88" t="s">
-        <v>21</v>
-      </c>
-      <c r="N88" t="s">
-        <v>24</v>
-      </c>
-      <c r="O88" t="s">
-        <v>27</v>
-      </c>
-      <c r="P88">
-        <v>30.458388</v>
-      </c>
-      <c r="Q88">
-        <v>74.453514</v>
-      </c>
-      <c r="R88" t="s">
-        <v>87</v>
-      </c>
-      <c r="S88">
-        <v>29640</v>
+        <v>150000</v>
       </c>
     </row>
   </sheetData>

--- a/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_Pre12.xlsx
+++ b/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_Pre12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="88">
   <si>
     <t>Scenario</t>
   </si>
@@ -265,7 +265,16 @@
     <t>agah</t>
   </si>
   <si>
-    <t>MALERKOTLA</t>
+    <t>Amritsar</t>
+  </si>
+  <si>
+    <t>Fazilka</t>
+  </si>
+  <si>
+    <t>Jalandhar</t>
+  </si>
+  <si>
+    <t>Malerkotla</t>
   </si>
   <si>
     <t>Paddy</t>
@@ -729,7 +738,7 @@
         <v>21</v>
       </c>
       <c r="N2" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="O2" t="s">
         <v>27</v>
@@ -741,7 +750,7 @@
         <v>74.91584450000001</v>
       </c>
       <c r="R2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S2">
         <v>50000</v>
@@ -788,7 +797,7 @@
         <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="O3" t="s">
         <v>27</v>
@@ -800,7 +809,7 @@
         <v>74.588493</v>
       </c>
       <c r="R3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S3">
         <v>50000</v>
@@ -847,7 +856,7 @@
         <v>21</v>
       </c>
       <c r="N4" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O4" t="s">
         <v>27</v>
@@ -859,7 +868,7 @@
         <v>74.18214294000001</v>
       </c>
       <c r="R4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S4">
         <v>90000</v>
@@ -906,7 +915,7 @@
         <v>21</v>
       </c>
       <c r="N5" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O5" t="s">
         <v>27</v>
@@ -918,7 +927,7 @@
         <v>74.18094151</v>
       </c>
       <c r="R5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S5">
         <v>60000</v>
@@ -965,7 +974,7 @@
         <v>21</v>
       </c>
       <c r="N6" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O6" t="s">
         <v>27</v>
@@ -977,7 +986,7 @@
         <v>74.18085842000001</v>
       </c>
       <c r="R6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S6">
         <v>120000</v>
@@ -1024,7 +1033,7 @@
         <v>21</v>
       </c>
       <c r="N7" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O7" t="s">
         <v>27</v>
@@ -1036,7 +1045,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S7">
         <v>33610</v>
@@ -1083,7 +1092,7 @@
         <v>21</v>
       </c>
       <c r="N8" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O8" t="s">
         <v>27</v>
@@ -1095,7 +1104,7 @@
         <v>74.18315728</v>
       </c>
       <c r="R8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S8">
         <v>150000</v>
@@ -1142,7 +1151,7 @@
         <v>21</v>
       </c>
       <c r="N9" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O9" t="s">
         <v>27</v>
@@ -1154,7 +1163,7 @@
         <v>74.161942</v>
       </c>
       <c r="R9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S9">
         <v>143264</v>
@@ -1201,7 +1210,7 @@
         <v>21</v>
       </c>
       <c r="N10" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O10" t="s">
         <v>27</v>
@@ -1213,7 +1222,7 @@
         <v>74.20908439</v>
       </c>
       <c r="R10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S10">
         <v>48247.5</v>
@@ -1260,7 +1269,7 @@
         <v>21</v>
       </c>
       <c r="N11" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O11" t="s">
         <v>27</v>
@@ -1272,7 +1281,7 @@
         <v>74.206666</v>
       </c>
       <c r="R11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S11">
         <v>23588</v>
@@ -1319,7 +1328,7 @@
         <v>21</v>
       </c>
       <c r="N12" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O12" t="s">
         <v>27</v>
@@ -1331,7 +1340,7 @@
         <v>74.18014506</v>
       </c>
       <c r="R12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S12">
         <v>73860.5</v>
@@ -1378,7 +1387,7 @@
         <v>21</v>
       </c>
       <c r="N13" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O13" t="s">
         <v>27</v>
@@ -1390,7 +1399,7 @@
         <v>74.161942</v>
       </c>
       <c r="R13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S13">
         <v>37309</v>
@@ -1437,7 +1446,7 @@
         <v>21</v>
       </c>
       <c r="N14" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O14" t="s">
         <v>27</v>
@@ -1449,7 +1458,7 @@
         <v>74.161942</v>
       </c>
       <c r="R14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S14">
         <v>18025.5</v>
@@ -1496,7 +1505,7 @@
         <v>21</v>
       </c>
       <c r="N15" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O15" t="s">
         <v>27</v>
@@ -1508,7 +1517,7 @@
         <v>74.20908439</v>
       </c>
       <c r="R15" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S15">
         <v>16177.5</v>
@@ -1555,7 +1564,7 @@
         <v>21</v>
       </c>
       <c r="N16" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O16" t="s">
         <v>27</v>
@@ -1567,7 +1576,7 @@
         <v>74.20888524</v>
       </c>
       <c r="R16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S16">
         <v>33588.5</v>
@@ -1614,7 +1623,7 @@
         <v>21</v>
       </c>
       <c r="N17" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O17" t="s">
         <v>27</v>
@@ -1626,7 +1635,7 @@
         <v>74.183232</v>
       </c>
       <c r="R17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S17">
         <v>13129</v>
@@ -1673,7 +1682,7 @@
         <v>21</v>
       </c>
       <c r="N18" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O18" t="s">
         <v>27</v>
@@ -1685,7 +1694,7 @@
         <v>74.161942</v>
       </c>
       <c r="R18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S18">
         <v>28578.5</v>
@@ -1732,7 +1741,7 @@
         <v>21</v>
       </c>
       <c r="N19" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O19" t="s">
         <v>27</v>
@@ -1744,7 +1753,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R19" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S19">
         <v>18038</v>
@@ -1791,7 +1800,7 @@
         <v>21</v>
       </c>
       <c r="N20" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O20" t="s">
         <v>27</v>
@@ -1803,7 +1812,7 @@
         <v>74.161942</v>
       </c>
       <c r="R20" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S20">
         <v>44568.5</v>
@@ -1850,7 +1859,7 @@
         <v>21</v>
       </c>
       <c r="N21" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O21" t="s">
         <v>27</v>
@@ -1862,7 +1871,7 @@
         <v>74.206666</v>
       </c>
       <c r="R21" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S21">
         <v>25216</v>
@@ -1909,7 +1918,7 @@
         <v>21</v>
       </c>
       <c r="N22" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O22" t="s">
         <v>27</v>
@@ -1921,7 +1930,7 @@
         <v>74.18179719</v>
       </c>
       <c r="R22" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S22">
         <v>44802</v>
@@ -1968,7 +1977,7 @@
         <v>21</v>
       </c>
       <c r="N23" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O23" t="s">
         <v>27</v>
@@ -1980,7 +1989,7 @@
         <v>74.161942</v>
       </c>
       <c r="R23" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S23">
         <v>30276.5</v>
@@ -2027,7 +2036,7 @@
         <v>21</v>
       </c>
       <c r="N24" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O24" t="s">
         <v>27</v>
@@ -2039,7 +2048,7 @@
         <v>74.20888524</v>
       </c>
       <c r="R24" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S24">
         <v>19961.5</v>
@@ -2086,7 +2095,7 @@
         <v>21</v>
       </c>
       <c r="N25" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O25" t="s">
         <v>27</v>
@@ -2098,7 +2107,7 @@
         <v>74.20908439</v>
       </c>
       <c r="R25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S25">
         <v>64381</v>
@@ -2145,7 +2154,7 @@
         <v>21</v>
       </c>
       <c r="N26" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O26" t="s">
         <v>27</v>
@@ -2157,7 +2166,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R26" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S26">
         <v>39817.5</v>
@@ -2204,7 +2213,7 @@
         <v>21</v>
       </c>
       <c r="N27" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O27" t="s">
         <v>27</v>
@@ -2216,7 +2225,7 @@
         <v>74.183232</v>
       </c>
       <c r="R27" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S27">
         <v>10375.5</v>
@@ -2263,7 +2272,7 @@
         <v>21</v>
       </c>
       <c r="N28" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O28" t="s">
         <v>27</v>
@@ -2275,7 +2284,7 @@
         <v>74.161942</v>
       </c>
       <c r="R28" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S28">
         <v>100949.5</v>
@@ -2322,7 +2331,7 @@
         <v>21</v>
       </c>
       <c r="N29" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O29" t="s">
         <v>27</v>
@@ -2334,7 +2343,7 @@
         <v>74.17723581</v>
       </c>
       <c r="R29" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S29">
         <v>36622.5</v>
@@ -2381,7 +2390,7 @@
         <v>21</v>
       </c>
       <c r="N30" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O30" t="s">
         <v>27</v>
@@ -2393,7 +2402,7 @@
         <v>74.18014506</v>
       </c>
       <c r="R30" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S30">
         <v>11652.5</v>
@@ -2440,7 +2449,7 @@
         <v>21</v>
       </c>
       <c r="N31" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O31" t="s">
         <v>27</v>
@@ -2452,7 +2461,7 @@
         <v>74.161942</v>
       </c>
       <c r="R31" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S31">
         <v>16592.5</v>
@@ -2499,7 +2508,7 @@
         <v>21</v>
       </c>
       <c r="N32" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O32" t="s">
         <v>27</v>
@@ -2511,7 +2520,7 @@
         <v>74.161942</v>
       </c>
       <c r="R32" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S32">
         <v>21311</v>
@@ -2558,7 +2567,7 @@
         <v>21</v>
       </c>
       <c r="N33" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O33" t="s">
         <v>27</v>
@@ -2570,7 +2579,7 @@
         <v>74.20908439</v>
       </c>
       <c r="R33" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S33">
         <v>34094</v>
@@ -2617,7 +2626,7 @@
         <v>21</v>
       </c>
       <c r="N34" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O34" t="s">
         <v>27</v>
@@ -2629,7 +2638,7 @@
         <v>74.183232</v>
       </c>
       <c r="R34" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S34">
         <v>10795.5</v>
@@ -2676,7 +2685,7 @@
         <v>21</v>
       </c>
       <c r="N35" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O35" t="s">
         <v>27</v>
@@ -2688,7 +2697,7 @@
         <v>74.18230296</v>
       </c>
       <c r="R35" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S35">
         <v>21605.5</v>
@@ -2735,7 +2744,7 @@
         <v>21</v>
       </c>
       <c r="N36" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O36" t="s">
         <v>27</v>
@@ -2747,7 +2756,7 @@
         <v>74.206666</v>
       </c>
       <c r="R36" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S36">
         <v>71196</v>
@@ -2794,7 +2803,7 @@
         <v>21</v>
       </c>
       <c r="N37" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O37" t="s">
         <v>27</v>
@@ -2806,7 +2815,7 @@
         <v>74.161942</v>
       </c>
       <c r="R37" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S37">
         <v>2489</v>
@@ -2853,7 +2862,7 @@
         <v>21</v>
       </c>
       <c r="N38" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O38" t="s">
         <v>27</v>
@@ -2865,7 +2874,7 @@
         <v>74.161942</v>
       </c>
       <c r="R38" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S38">
         <v>34208</v>
@@ -2912,7 +2921,7 @@
         <v>21</v>
       </c>
       <c r="N39" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O39" t="s">
         <v>27</v>
@@ -2924,7 +2933,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R39" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S39">
         <v>54819.5</v>
@@ -2971,7 +2980,7 @@
         <v>21</v>
       </c>
       <c r="N40" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O40" t="s">
         <v>27</v>
@@ -2983,7 +2992,7 @@
         <v>74.161942</v>
       </c>
       <c r="R40" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S40">
         <v>37768</v>
@@ -3030,7 +3039,7 @@
         <v>21</v>
       </c>
       <c r="N41" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O41" t="s">
         <v>27</v>
@@ -3042,7 +3051,7 @@
         <v>74.161942</v>
       </c>
       <c r="R41" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S41">
         <v>29874.5</v>
@@ -3089,7 +3098,7 @@
         <v>21</v>
       </c>
       <c r="N42" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O42" t="s">
         <v>27</v>
@@ -3101,7 +3110,7 @@
         <v>74.161942</v>
       </c>
       <c r="R42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S42">
         <v>56983.5</v>
@@ -3148,7 +3157,7 @@
         <v>21</v>
       </c>
       <c r="N43" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O43" t="s">
         <v>27</v>
@@ -3160,7 +3169,7 @@
         <v>74.161942</v>
       </c>
       <c r="R43" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S43">
         <v>23195.5</v>
@@ -3207,7 +3216,7 @@
         <v>21</v>
       </c>
       <c r="N44" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O44" t="s">
         <v>27</v>
@@ -3219,7 +3228,7 @@
         <v>74.161942</v>
       </c>
       <c r="R44" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S44">
         <v>57368</v>
@@ -3266,7 +3275,7 @@
         <v>21</v>
       </c>
       <c r="N45" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O45" t="s">
         <v>27</v>
@@ -3278,7 +3287,7 @@
         <v>74.18014506</v>
       </c>
       <c r="R45" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S45">
         <v>2487</v>
@@ -3325,7 +3334,7 @@
         <v>21</v>
       </c>
       <c r="N46" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O46" t="s">
         <v>27</v>
@@ -3337,7 +3346,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R46" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S46">
         <v>29195</v>
@@ -3384,7 +3393,7 @@
         <v>21</v>
       </c>
       <c r="N47" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O47" t="s">
         <v>27</v>
@@ -3396,7 +3405,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R47" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S47">
         <v>26795</v>
@@ -3443,7 +3452,7 @@
         <v>21</v>
       </c>
       <c r="N48" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O48" t="s">
         <v>27</v>
@@ -3455,7 +3464,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R48" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S48">
         <v>7950</v>
@@ -3502,7 +3511,7 @@
         <v>21</v>
       </c>
       <c r="N49" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O49" t="s">
         <v>27</v>
@@ -3514,7 +3523,7 @@
         <v>74.18014506</v>
       </c>
       <c r="R49" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S49">
         <v>5500</v>
@@ -3561,7 +3570,7 @@
         <v>21</v>
       </c>
       <c r="N50" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O50" t="s">
         <v>27</v>
@@ -3573,7 +3582,7 @@
         <v>74.161942</v>
       </c>
       <c r="R50" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S50">
         <v>12630.5</v>
@@ -3620,7 +3629,7 @@
         <v>21</v>
       </c>
       <c r="N51" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O51" t="s">
         <v>27</v>
@@ -3632,7 +3641,7 @@
         <v>74.161942</v>
       </c>
       <c r="R51" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S51">
         <v>13803</v>
@@ -3679,7 +3688,7 @@
         <v>21</v>
       </c>
       <c r="N52" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O52" t="s">
         <v>27</v>
@@ -3691,7 +3700,7 @@
         <v>74.161942</v>
       </c>
       <c r="R52" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S52">
         <v>9145</v>
@@ -3738,7 +3747,7 @@
         <v>21</v>
       </c>
       <c r="N53" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O53" t="s">
         <v>27</v>
@@ -3750,7 +3759,7 @@
         <v>74.18179719</v>
       </c>
       <c r="R53" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S53">
         <v>17622.5</v>
@@ -3797,7 +3806,7 @@
         <v>21</v>
       </c>
       <c r="N54" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O54" t="s">
         <v>27</v>
@@ -3809,7 +3818,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R54" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S54">
         <v>2347.5</v>
@@ -3856,7 +3865,7 @@
         <v>21</v>
       </c>
       <c r="N55" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O55" t="s">
         <v>27</v>
@@ -3868,7 +3877,7 @@
         <v>74.17723581</v>
       </c>
       <c r="R55" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S55">
         <v>40337.5</v>
@@ -3915,7 +3924,7 @@
         <v>21</v>
       </c>
       <c r="N56" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O56" t="s">
         <v>27</v>
@@ -3927,7 +3936,7 @@
         <v>74.18179719</v>
       </c>
       <c r="R56" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S56">
         <v>56502.5</v>
@@ -3974,7 +3983,7 @@
         <v>21</v>
       </c>
       <c r="N57" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O57" t="s">
         <v>27</v>
@@ -3986,7 +3995,7 @@
         <v>74.18179719</v>
       </c>
       <c r="R57" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S57">
         <v>43110</v>
@@ -4033,7 +4042,7 @@
         <v>21</v>
       </c>
       <c r="N58" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O58" t="s">
         <v>27</v>
@@ -4045,7 +4054,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R58" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S58">
         <v>128218</v>
@@ -4092,7 +4101,7 @@
         <v>21</v>
       </c>
       <c r="N59" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O59" t="s">
         <v>27</v>
@@ -4104,7 +4113,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R59" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S59">
         <v>62709.5</v>
@@ -4151,7 +4160,7 @@
         <v>21</v>
       </c>
       <c r="N60" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O60" t="s">
         <v>27</v>
@@ -4163,7 +4172,7 @@
         <v>74.18179719</v>
       </c>
       <c r="R60" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S60">
         <v>47189.5</v>
@@ -4210,7 +4219,7 @@
         <v>21</v>
       </c>
       <c r="N61" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="O61" t="s">
         <v>27</v>
@@ -4222,7 +4231,7 @@
         <v>75.685958</v>
       </c>
       <c r="R61" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S61">
         <v>21500</v>
@@ -4269,7 +4278,7 @@
         <v>21</v>
       </c>
       <c r="N62" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O62" t="s">
         <v>27</v>
@@ -4281,7 +4290,7 @@
         <v>74.453514</v>
       </c>
       <c r="R62" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S62">
         <v>88594</v>
@@ -4328,7 +4337,7 @@
         <v>21</v>
       </c>
       <c r="N63" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O63" t="s">
         <v>27</v>
@@ -4340,7 +4349,7 @@
         <v>74.453514</v>
       </c>
       <c r="R63" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S63">
         <v>10000</v>
@@ -4387,7 +4396,7 @@
         <v>21</v>
       </c>
       <c r="N64" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O64" t="s">
         <v>27</v>
@@ -4399,7 +4408,7 @@
         <v>74.453514</v>
       </c>
       <c r="R64" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S64">
         <v>5000</v>
@@ -4446,7 +4455,7 @@
         <v>21</v>
       </c>
       <c r="N65" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O65" t="s">
         <v>27</v>
@@ -4458,7 +4467,7 @@
         <v>74.453514</v>
       </c>
       <c r="R65" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S65">
         <v>5000</v>
@@ -4505,7 +4514,7 @@
         <v>21</v>
       </c>
       <c r="N66" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O66" t="s">
         <v>27</v>
@@ -4517,7 +4526,7 @@
         <v>74.453514</v>
       </c>
       <c r="R66" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S66">
         <v>38086</v>
@@ -4564,7 +4573,7 @@
         <v>21</v>
       </c>
       <c r="N67" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O67" t="s">
         <v>27</v>
@@ -4576,7 +4585,7 @@
         <v>74.453514</v>
       </c>
       <c r="R67" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S67">
         <v>30720</v>
@@ -4623,7 +4632,7 @@
         <v>21</v>
       </c>
       <c r="N68" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O68" t="s">
         <v>27</v>
@@ -4635,7 +4644,7 @@
         <v>74.453514</v>
       </c>
       <c r="R68" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S68">
         <v>5127</v>
@@ -4682,7 +4691,7 @@
         <v>21</v>
       </c>
       <c r="N69" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O69" t="s">
         <v>27</v>
@@ -4694,7 +4703,7 @@
         <v>74.453514</v>
       </c>
       <c r="R69" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S69">
         <v>294680</v>
@@ -4741,7 +4750,7 @@
         <v>21</v>
       </c>
       <c r="N70" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O70" t="s">
         <v>27</v>
@@ -4753,7 +4762,7 @@
         <v>74.453514</v>
       </c>
       <c r="R70" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S70">
         <v>16680</v>
@@ -4800,7 +4809,7 @@
         <v>21</v>
       </c>
       <c r="N71" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O71" t="s">
         <v>27</v>
@@ -4812,7 +4821,7 @@
         <v>74.453514</v>
       </c>
       <c r="R71" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S71">
         <v>10000</v>
@@ -4859,7 +4868,7 @@
         <v>21</v>
       </c>
       <c r="N72" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O72" t="s">
         <v>27</v>
@@ -4871,7 +4880,7 @@
         <v>74.453514</v>
       </c>
       <c r="R72" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S72">
         <v>10000</v>
@@ -4918,7 +4927,7 @@
         <v>21</v>
       </c>
       <c r="N73" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O73" t="s">
         <v>27</v>
@@ -4930,7 +4939,7 @@
         <v>74.453514</v>
       </c>
       <c r="R73" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S73">
         <v>10000</v>
@@ -4977,7 +4986,7 @@
         <v>21</v>
       </c>
       <c r="N74" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O74" t="s">
         <v>27</v>
@@ -4989,7 +4998,7 @@
         <v>74.453514</v>
       </c>
       <c r="R74" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S74">
         <v>30720</v>
@@ -5036,7 +5045,7 @@
         <v>21</v>
       </c>
       <c r="N75" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O75" t="s">
         <v>27</v>
@@ -5048,7 +5057,7 @@
         <v>74.453514</v>
       </c>
       <c r="R75" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S75">
         <v>29640</v>
@@ -5095,7 +5104,7 @@
         <v>21</v>
       </c>
       <c r="N76" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O76" t="s">
         <v>27</v>
@@ -5107,7 +5116,7 @@
         <v>74.453514</v>
       </c>
       <c r="R76" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S76">
         <v>28460</v>
@@ -5154,7 +5163,7 @@
         <v>21</v>
       </c>
       <c r="N77" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O77" t="s">
         <v>27</v>
@@ -5166,7 +5175,7 @@
         <v>74.453514</v>
       </c>
       <c r="R77" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S77">
         <v>15353</v>
@@ -5213,7 +5222,7 @@
         <v>21</v>
       </c>
       <c r="N78" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O78" t="s">
         <v>27</v>
@@ -5225,7 +5234,7 @@
         <v>74.453514</v>
       </c>
       <c r="R78" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S78">
         <v>20480</v>
@@ -5272,7 +5281,7 @@
         <v>21</v>
       </c>
       <c r="N79" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O79" t="s">
         <v>27</v>
@@ -5284,7 +5293,7 @@
         <v>74.453514</v>
       </c>
       <c r="R79" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S79">
         <v>20480</v>
@@ -5331,7 +5340,7 @@
         <v>21</v>
       </c>
       <c r="N80" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O80" t="s">
         <v>27</v>
@@ -5343,7 +5352,7 @@
         <v>74.453514</v>
       </c>
       <c r="R80" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S80">
         <v>15360</v>
@@ -5390,7 +5399,7 @@
         <v>21</v>
       </c>
       <c r="N81" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O81" t="s">
         <v>27</v>
@@ -5402,7 +5411,7 @@
         <v>74.18179719</v>
       </c>
       <c r="R81" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S81">
         <v>1314.5</v>
@@ -5449,7 +5458,7 @@
         <v>21</v>
       </c>
       <c r="N82" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O82" t="s">
         <v>27</v>
@@ -5461,7 +5470,7 @@
         <v>74.18230296</v>
       </c>
       <c r="R82" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S82">
         <v>52394.5</v>
@@ -5508,7 +5517,7 @@
         <v>21</v>
       </c>
       <c r="N83" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="O83" t="s">
         <v>27</v>
@@ -5520,7 +5529,7 @@
         <v>74.46541999999999</v>
       </c>
       <c r="R83" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S83">
         <v>150000</v>
@@ -5567,7 +5576,7 @@
         <v>21</v>
       </c>
       <c r="N84" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="O84" t="s">
         <v>27</v>
@@ -5579,7 +5588,7 @@
         <v>74.46541999999999</v>
       </c>
       <c r="R84" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S84">
         <v>150000</v>

--- a/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_Pre12.xlsx
+++ b/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_Pre12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1579" uniqueCount="113">
   <si>
     <t>Scenario</t>
   </si>
@@ -85,196 +85,271 @@
     <t>AMRITSAR</t>
   </si>
   <si>
+    <t>MALERKOTLA</t>
+  </si>
+  <si>
     <t>FAZILKA</t>
   </si>
   <si>
     <t>JALANDHAR</t>
   </si>
   <si>
-    <t>SRI MUKTSAR SAHIB</t>
-  </si>
-  <si>
-    <t>TARN TARAN</t>
-  </si>
-  <si>
-    <t>Stor</t>
+    <t>AJNALA</t>
+  </si>
+  <si>
+    <t>AHMEDGARH</t>
+  </si>
+  <si>
+    <t>MAJITHA</t>
+  </si>
+  <si>
+    <t>Abohar</t>
+  </si>
+  <si>
+    <t>ADAMPUR</t>
+  </si>
+  <si>
+    <t>RAYYA</t>
+  </si>
+  <si>
+    <t>CHOGAWAN</t>
+  </si>
+  <si>
+    <t>JANDIALA</t>
+  </si>
+  <si>
+    <t>AJNALA GRAIN MARKET</t>
   </si>
   <si>
     <t>CHAK SAKANDAR GRAIN MARKET</t>
   </si>
   <si>
+    <t>CHAKDOGRA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>CHAMIARI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHATRAI KALAN GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BHIKHAMPUR BEGOWAL</t>
+  </si>
+  <si>
+    <t>DHALER KHURD</t>
+  </si>
+  <si>
+    <t>KANGANWAL</t>
+  </si>
+  <si>
+    <t>KUP</t>
+  </si>
+  <si>
+    <t>MAHOLI KALAN</t>
+  </si>
+  <si>
+    <t>MANAK HERI</t>
+  </si>
+  <si>
+    <t>MOMNA BAD</t>
+  </si>
+  <si>
+    <t>UMARPURA (NATHUMAJRA)</t>
+  </si>
+  <si>
+    <t>DHADDE GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KATHUNANGAL GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MAJITHA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>SOHIAN KALAN GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>ABOHAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BAHADUR KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BAHAAW WALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BUKENWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BALLUANA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BHAAGU GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>CHANNAN KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>CHURHI WALA DHANNA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DEEWAN KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DHABA KOKARIYA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DHARANGWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DHINGANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DODHEWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DUTARANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>GADA DOB GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>GHALLU GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>GOBINDGARH GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JANDWALA MEERA SANGLA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JHUMIYANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JHURAD KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KALAR KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHUMBAN GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHUPAYA SARWAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KULAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KUNDAL GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MALOOKPURA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MAUJGARH GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>NARAINPURA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>NIHAL KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>PANJKOSI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>PATRE WALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>RUKANPURA KHUI KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>SAIDANWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>SITO GUNO GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>VAJIDPUR BHOMA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>WAREYAM KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>Bhadoo Waxing Plant</t>
+  </si>
+  <si>
+    <t>P.S. Waxing Plant</t>
+  </si>
+  <si>
+    <t>Sandhu waxing plant</t>
+  </si>
+  <si>
+    <t>Sri Ram cotton &amp; oil mill</t>
+  </si>
+  <si>
+    <t>Near Mandir</t>
+  </si>
+  <si>
+    <t>Near Gurdwara Sahib</t>
+  </si>
+  <si>
+    <t>Dera Jhangi wala</t>
+  </si>
+  <si>
+    <t>Near Jandwala Meera Sangla purchase center</t>
+  </si>
+  <si>
+    <t>GHARHIANA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MAMMU KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MURADWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KUHADIANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAMPUR  </t>
+  </si>
+  <si>
+    <t>BUTALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KAALEKE GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHALCHIYA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>RAYYA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>SATHEALA GRAIN MARKET</t>
+  </si>
+  <si>
     <t>BHILOWAL GRAIN MARKET</t>
   </si>
   <si>
-    <t>ABOHAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BAHADUR KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BAHAAW WALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BUKENWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BALLUANA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BHAAGU GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>CHANNAN KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>CHURHI WALA DHANNA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DEEWAN KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DHABA KOKARIYA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DHARANGWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DHINGANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DODHEWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DUTARANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>GHALLU GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>GOBINDGARH GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JANDWALA MEERA SANGLA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JHUMIYANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JHURAD KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KHUPAYA SARWAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KULAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KUNDAL GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MALOOKPURA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MAUJGARH GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>NIHAL KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>PANJKOSI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>PATRE WALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>RUKANPURA KHUI KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>SAIDANWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>WAREYAM KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>Bhadoo Waxing Plant</t>
-  </si>
-  <si>
-    <t>P.S. Waxing Plant</t>
-  </si>
-  <si>
-    <t>Sandhu waxing plant</t>
-  </si>
-  <si>
-    <t>Sri Ram cotton &amp; oil mill</t>
-  </si>
-  <si>
-    <t>Near Mandir</t>
-  </si>
-  <si>
-    <t>Near Gurdwara Sahib</t>
-  </si>
-  <si>
-    <t>Dera Jhangi wala</t>
-  </si>
-  <si>
-    <t>Near Jandwala Meera Sangla purchase center</t>
-  </si>
-  <si>
-    <t>GHARHIANA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MAMMU KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MURADWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KUHADIANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KHIUWALA DHAB GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>RAMKOT GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KANDHWALA HAZARKHAN GRAIN MARKET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAMPUR  </t>
-  </si>
-  <si>
-    <t>BHAGSAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MAHABADAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>sri muktsar sahib grain market</t>
-  </si>
-  <si>
-    <t>KARAM PATTI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KHALRA GRAIN MARKET</t>
+    <t>CHOGAWAN GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JANDIALA GURU GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>TANGRA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JABBOWAL GRAIN MARKET</t>
   </si>
   <si>
     <t>Depot</t>
   </si>
   <si>
     <t>agah</t>
-  </si>
-  <si>
-    <t>Amritsar</t>
-  </si>
-  <si>
-    <t>Fazilka</t>
-  </si>
-  <si>
-    <t>Jalandhar</t>
-  </si>
-  <si>
-    <t>Malerkotla</t>
   </si>
   <si>
     <t>Paddy</t>
@@ -635,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S84"/>
+  <dimension ref="A1:S131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -711,49 +786,49 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H2">
-        <v>31.84430551</v>
+        <v>31.83562081</v>
       </c>
       <c r="I2">
-        <v>74.91208039999999</v>
+        <v>74.75035127</v>
       </c>
       <c r="J2" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M2" t="s">
         <v>21</v>
       </c>
       <c r="N2" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="O2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P2">
-        <v>31.8529346</v>
+        <v>31.81488868</v>
       </c>
       <c r="Q2">
-        <v>74.91584450000001</v>
+        <v>74.76977281000001</v>
       </c>
       <c r="R2" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S2">
-        <v>50000</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -770,49 +845,49 @@
         <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H3">
-        <v>31.7398221</v>
+        <v>31.83562081</v>
       </c>
       <c r="I3">
-        <v>74.6072853</v>
+        <v>74.75035127</v>
       </c>
       <c r="J3" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L3" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M3" t="s">
         <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="O3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P3">
-        <v>31.800077</v>
+        <v>31.45335</v>
       </c>
       <c r="Q3">
-        <v>74.588493</v>
+        <v>74.46541999999999</v>
       </c>
       <c r="R3" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S3">
-        <v>50000</v>
+        <v>132250</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -826,52 +901,52 @@
         <v>21</v>
       </c>
       <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4">
+        <v>31.83562081</v>
+      </c>
+      <c r="I4">
+        <v>74.75035127</v>
+      </c>
+      <c r="J4" t="s">
+        <v>110</v>
+      </c>
+      <c r="K4">
         <v>23</v>
       </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4">
-        <v>501</v>
-      </c>
-      <c r="G4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4">
-        <v>30.156605</v>
-      </c>
-      <c r="I4">
-        <v>74.19572100000001</v>
-      </c>
-      <c r="J4" t="s">
-        <v>81</v>
-      </c>
-      <c r="K4">
-        <v>396</v>
-      </c>
       <c r="L4" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M4" t="s">
         <v>21</v>
       </c>
       <c r="N4" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="O4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P4">
-        <v>30.15881226</v>
+        <v>31.781936</v>
       </c>
       <c r="Q4">
-        <v>74.18214294000001</v>
+        <v>74.76758049999999</v>
       </c>
       <c r="R4" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S4">
-        <v>90000</v>
+        <v>139400</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -885,52 +960,52 @@
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>501</v>
+        <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H5">
-        <v>30.156605</v>
+        <v>31.84430551</v>
       </c>
       <c r="I5">
-        <v>74.19572100000001</v>
+        <v>74.91208039999999</v>
       </c>
       <c r="J5" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K5">
-        <v>398</v>
+        <v>3</v>
       </c>
       <c r="L5" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M5" t="s">
         <v>21</v>
       </c>
       <c r="N5" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="O5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P5">
-        <v>30.15894356</v>
+        <v>31.8529346</v>
       </c>
       <c r="Q5">
-        <v>74.18094151</v>
+        <v>74.91584450000001</v>
       </c>
       <c r="R5" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S5">
-        <v>60000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -944,52 +1019,52 @@
         <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>501</v>
+        <v>4</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H6">
-        <v>30.156605</v>
+        <v>31.8895439</v>
       </c>
       <c r="I6">
-        <v>74.19572100000001</v>
+        <v>74.7119419</v>
       </c>
       <c r="J6" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K6">
-        <v>399</v>
+        <v>2</v>
       </c>
       <c r="L6" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s">
         <v>21</v>
       </c>
       <c r="N6" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="O6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P6">
-        <v>30.15848535</v>
+        <v>31.45335</v>
       </c>
       <c r="Q6">
-        <v>74.18085842000001</v>
+        <v>74.46541999999999</v>
       </c>
       <c r="R6" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S6">
-        <v>120000</v>
+        <v>17750</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1003,52 +1078,52 @@
         <v>21</v>
       </c>
       <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7">
+        <v>31.86063083</v>
+      </c>
+      <c r="I7">
+        <v>74.81790506999999</v>
+      </c>
+      <c r="J7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K7">
         <v>23</v>
       </c>
-      <c r="E7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7">
-        <v>501</v>
-      </c>
-      <c r="G7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7">
-        <v>30.156605</v>
-      </c>
-      <c r="I7">
-        <v>74.19572100000001</v>
-      </c>
-      <c r="J7" t="s">
-        <v>81</v>
-      </c>
-      <c r="K7">
-        <v>400</v>
-      </c>
       <c r="L7" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M7" t="s">
         <v>21</v>
       </c>
       <c r="N7" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="O7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P7">
-        <v>30.15809938</v>
+        <v>31.781936</v>
       </c>
       <c r="Q7">
-        <v>74.16401603</v>
+        <v>74.76758049999999</v>
       </c>
       <c r="R7" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S7">
-        <v>33610</v>
+        <v>12425</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1062,52 +1137,52 @@
         <v>21</v>
       </c>
       <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8">
+        <v>31.819463</v>
+      </c>
+      <c r="I8">
+        <v>74.8593226</v>
+      </c>
+      <c r="J8" t="s">
+        <v>110</v>
+      </c>
+      <c r="K8">
         <v>23</v>
       </c>
-      <c r="E8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8">
-        <v>501</v>
-      </c>
-      <c r="G8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8">
-        <v>30.156605</v>
-      </c>
-      <c r="I8">
-        <v>74.19572100000001</v>
-      </c>
-      <c r="J8" t="s">
-        <v>81</v>
-      </c>
-      <c r="K8">
-        <v>405</v>
-      </c>
       <c r="L8" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M8" t="s">
         <v>21</v>
       </c>
       <c r="N8" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="O8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P8">
-        <v>30.15857797</v>
+        <v>31.781936</v>
       </c>
       <c r="Q8">
-        <v>74.18315728</v>
+        <v>74.76758049999999</v>
       </c>
       <c r="R8" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S8">
-        <v>150000</v>
+        <v>98175</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1127,46 +1202,46 @@
         <v>27</v>
       </c>
       <c r="F9">
-        <v>501</v>
+        <v>1322</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H9">
-        <v>30.156605</v>
+        <v>30.67924</v>
       </c>
       <c r="I9">
-        <v>74.19572100000001</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J9" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K9">
-        <v>407</v>
+        <v>864</v>
       </c>
       <c r="L9" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M9" t="s">
         <v>21</v>
       </c>
       <c r="N9" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O9" t="s">
         <v>27</v>
       </c>
       <c r="P9">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q9">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R9" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S9">
-        <v>143264</v>
+        <v>197630</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1186,46 +1261,46 @@
         <v>27</v>
       </c>
       <c r="F10">
-        <v>502</v>
+        <v>1322</v>
       </c>
       <c r="G10" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H10">
-        <v>30.099748</v>
+        <v>30.67924</v>
       </c>
       <c r="I10">
-        <v>74.34759699999999</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J10" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K10">
-        <v>394</v>
+        <v>865</v>
       </c>
       <c r="L10" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M10" t="s">
         <v>21</v>
       </c>
       <c r="N10" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O10" t="s">
         <v>27</v>
       </c>
       <c r="P10">
-        <v>30.08793156</v>
+        <v>30.458388</v>
       </c>
       <c r="Q10">
-        <v>74.20908439</v>
+        <v>74.453514</v>
       </c>
       <c r="R10" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S10">
-        <v>48247.5</v>
+        <v>16680</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1245,46 +1320,46 @@
         <v>27</v>
       </c>
       <c r="F11">
-        <v>502</v>
+        <v>1322</v>
       </c>
       <c r="G11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H11">
-        <v>30.099748</v>
+        <v>30.67924</v>
       </c>
       <c r="I11">
-        <v>74.34759699999999</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J11" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K11">
-        <v>397</v>
+        <v>866</v>
       </c>
       <c r="L11" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s">
         <v>21</v>
       </c>
       <c r="N11" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O11" t="s">
         <v>27</v>
       </c>
       <c r="P11">
-        <v>30.0974593</v>
+        <v>30.458388</v>
       </c>
       <c r="Q11">
-        <v>74.206666</v>
+        <v>74.453514</v>
       </c>
       <c r="R11" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S11">
-        <v>23588</v>
+        <v>42630</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1304,46 +1379,46 @@
         <v>27</v>
       </c>
       <c r="F12">
-        <v>503</v>
+        <v>1322</v>
       </c>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H12">
-        <v>30.028699</v>
+        <v>30.67924</v>
       </c>
       <c r="I12">
-        <v>74.197309</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J12" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K12">
-        <v>404</v>
+        <v>868</v>
       </c>
       <c r="L12" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M12" t="s">
         <v>21</v>
       </c>
       <c r="N12" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O12" t="s">
         <v>27</v>
       </c>
       <c r="P12">
-        <v>30.10552983</v>
+        <v>30.458388</v>
       </c>
       <c r="Q12">
-        <v>74.18014506</v>
+        <v>74.453514</v>
       </c>
       <c r="R12" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S12">
-        <v>73860.5</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1363,46 +1438,46 @@
         <v>27</v>
       </c>
       <c r="F13">
-        <v>505</v>
+        <v>1322</v>
       </c>
       <c r="G13" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H13">
-        <v>30.162859</v>
+        <v>30.67924</v>
       </c>
       <c r="I13">
-        <v>73.991192</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J13" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K13">
-        <v>407</v>
+        <v>869</v>
       </c>
       <c r="L13" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M13" t="s">
         <v>21</v>
       </c>
       <c r="N13" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O13" t="s">
         <v>27</v>
       </c>
       <c r="P13">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q13">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R13" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S13">
-        <v>37309</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1422,46 +1497,46 @@
         <v>27</v>
       </c>
       <c r="F14">
-        <v>506</v>
+        <v>1322</v>
       </c>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H14">
-        <v>30.16948</v>
+        <v>30.67924</v>
       </c>
       <c r="I14">
-        <v>74.28432100000001</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J14" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K14">
-        <v>407</v>
+        <v>870</v>
       </c>
       <c r="L14" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M14" t="s">
         <v>21</v>
       </c>
       <c r="N14" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O14" t="s">
         <v>27</v>
       </c>
       <c r="P14">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q14">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R14" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S14">
-        <v>18025.5</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -1481,46 +1556,46 @@
         <v>27</v>
       </c>
       <c r="F15">
-        <v>507</v>
+        <v>1322</v>
       </c>
       <c r="G15" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H15">
-        <v>30.034436</v>
+        <v>30.67924</v>
       </c>
       <c r="I15">
-        <v>74.233859</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J15" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K15">
-        <v>394</v>
+        <v>871</v>
       </c>
       <c r="L15" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M15" t="s">
         <v>21</v>
       </c>
       <c r="N15" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O15" t="s">
         <v>27</v>
       </c>
       <c r="P15">
-        <v>30.08793156</v>
+        <v>30.458388</v>
       </c>
       <c r="Q15">
-        <v>74.20908439</v>
+        <v>74.453514</v>
       </c>
       <c r="R15" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S15">
-        <v>16177.5</v>
+        <v>30720</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -1540,46 +1615,46 @@
         <v>27</v>
       </c>
       <c r="F16">
-        <v>507</v>
+        <v>1322</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H16">
-        <v>30.034436</v>
+        <v>30.67924</v>
       </c>
       <c r="I16">
-        <v>74.233859</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J16" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K16">
-        <v>395</v>
+        <v>872</v>
       </c>
       <c r="L16" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M16" t="s">
         <v>21</v>
       </c>
       <c r="N16" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O16" t="s">
         <v>27</v>
       </c>
       <c r="P16">
-        <v>30.08675444</v>
+        <v>30.458388</v>
       </c>
       <c r="Q16">
-        <v>74.20888524</v>
+        <v>74.453514</v>
       </c>
       <c r="R16" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S16">
-        <v>33588.5</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -1599,46 +1674,46 @@
         <v>27</v>
       </c>
       <c r="F17">
-        <v>508</v>
+        <v>1322</v>
       </c>
       <c r="G17" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="H17">
-        <v>30.182524</v>
+        <v>30.67924</v>
       </c>
       <c r="I17">
-        <v>74.326095</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J17" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K17">
-        <v>403</v>
+        <v>873</v>
       </c>
       <c r="L17" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M17" t="s">
         <v>21</v>
       </c>
       <c r="N17" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O17" t="s">
         <v>27</v>
       </c>
       <c r="P17">
-        <v>30.1689126</v>
+        <v>30.458388</v>
       </c>
       <c r="Q17">
-        <v>74.183232</v>
+        <v>74.453514</v>
       </c>
       <c r="R17" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S17">
-        <v>13129</v>
+        <v>29640</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -1658,46 +1733,46 @@
         <v>27</v>
       </c>
       <c r="F18">
-        <v>508</v>
+        <v>1322</v>
       </c>
       <c r="G18" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="H18">
-        <v>30.182524</v>
+        <v>30.67924</v>
       </c>
       <c r="I18">
-        <v>74.326095</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J18" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K18">
-        <v>407</v>
+        <v>877</v>
       </c>
       <c r="L18" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M18" t="s">
         <v>21</v>
       </c>
       <c r="N18" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O18" t="s">
         <v>27</v>
       </c>
       <c r="P18">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q18">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R18" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S18">
-        <v>28578.5</v>
+        <v>9950</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -1717,46 +1792,46 @@
         <v>27</v>
       </c>
       <c r="F19">
-        <v>509</v>
+        <v>1323</v>
       </c>
       <c r="G19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H19">
-        <v>30.199756</v>
+        <v>30.61296</v>
       </c>
       <c r="I19">
-        <v>74.108656</v>
+        <v>75.84106</v>
       </c>
       <c r="J19" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K19">
-        <v>400</v>
+        <v>867</v>
       </c>
       <c r="L19" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M19" t="s">
         <v>21</v>
       </c>
       <c r="N19" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O19" t="s">
         <v>27</v>
       </c>
       <c r="P19">
-        <v>30.15809938</v>
+        <v>30.458388</v>
       </c>
       <c r="Q19">
-        <v>74.16401603</v>
+        <v>74.453514</v>
       </c>
       <c r="R19" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S19">
-        <v>18038</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -1776,46 +1851,46 @@
         <v>27</v>
       </c>
       <c r="F20">
-        <v>510</v>
+        <v>1323</v>
       </c>
       <c r="G20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H20">
-        <v>30.113508</v>
+        <v>30.61296</v>
       </c>
       <c r="I20">
-        <v>73.989543</v>
+        <v>75.84106</v>
       </c>
       <c r="J20" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K20">
-        <v>407</v>
+        <v>875</v>
       </c>
       <c r="L20" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M20" t="s">
         <v>21</v>
       </c>
       <c r="N20" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O20" t="s">
         <v>27</v>
       </c>
       <c r="P20">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q20">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R20" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S20">
-        <v>44568.5</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -1835,46 +1910,46 @@
         <v>27</v>
       </c>
       <c r="F21">
-        <v>511</v>
+        <v>1323</v>
       </c>
       <c r="G21" t="s">
         <v>39</v>
       </c>
       <c r="H21">
-        <v>30.122605</v>
+        <v>30.61296</v>
       </c>
       <c r="I21">
-        <v>74.328892</v>
+        <v>75.84106</v>
       </c>
       <c r="J21" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K21">
-        <v>397</v>
+        <v>876</v>
       </c>
       <c r="L21" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M21" t="s">
         <v>21</v>
       </c>
       <c r="N21" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O21" t="s">
         <v>27</v>
       </c>
       <c r="P21">
-        <v>30.0974593</v>
+        <v>30.458388</v>
       </c>
       <c r="Q21">
-        <v>74.206666</v>
+        <v>74.453514</v>
       </c>
       <c r="R21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S21">
-        <v>25216</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -1894,46 +1969,46 @@
         <v>27</v>
       </c>
       <c r="F22">
-        <v>512</v>
+        <v>1323</v>
       </c>
       <c r="G22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H22">
-        <v>30.237206</v>
+        <v>30.61296</v>
       </c>
       <c r="I22">
-        <v>74.23982700000001</v>
+        <v>75.84106</v>
       </c>
       <c r="J22" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K22">
-        <v>401</v>
+        <v>878</v>
       </c>
       <c r="L22" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M22" t="s">
         <v>21</v>
       </c>
       <c r="N22" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O22" t="s">
         <v>27</v>
       </c>
       <c r="P22">
-        <v>30.17081207</v>
+        <v>30.458388</v>
       </c>
       <c r="Q22">
-        <v>74.18179719</v>
+        <v>74.453514</v>
       </c>
       <c r="R22" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S22">
-        <v>44802</v>
+        <v>20480</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -1953,46 +2028,46 @@
         <v>27</v>
       </c>
       <c r="F23">
-        <v>513</v>
+        <v>1323</v>
       </c>
       <c r="G23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H23">
-        <v>30.023582</v>
+        <v>30.61296</v>
       </c>
       <c r="I23">
-        <v>74.04262799999999</v>
+        <v>75.84106</v>
       </c>
       <c r="J23" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K23">
-        <v>407</v>
+        <v>879</v>
       </c>
       <c r="L23" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M23" t="s">
         <v>21</v>
       </c>
       <c r="N23" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O23" t="s">
         <v>27</v>
       </c>
       <c r="P23">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q23">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R23" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S23">
-        <v>30276.5</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -2012,46 +2087,46 @@
         <v>27</v>
       </c>
       <c r="F24">
-        <v>514</v>
+        <v>1324</v>
       </c>
       <c r="G24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H24">
-        <v>29.960526</v>
+        <v>30.59296</v>
       </c>
       <c r="I24">
-        <v>74.219824</v>
+        <v>75.78903</v>
       </c>
       <c r="J24" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K24">
-        <v>395</v>
+        <v>864</v>
       </c>
       <c r="L24" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M24" t="s">
         <v>21</v>
       </c>
       <c r="N24" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O24" t="s">
         <v>27</v>
       </c>
       <c r="P24">
-        <v>30.08675444</v>
+        <v>30.458388</v>
       </c>
       <c r="Q24">
-        <v>74.20888524</v>
+        <v>74.453514</v>
       </c>
       <c r="R24" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S24">
-        <v>19961.5</v>
+        <v>41830</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -2071,46 +2146,46 @@
         <v>27</v>
       </c>
       <c r="F25">
-        <v>515</v>
+        <v>1325</v>
       </c>
       <c r="G25" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H25">
-        <v>30.082625</v>
+        <v>30.61907</v>
       </c>
       <c r="I25">
-        <v>74.288794</v>
+        <v>75.8098</v>
       </c>
       <c r="J25" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K25">
-        <v>394</v>
+        <v>864</v>
       </c>
       <c r="L25" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M25" t="s">
         <v>21</v>
       </c>
       <c r="N25" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O25" t="s">
         <v>27</v>
       </c>
       <c r="P25">
-        <v>30.08793156</v>
+        <v>30.458388</v>
       </c>
       <c r="Q25">
-        <v>74.20908439</v>
+        <v>74.453514</v>
       </c>
       <c r="R25" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S25">
-        <v>64381</v>
+        <v>55220</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -2130,46 +2205,46 @@
         <v>27</v>
       </c>
       <c r="F26">
-        <v>517</v>
+        <v>1326</v>
       </c>
       <c r="G26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H26">
-        <v>30.254598</v>
+        <v>30.60582</v>
       </c>
       <c r="I26">
-        <v>74.124285</v>
+        <v>75.87558</v>
       </c>
       <c r="J26" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K26">
-        <v>400</v>
+        <v>866</v>
       </c>
       <c r="L26" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M26" t="s">
         <v>21</v>
       </c>
       <c r="N26" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O26" t="s">
         <v>27</v>
       </c>
       <c r="P26">
-        <v>30.15809938</v>
+        <v>30.458388</v>
       </c>
       <c r="Q26">
-        <v>74.16401603</v>
+        <v>74.453514</v>
       </c>
       <c r="R26" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S26">
-        <v>39817.5</v>
+        <v>13140</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -2189,46 +2264,46 @@
         <v>27</v>
       </c>
       <c r="F27">
-        <v>518</v>
+        <v>1326</v>
       </c>
       <c r="G27" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H27">
-        <v>30.173582</v>
+        <v>30.60582</v>
       </c>
       <c r="I27">
-        <v>74.250483</v>
+        <v>75.87558</v>
       </c>
       <c r="J27" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K27">
-        <v>403</v>
+        <v>874</v>
       </c>
       <c r="L27" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M27" t="s">
         <v>21</v>
       </c>
       <c r="N27" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O27" t="s">
         <v>27</v>
       </c>
       <c r="P27">
-        <v>30.1689126</v>
+        <v>30.458388</v>
       </c>
       <c r="Q27">
-        <v>74.183232</v>
+        <v>74.453514</v>
       </c>
       <c r="R27" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S27">
-        <v>10375.5</v>
+        <v>28460</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -2248,46 +2323,46 @@
         <v>27</v>
       </c>
       <c r="F28">
-        <v>520</v>
+        <v>1326</v>
       </c>
       <c r="G28" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H28">
-        <v>30.21019</v>
+        <v>30.60582</v>
       </c>
       <c r="I28">
-        <v>74.024728</v>
+        <v>75.87558</v>
       </c>
       <c r="J28" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K28">
-        <v>407</v>
+        <v>879</v>
       </c>
       <c r="L28" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M28" t="s">
         <v>21</v>
       </c>
       <c r="N28" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O28" t="s">
         <v>27</v>
       </c>
       <c r="P28">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q28">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R28" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S28">
-        <v>100949.5</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -2307,46 +2382,46 @@
         <v>27</v>
       </c>
       <c r="F29">
-        <v>521</v>
+        <v>1327</v>
       </c>
       <c r="G29" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H29">
-        <v>30.257887</v>
+        <v>30.62411</v>
       </c>
       <c r="I29">
-        <v>74.185624</v>
+        <v>75.75073</v>
       </c>
       <c r="J29" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K29">
-        <v>402</v>
+        <v>866</v>
       </c>
       <c r="L29" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M29" t="s">
         <v>21</v>
       </c>
       <c r="N29" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O29" t="s">
         <v>27</v>
       </c>
       <c r="P29">
-        <v>30.17767461</v>
+        <v>30.458388</v>
       </c>
       <c r="Q29">
-        <v>74.17723581</v>
+        <v>74.453514</v>
       </c>
       <c r="R29" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S29">
-        <v>36622.5</v>
+        <v>59240</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -2366,46 +2441,46 @@
         <v>27</v>
       </c>
       <c r="F30">
-        <v>522</v>
+        <v>1328</v>
       </c>
       <c r="G30" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H30">
-        <v>30.007285</v>
+        <v>30.58776</v>
       </c>
       <c r="I30">
-        <v>74.126166</v>
+        <v>75.81787</v>
       </c>
       <c r="J30" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K30">
-        <v>404</v>
+        <v>866</v>
       </c>
       <c r="L30" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M30" t="s">
         <v>21</v>
       </c>
       <c r="N30" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O30" t="s">
         <v>27</v>
       </c>
       <c r="P30">
-        <v>30.10552983</v>
+        <v>30.458388</v>
       </c>
       <c r="Q30">
-        <v>74.18014506</v>
+        <v>74.453514</v>
       </c>
       <c r="R30" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S30">
-        <v>11652.5</v>
+        <v>11670</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -2425,46 +2500,46 @@
         <v>27</v>
       </c>
       <c r="F31">
-        <v>522</v>
+        <v>1328</v>
       </c>
       <c r="G31" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H31">
-        <v>30.007285</v>
+        <v>30.58776</v>
       </c>
       <c r="I31">
-        <v>74.126166</v>
+        <v>75.81787</v>
       </c>
       <c r="J31" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K31">
-        <v>407</v>
+        <v>880</v>
       </c>
       <c r="L31" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M31" t="s">
         <v>21</v>
       </c>
       <c r="N31" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O31" t="s">
         <v>27</v>
       </c>
       <c r="P31">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q31">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R31" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S31">
-        <v>16592.5</v>
+        <v>15360</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -2484,46 +2559,46 @@
         <v>27</v>
       </c>
       <c r="F32">
-        <v>525</v>
+        <v>1329</v>
       </c>
       <c r="G32" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H32">
-        <v>30.127701</v>
+        <v>30.669134</v>
       </c>
       <c r="I32">
-        <v>74.06368999999999</v>
+        <v>75.877723</v>
       </c>
       <c r="J32" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K32">
-        <v>407</v>
+        <v>877</v>
       </c>
       <c r="L32" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M32" t="s">
         <v>21</v>
       </c>
       <c r="N32" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O32" t="s">
         <v>27</v>
       </c>
       <c r="P32">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q32">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R32" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S32">
-        <v>21311</v>
+        <v>10530</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -2543,46 +2618,46 @@
         <v>27</v>
       </c>
       <c r="F33">
-        <v>526</v>
+        <v>1330</v>
       </c>
       <c r="G33" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H33">
-        <v>29.98347</v>
+        <v>30.651445</v>
       </c>
       <c r="I33">
-        <v>74.283652</v>
+        <v>75.890028</v>
       </c>
       <c r="J33" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K33">
-        <v>394</v>
+        <v>872</v>
       </c>
       <c r="L33" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M33" t="s">
         <v>21</v>
       </c>
       <c r="N33" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="O33" t="s">
         <v>27</v>
       </c>
       <c r="P33">
-        <v>30.08793156</v>
+        <v>30.458388</v>
       </c>
       <c r="Q33">
-        <v>74.20908439</v>
+        <v>74.453514</v>
       </c>
       <c r="R33" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S33">
-        <v>34094</v>
+        <v>29640</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -2596,52 +2671,52 @@
         <v>21</v>
       </c>
       <c r="D34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F34">
-        <v>527</v>
+        <v>43</v>
       </c>
       <c r="G34" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H34">
-        <v>30.216512</v>
+        <v>31.6939305</v>
       </c>
       <c r="I34">
-        <v>74.269492</v>
+        <v>75.09889200000001</v>
       </c>
       <c r="J34" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K34">
-        <v>403</v>
+        <v>38</v>
       </c>
       <c r="L34" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M34" t="s">
         <v>21</v>
       </c>
       <c r="N34" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="O34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P34">
-        <v>30.1689126</v>
+        <v>31.43316</v>
       </c>
       <c r="Q34">
-        <v>74.183232</v>
+        <v>75.00457</v>
       </c>
       <c r="R34" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S34">
-        <v>10795.5</v>
+        <v>35025</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -2655,52 +2730,52 @@
         <v>21</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F35">
-        <v>527</v>
+        <v>44</v>
       </c>
       <c r="G35" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H35">
-        <v>30.216512</v>
+        <v>31.7224291</v>
       </c>
       <c r="I35">
-        <v>74.269492</v>
+        <v>75.02844</v>
       </c>
       <c r="J35" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K35">
-        <v>406</v>
+        <v>38</v>
       </c>
       <c r="L35" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M35" t="s">
         <v>21</v>
       </c>
       <c r="N35" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="O35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P35">
-        <v>30.16991135</v>
+        <v>31.43316</v>
       </c>
       <c r="Q35">
-        <v>74.18230296</v>
+        <v>75.00457</v>
       </c>
       <c r="R35" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S35">
-        <v>21605.5</v>
+        <v>52002</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -2714,52 +2789,52 @@
         <v>21</v>
       </c>
       <c r="D36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F36">
-        <v>528</v>
+        <v>45</v>
       </c>
       <c r="G36" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H36">
-        <v>30.132598</v>
+        <v>31.7521051</v>
       </c>
       <c r="I36">
-        <v>74.343463</v>
+        <v>74.9515121</v>
       </c>
       <c r="J36" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K36">
-        <v>397</v>
+        <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M36" t="s">
         <v>21</v>
       </c>
       <c r="N36" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="O36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P36">
-        <v>30.0974593</v>
+        <v>31.70744121</v>
       </c>
       <c r="Q36">
-        <v>74.206666</v>
+        <v>74.92578249</v>
       </c>
       <c r="R36" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S36">
-        <v>71196</v>
+        <v>137745</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -2773,52 +2848,52 @@
         <v>21</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F37">
-        <v>528</v>
+        <v>45</v>
       </c>
       <c r="G37" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H37">
-        <v>30.132598</v>
+        <v>31.7521051</v>
       </c>
       <c r="I37">
-        <v>74.343463</v>
+        <v>74.9515121</v>
       </c>
       <c r="J37" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K37">
-        <v>407</v>
+        <v>16</v>
       </c>
       <c r="L37" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M37" t="s">
         <v>21</v>
       </c>
       <c r="N37" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="O37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P37">
-        <v>30.126927</v>
+        <v>31.70744121</v>
       </c>
       <c r="Q37">
-        <v>74.161942</v>
+        <v>74.92578249</v>
       </c>
       <c r="R37" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S37">
-        <v>2489</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -2832,52 +2907,52 @@
         <v>21</v>
       </c>
       <c r="D38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F38">
-        <v>529</v>
+        <v>45</v>
       </c>
       <c r="G38" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H38">
-        <v>30.065633</v>
+        <v>31.7521051</v>
       </c>
       <c r="I38">
-        <v>73.98462499999999</v>
+        <v>74.9515121</v>
       </c>
       <c r="J38" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K38">
-        <v>407</v>
+        <v>38</v>
       </c>
       <c r="L38" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M38" t="s">
         <v>21</v>
       </c>
       <c r="N38" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="O38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P38">
-        <v>30.126927</v>
+        <v>31.43316</v>
       </c>
       <c r="Q38">
-        <v>74.161942</v>
+        <v>75.00457</v>
       </c>
       <c r="R38" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S38">
-        <v>34208</v>
+        <v>12973</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -2891,52 +2966,52 @@
         <v>21</v>
       </c>
       <c r="D39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F39">
-        <v>531</v>
+        <v>45</v>
       </c>
       <c r="G39" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H39">
-        <v>30.224829</v>
+        <v>31.7521051</v>
       </c>
       <c r="I39">
-        <v>74.12361199999999</v>
+        <v>74.9515121</v>
       </c>
       <c r="J39" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K39">
-        <v>400</v>
+        <v>39</v>
       </c>
       <c r="L39" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M39" t="s">
         <v>21</v>
       </c>
       <c r="N39" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="O39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P39">
-        <v>30.15809938</v>
+        <v>31.43316</v>
       </c>
       <c r="Q39">
-        <v>74.16401603</v>
+        <v>75.00457</v>
       </c>
       <c r="R39" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S39">
-        <v>54819.5</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -2950,52 +3025,52 @@
         <v>21</v>
       </c>
       <c r="D40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F40">
-        <v>532</v>
+        <v>46</v>
       </c>
       <c r="G40" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H40">
-        <v>30.178444</v>
+        <v>31.7478304</v>
       </c>
       <c r="I40">
-        <v>74.065141</v>
+        <v>74.9068102</v>
       </c>
       <c r="J40" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K40">
-        <v>407</v>
+        <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M40" t="s">
         <v>21</v>
       </c>
       <c r="N40" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="O40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P40">
-        <v>30.126927</v>
+        <v>31.70744121</v>
       </c>
       <c r="Q40">
-        <v>74.161942</v>
+        <v>74.92578249</v>
       </c>
       <c r="R40" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S40">
-        <v>37768</v>
+        <v>42255</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -3009,52 +3084,52 @@
         <v>21</v>
       </c>
       <c r="D41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F41">
-        <v>533</v>
+        <v>46</v>
       </c>
       <c r="G41" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H41">
-        <v>30.196706</v>
+        <v>31.7478304</v>
       </c>
       <c r="I41">
-        <v>74.04839699999999</v>
+        <v>74.9068102</v>
       </c>
       <c r="J41" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K41">
-        <v>407</v>
+        <v>45</v>
       </c>
       <c r="L41" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M41" t="s">
         <v>21</v>
       </c>
       <c r="N41" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="O41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P41">
-        <v>30.126927</v>
+        <v>31.48214</v>
       </c>
       <c r="Q41">
-        <v>74.161942</v>
+        <v>74.55329999999999</v>
       </c>
       <c r="R41" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S41">
-        <v>29874.5</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -3068,52 +3143,52 @@
         <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F42">
-        <v>534</v>
+        <v>46</v>
       </c>
       <c r="G42" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H42">
-        <v>30.035803</v>
+        <v>31.7478304</v>
       </c>
       <c r="I42">
-        <v>74.111367</v>
+        <v>74.9068102</v>
       </c>
       <c r="J42" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K42">
-        <v>407</v>
+        <v>46</v>
       </c>
       <c r="L42" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M42" t="s">
         <v>21</v>
       </c>
       <c r="N42" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="O42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P42">
-        <v>30.126927</v>
+        <v>31.48214</v>
       </c>
       <c r="Q42">
-        <v>74.161942</v>
+        <v>74.55329999999999</v>
       </c>
       <c r="R42" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S42">
-        <v>56983.5</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -3127,52 +3202,52 @@
         <v>21</v>
       </c>
       <c r="D43" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E43" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F43">
-        <v>535</v>
+        <v>501</v>
       </c>
       <c r="G43" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H43">
-        <v>30.131281</v>
+        <v>30.156605</v>
       </c>
       <c r="I43">
-        <v>74.103374</v>
+        <v>74.19572100000001</v>
       </c>
       <c r="J43" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K43">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="L43" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M43" t="s">
         <v>21</v>
       </c>
       <c r="N43" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O43" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P43">
-        <v>30.126927</v>
+        <v>30.15881226</v>
       </c>
       <c r="Q43">
-        <v>74.161942</v>
+        <v>74.18214294000001</v>
       </c>
       <c r="R43" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S43">
-        <v>23195.5</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -3186,52 +3261,52 @@
         <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F44">
-        <v>538</v>
+        <v>501</v>
       </c>
       <c r="G44" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="H44">
-        <v>30.029455</v>
+        <v>30.156605</v>
       </c>
       <c r="I44">
-        <v>74.077962</v>
+        <v>74.19572100000001</v>
       </c>
       <c r="J44" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K44">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="L44" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M44" t="s">
         <v>21</v>
       </c>
       <c r="N44" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O44" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P44">
-        <v>30.126927</v>
+        <v>30.15894356</v>
       </c>
       <c r="Q44">
-        <v>74.161942</v>
+        <v>74.18094151</v>
       </c>
       <c r="R44" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S44">
-        <v>57368</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -3245,52 +3320,52 @@
         <v>21</v>
       </c>
       <c r="D45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F45">
-        <v>540</v>
+        <v>501</v>
       </c>
       <c r="G45" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H45">
-        <v>29.983545</v>
+        <v>30.156605</v>
       </c>
       <c r="I45">
-        <v>74.173574</v>
+        <v>74.19572100000001</v>
       </c>
       <c r="J45" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K45">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="L45" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M45" t="s">
         <v>21</v>
       </c>
       <c r="N45" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O45" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P45">
-        <v>30.10552983</v>
+        <v>30.15848535</v>
       </c>
       <c r="Q45">
-        <v>74.18014506</v>
+        <v>74.18085842000001</v>
       </c>
       <c r="R45" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S45">
-        <v>2487</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="46" spans="1:19">
@@ -3304,40 +3379,40 @@
         <v>21</v>
       </c>
       <c r="D46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E46" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F46">
-        <v>541</v>
+        <v>501</v>
       </c>
       <c r="G46" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="H46">
-        <v>30.254422</v>
+        <v>30.156605</v>
       </c>
       <c r="I46">
-        <v>74.126414</v>
+        <v>74.19572100000001</v>
       </c>
       <c r="J46" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K46">
         <v>400</v>
       </c>
       <c r="L46" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M46" t="s">
         <v>21</v>
       </c>
       <c r="N46" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O46" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P46">
         <v>30.15809938</v>
@@ -3346,10 +3421,10 @@
         <v>74.16401603</v>
       </c>
       <c r="R46" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S46">
-        <v>29195</v>
+        <v>145397</v>
       </c>
     </row>
     <row r="47" spans="1:19">
@@ -3363,52 +3438,52 @@
         <v>21</v>
       </c>
       <c r="D47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E47" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F47">
-        <v>542</v>
+        <v>501</v>
       </c>
       <c r="G47" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="H47">
-        <v>30.247905</v>
+        <v>30.156605</v>
       </c>
       <c r="I47">
-        <v>74.129536</v>
+        <v>74.19572100000001</v>
       </c>
       <c r="J47" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K47">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L47" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M47" t="s">
         <v>21</v>
       </c>
       <c r="N47" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O47" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P47">
-        <v>30.15809938</v>
+        <v>30.1689126</v>
       </c>
       <c r="Q47">
-        <v>74.16401603</v>
+        <v>74.183232</v>
       </c>
       <c r="R47" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S47">
-        <v>26795</v>
+        <v>31477</v>
       </c>
     </row>
     <row r="48" spans="1:19">
@@ -3422,52 +3497,52 @@
         <v>21</v>
       </c>
       <c r="D48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E48" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F48">
-        <v>543</v>
+        <v>501</v>
       </c>
       <c r="G48" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="H48">
-        <v>30.25374</v>
+        <v>30.156605</v>
       </c>
       <c r="I48">
-        <v>74.122122</v>
+        <v>74.19572100000001</v>
       </c>
       <c r="J48" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K48">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="L48" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M48" t="s">
         <v>21</v>
       </c>
       <c r="N48" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O48" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P48">
-        <v>30.15809938</v>
+        <v>30.15857797</v>
       </c>
       <c r="Q48">
-        <v>74.16401603</v>
+        <v>74.18315728</v>
       </c>
       <c r="R48" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S48">
-        <v>7950</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="49" spans="1:19">
@@ -3481,52 +3556,52 @@
         <v>21</v>
       </c>
       <c r="D49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E49" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F49">
-        <v>545</v>
+        <v>502</v>
       </c>
       <c r="G49" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H49">
-        <v>29.975306</v>
+        <v>30.099748</v>
       </c>
       <c r="I49">
-        <v>74.164011</v>
+        <v>74.34759699999999</v>
       </c>
       <c r="J49" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K49">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="L49" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M49" t="s">
         <v>21</v>
       </c>
       <c r="N49" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O49" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P49">
-        <v>30.10552983</v>
+        <v>30.126927</v>
       </c>
       <c r="Q49">
-        <v>74.18014506</v>
+        <v>74.161942</v>
       </c>
       <c r="R49" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S49">
-        <v>5500</v>
+        <v>71835.5</v>
       </c>
     </row>
     <row r="50" spans="1:19">
@@ -3540,52 +3615,52 @@
         <v>21</v>
       </c>
       <c r="D50" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F50">
-        <v>546</v>
+        <v>503</v>
       </c>
       <c r="G50" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="H50">
-        <v>30.144184</v>
+        <v>30.028699</v>
       </c>
       <c r="I50">
-        <v>74.122771</v>
+        <v>74.197309</v>
       </c>
       <c r="J50" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K50">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="L50" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M50" t="s">
         <v>21</v>
       </c>
       <c r="N50" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O50" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P50">
-        <v>30.126927</v>
+        <v>30.10552983</v>
       </c>
       <c r="Q50">
-        <v>74.161942</v>
+        <v>74.18014506</v>
       </c>
       <c r="R50" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S50">
-        <v>12630.5</v>
+        <v>73538.5</v>
       </c>
     </row>
     <row r="51" spans="1:19">
@@ -3599,40 +3674,40 @@
         <v>21</v>
       </c>
       <c r="D51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E51" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F51">
-        <v>547</v>
+        <v>503</v>
       </c>
       <c r="G51" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="H51">
-        <v>30.161715</v>
+        <v>30.028699</v>
       </c>
       <c r="I51">
-        <v>73.987483</v>
+        <v>74.197309</v>
       </c>
       <c r="J51" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K51">
         <v>407</v>
       </c>
       <c r="L51" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M51" t="s">
         <v>21</v>
       </c>
       <c r="N51" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O51" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P51">
         <v>30.126927</v>
@@ -3641,10 +3716,10 @@
         <v>74.161942</v>
       </c>
       <c r="R51" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S51">
-        <v>13803</v>
+        <v>322</v>
       </c>
     </row>
     <row r="52" spans="1:19">
@@ -3658,40 +3733,40 @@
         <v>21</v>
       </c>
       <c r="D52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E52" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F52">
-        <v>548</v>
+        <v>505</v>
       </c>
       <c r="G52" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="H52">
-        <v>30.21135</v>
+        <v>30.162859</v>
       </c>
       <c r="I52">
-        <v>74.02397999999999</v>
+        <v>73.991192</v>
       </c>
       <c r="J52" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K52">
         <v>407</v>
       </c>
       <c r="L52" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M52" t="s">
         <v>21</v>
       </c>
       <c r="N52" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O52" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P52">
         <v>30.126927</v>
@@ -3700,10 +3775,10 @@
         <v>74.161942</v>
       </c>
       <c r="R52" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S52">
-        <v>9145</v>
+        <v>37309</v>
       </c>
     </row>
     <row r="53" spans="1:19">
@@ -3717,52 +3792,52 @@
         <v>21</v>
       </c>
       <c r="D53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E53" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F53">
-        <v>549</v>
+        <v>506</v>
       </c>
       <c r="G53" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H53">
-        <v>30.296726</v>
+        <v>30.16948</v>
       </c>
       <c r="I53">
-        <v>74.263169</v>
+        <v>74.28432100000001</v>
       </c>
       <c r="J53" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K53">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L53" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M53" t="s">
         <v>21</v>
       </c>
       <c r="N53" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O53" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P53">
-        <v>30.17081207</v>
+        <v>30.1689126</v>
       </c>
       <c r="Q53">
-        <v>74.18179719</v>
+        <v>74.183232</v>
       </c>
       <c r="R53" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S53">
-        <v>17622.5</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="54" spans="1:19">
@@ -3776,52 +3851,52 @@
         <v>21</v>
       </c>
       <c r="D54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E54" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F54">
-        <v>550</v>
+        <v>506</v>
       </c>
       <c r="G54" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="H54">
-        <v>30.285139</v>
+        <v>30.16948</v>
       </c>
       <c r="I54">
-        <v>74.172681</v>
+        <v>74.28432100000001</v>
       </c>
       <c r="J54" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K54">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="L54" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M54" t="s">
         <v>21</v>
       </c>
       <c r="N54" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O54" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P54">
-        <v>30.15809938</v>
+        <v>30.16991135</v>
       </c>
       <c r="Q54">
-        <v>74.16401603</v>
+        <v>74.18230296</v>
       </c>
       <c r="R54" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S54">
-        <v>2347.5</v>
+        <v>15202.5</v>
       </c>
     </row>
     <row r="55" spans="1:19">
@@ -3835,52 +3910,52 @@
         <v>21</v>
       </c>
       <c r="D55" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F55">
-        <v>550</v>
+        <v>507</v>
       </c>
       <c r="G55" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="H55">
-        <v>30.285139</v>
+        <v>30.034436</v>
       </c>
       <c r="I55">
-        <v>74.172681</v>
+        <v>74.233859</v>
       </c>
       <c r="J55" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K55">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="L55" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M55" t="s">
         <v>21</v>
       </c>
       <c r="N55" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O55" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P55">
-        <v>30.17767461</v>
+        <v>30.08675444</v>
       </c>
       <c r="Q55">
-        <v>74.17723581</v>
+        <v>74.20888524</v>
       </c>
       <c r="R55" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S55">
-        <v>40337.5</v>
+        <v>49766</v>
       </c>
     </row>
     <row r="56" spans="1:19">
@@ -3894,52 +3969,52 @@
         <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F56">
-        <v>551</v>
+        <v>508</v>
       </c>
       <c r="G56" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H56">
-        <v>30.260814</v>
+        <v>30.182524</v>
       </c>
       <c r="I56">
-        <v>74.269329</v>
+        <v>74.326095</v>
       </c>
       <c r="J56" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K56">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="L56" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M56" t="s">
         <v>21</v>
       </c>
       <c r="N56" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O56" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P56">
-        <v>30.17081207</v>
+        <v>30.16991135</v>
       </c>
       <c r="Q56">
-        <v>74.18179719</v>
+        <v>74.18230296</v>
       </c>
       <c r="R56" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S56">
-        <v>56502.5</v>
+        <v>41707.5</v>
       </c>
     </row>
     <row r="57" spans="1:19">
@@ -3953,52 +4028,52 @@
         <v>21</v>
       </c>
       <c r="D57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F57">
-        <v>552</v>
+        <v>509</v>
       </c>
       <c r="G57" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="H57">
-        <v>30.290503</v>
+        <v>30.199756</v>
       </c>
       <c r="I57">
-        <v>74.220803</v>
+        <v>74.108656</v>
       </c>
       <c r="J57" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K57">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L57" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M57" t="s">
         <v>21</v>
       </c>
       <c r="N57" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O57" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P57">
-        <v>30.17081207</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q57">
-        <v>74.18179719</v>
+        <v>74.16401603</v>
       </c>
       <c r="R57" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S57">
-        <v>43110</v>
+        <v>18038</v>
       </c>
     </row>
     <row r="58" spans="1:19">
@@ -4012,52 +4087,52 @@
         <v>21</v>
       </c>
       <c r="D58" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F58">
-        <v>560</v>
+        <v>510</v>
       </c>
       <c r="G58" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="H58">
-        <v>30.251211</v>
+        <v>30.113508</v>
       </c>
       <c r="I58">
-        <v>74.011872</v>
+        <v>73.989543</v>
       </c>
       <c r="J58" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K58">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="L58" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M58" t="s">
         <v>21</v>
       </c>
       <c r="N58" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O58" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P58">
-        <v>30.15809938</v>
+        <v>30.126927</v>
       </c>
       <c r="Q58">
-        <v>74.16401603</v>
+        <v>74.161942</v>
       </c>
       <c r="R58" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S58">
-        <v>128218</v>
+        <v>44568.5</v>
       </c>
     </row>
     <row r="59" spans="1:19">
@@ -4071,52 +4146,52 @@
         <v>21</v>
       </c>
       <c r="D59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F59">
-        <v>565</v>
+        <v>511</v>
       </c>
       <c r="G59" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="H59">
-        <v>30.280985</v>
+        <v>30.122605</v>
       </c>
       <c r="I59">
-        <v>74.057811</v>
+        <v>74.328892</v>
       </c>
       <c r="J59" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K59">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="L59" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M59" t="s">
         <v>21</v>
       </c>
       <c r="N59" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O59" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P59">
-        <v>30.15809938</v>
+        <v>30.126927</v>
       </c>
       <c r="Q59">
-        <v>74.16401603</v>
+        <v>74.161942</v>
       </c>
       <c r="R59" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S59">
-        <v>62709.5</v>
+        <v>25216</v>
       </c>
     </row>
     <row r="60" spans="1:19">
@@ -4130,40 +4205,40 @@
         <v>21</v>
       </c>
       <c r="D60" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F60">
-        <v>612</v>
+        <v>512</v>
       </c>
       <c r="G60" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="H60">
-        <v>30.3064</v>
+        <v>30.237206</v>
       </c>
       <c r="I60">
-        <v>74.22073899999999</v>
+        <v>74.23982700000001</v>
       </c>
       <c r="J60" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K60">
         <v>401</v>
       </c>
       <c r="L60" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M60" t="s">
         <v>21</v>
       </c>
       <c r="N60" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O60" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P60">
         <v>30.17081207</v>
@@ -4172,10 +4247,10 @@
         <v>74.18179719</v>
       </c>
       <c r="R60" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S60">
-        <v>47189.5</v>
+        <v>44802</v>
       </c>
     </row>
     <row r="61" spans="1:19">
@@ -4192,49 +4267,49 @@
         <v>24</v>
       </c>
       <c r="E61" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F61">
-        <v>1046</v>
+        <v>513</v>
       </c>
       <c r="G61" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="H61">
-        <v>31.425406</v>
+        <v>30.023582</v>
       </c>
       <c r="I61">
-        <v>75.719528</v>
+        <v>74.04262799999999</v>
       </c>
       <c r="J61" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K61">
-        <v>625</v>
+        <v>407</v>
       </c>
       <c r="L61" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M61" t="s">
         <v>21</v>
       </c>
       <c r="N61" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="O61" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P61">
-        <v>31.408658</v>
+        <v>30.126927</v>
       </c>
       <c r="Q61">
-        <v>75.685958</v>
+        <v>74.161942</v>
       </c>
       <c r="R61" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S61">
-        <v>21500</v>
+        <v>30276.5</v>
       </c>
     </row>
     <row r="62" spans="1:19">
@@ -4248,52 +4323,52 @@
         <v>21</v>
       </c>
       <c r="D62" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E62" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F62">
-        <v>1577</v>
+        <v>514</v>
       </c>
       <c r="G62" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="H62">
-        <v>30.4426709</v>
+        <v>29.960526</v>
       </c>
       <c r="I62">
-        <v>74.4101264</v>
+        <v>74.219824</v>
       </c>
       <c r="J62" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K62">
-        <v>866</v>
+        <v>404</v>
       </c>
       <c r="L62" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M62" t="s">
         <v>21</v>
       </c>
       <c r="N62" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O62" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P62">
-        <v>30.458388</v>
+        <v>30.10552983</v>
       </c>
       <c r="Q62">
-        <v>74.453514</v>
+        <v>74.18014506</v>
       </c>
       <c r="R62" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S62">
-        <v>88594</v>
+        <v>19961.5</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4307,52 +4382,52 @@
         <v>21</v>
       </c>
       <c r="D63" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E63" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F63">
-        <v>1577</v>
+        <v>515</v>
       </c>
       <c r="G63" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="H63">
-        <v>30.4426709</v>
+        <v>30.082625</v>
       </c>
       <c r="I63">
-        <v>74.4101264</v>
+        <v>74.288794</v>
       </c>
       <c r="J63" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K63">
-        <v>870</v>
+        <v>397</v>
       </c>
       <c r="L63" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M63" t="s">
         <v>21</v>
       </c>
       <c r="N63" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O63" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P63">
-        <v>30.458388</v>
+        <v>30.0974593</v>
       </c>
       <c r="Q63">
-        <v>74.453514</v>
+        <v>74.206666</v>
       </c>
       <c r="R63" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S63">
-        <v>10000</v>
+        <v>9709</v>
       </c>
     </row>
     <row r="64" spans="1:19">
@@ -4366,52 +4441,52 @@
         <v>21</v>
       </c>
       <c r="D64" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64">
-        <v>1577</v>
+        <v>515</v>
       </c>
       <c r="G64" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="H64">
-        <v>30.4426709</v>
+        <v>30.082625</v>
       </c>
       <c r="I64">
-        <v>74.4101264</v>
+        <v>74.288794</v>
       </c>
       <c r="J64" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K64">
-        <v>875</v>
+        <v>407</v>
       </c>
       <c r="L64" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M64" t="s">
         <v>21</v>
       </c>
       <c r="N64" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O64" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P64">
-        <v>30.458388</v>
+        <v>30.126927</v>
       </c>
       <c r="Q64">
-        <v>74.453514</v>
+        <v>74.161942</v>
       </c>
       <c r="R64" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S64">
-        <v>5000</v>
+        <v>54672</v>
       </c>
     </row>
     <row r="65" spans="1:19">
@@ -4425,52 +4500,52 @@
         <v>21</v>
       </c>
       <c r="D65" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F65">
-        <v>1577</v>
+        <v>516</v>
       </c>
       <c r="G65" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="H65">
-        <v>30.4426709</v>
+        <v>30.221432</v>
       </c>
       <c r="I65">
-        <v>74.4101264</v>
+        <v>74.35153099999999</v>
       </c>
       <c r="J65" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K65">
-        <v>876</v>
+        <v>401</v>
       </c>
       <c r="L65" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M65" t="s">
         <v>21</v>
       </c>
       <c r="N65" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O65" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P65">
-        <v>30.458388</v>
+        <v>30.17081207</v>
       </c>
       <c r="Q65">
-        <v>74.453514</v>
+        <v>74.18179719</v>
       </c>
       <c r="R65" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S65">
-        <v>5000</v>
+        <v>13755.5</v>
       </c>
     </row>
     <row r="66" spans="1:19">
@@ -4484,52 +4559,52 @@
         <v>21</v>
       </c>
       <c r="D66" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F66">
-        <v>1597</v>
+        <v>516</v>
       </c>
       <c r="G66" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="H66">
-        <v>30.419565</v>
+        <v>30.221432</v>
       </c>
       <c r="I66">
-        <v>74.44302166999999</v>
+        <v>74.35153099999999</v>
       </c>
       <c r="J66" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K66">
-        <v>866</v>
+        <v>406</v>
       </c>
       <c r="L66" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M66" t="s">
         <v>21</v>
       </c>
       <c r="N66" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O66" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P66">
-        <v>30.458388</v>
+        <v>30.16991135</v>
       </c>
       <c r="Q66">
-        <v>74.453514</v>
+        <v>74.18230296</v>
       </c>
       <c r="R66" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S66">
-        <v>38086</v>
+        <v>6714.5</v>
       </c>
     </row>
     <row r="67" spans="1:19">
@@ -4543,52 +4618,52 @@
         <v>21</v>
       </c>
       <c r="D67" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E67" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F67">
-        <v>1597</v>
+        <v>517</v>
       </c>
       <c r="G67" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="H67">
-        <v>30.419565</v>
+        <v>30.254598</v>
       </c>
       <c r="I67">
-        <v>74.44302166999999</v>
+        <v>74.124285</v>
       </c>
       <c r="J67" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K67">
-        <v>872</v>
+        <v>400</v>
       </c>
       <c r="L67" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M67" t="s">
         <v>21</v>
       </c>
       <c r="N67" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O67" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P67">
-        <v>30.458388</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q67">
-        <v>74.453514</v>
+        <v>74.16401603</v>
       </c>
       <c r="R67" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S67">
-        <v>30720</v>
+        <v>39817.5</v>
       </c>
     </row>
     <row r="68" spans="1:19">
@@ -4602,52 +4677,52 @@
         <v>21</v>
       </c>
       <c r="D68" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E68" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F68">
-        <v>1597</v>
+        <v>518</v>
       </c>
       <c r="G68" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H68">
-        <v>30.419565</v>
+        <v>30.173582</v>
       </c>
       <c r="I68">
-        <v>74.44302166999999</v>
+        <v>74.250483</v>
       </c>
       <c r="J68" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K68">
-        <v>877</v>
+        <v>406</v>
       </c>
       <c r="L68" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M68" t="s">
         <v>21</v>
       </c>
       <c r="N68" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O68" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P68">
-        <v>30.458388</v>
+        <v>30.16991135</v>
       </c>
       <c r="Q68">
-        <v>74.453514</v>
+        <v>74.18230296</v>
       </c>
       <c r="R68" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S68">
-        <v>5127</v>
+        <v>10375.5</v>
       </c>
     </row>
     <row r="69" spans="1:19">
@@ -4661,52 +4736,52 @@
         <v>21</v>
       </c>
       <c r="D69" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E69" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F69">
-        <v>1607</v>
+        <v>520</v>
       </c>
       <c r="G69" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="H69">
-        <v>30.4726737</v>
+        <v>30.21019</v>
       </c>
       <c r="I69">
-        <v>74.5049465</v>
+        <v>74.024728</v>
       </c>
       <c r="J69" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K69">
-        <v>864</v>
+        <v>400</v>
       </c>
       <c r="L69" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M69" t="s">
         <v>21</v>
       </c>
       <c r="N69" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O69" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P69">
-        <v>30.458388</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q69">
-        <v>74.453514</v>
+        <v>74.16401603</v>
       </c>
       <c r="R69" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S69">
-        <v>294680</v>
+        <v>72343</v>
       </c>
     </row>
     <row r="70" spans="1:19">
@@ -4720,52 +4795,52 @@
         <v>21</v>
       </c>
       <c r="D70" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E70" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F70">
-        <v>1607</v>
+        <v>520</v>
       </c>
       <c r="G70" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="H70">
-        <v>30.4726737</v>
+        <v>30.21019</v>
       </c>
       <c r="I70">
-        <v>74.5049465</v>
+        <v>74.024728</v>
       </c>
       <c r="J70" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K70">
-        <v>865</v>
+        <v>407</v>
       </c>
       <c r="L70" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M70" t="s">
         <v>21</v>
       </c>
       <c r="N70" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O70" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P70">
-        <v>30.458388</v>
+        <v>30.126927</v>
       </c>
       <c r="Q70">
-        <v>74.453514</v>
+        <v>74.161942</v>
       </c>
       <c r="R70" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S70">
-        <v>16680</v>
+        <v>28606.5</v>
       </c>
     </row>
     <row r="71" spans="1:19">
@@ -4779,52 +4854,52 @@
         <v>21</v>
       </c>
       <c r="D71" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E71" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F71">
-        <v>1607</v>
+        <v>521</v>
       </c>
       <c r="G71" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="H71">
-        <v>30.4726737</v>
+        <v>30.257887</v>
       </c>
       <c r="I71">
-        <v>74.5049465</v>
+        <v>74.185624</v>
       </c>
       <c r="J71" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K71">
-        <v>867</v>
+        <v>401</v>
       </c>
       <c r="L71" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M71" t="s">
         <v>21</v>
       </c>
       <c r="N71" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O71" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P71">
-        <v>30.458388</v>
+        <v>30.17081207</v>
       </c>
       <c r="Q71">
-        <v>74.453514</v>
+        <v>74.18179719</v>
       </c>
       <c r="R71" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S71">
-        <v>10000</v>
+        <v>2347.5</v>
       </c>
     </row>
     <row r="72" spans="1:19">
@@ -4838,52 +4913,52 @@
         <v>21</v>
       </c>
       <c r="D72" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F72">
-        <v>1607</v>
+        <v>521</v>
       </c>
       <c r="G72" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="H72">
-        <v>30.4726737</v>
+        <v>30.257887</v>
       </c>
       <c r="I72">
-        <v>74.5049465</v>
+        <v>74.185624</v>
       </c>
       <c r="J72" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K72">
-        <v>868</v>
+        <v>402</v>
       </c>
       <c r="L72" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M72" t="s">
         <v>21</v>
       </c>
       <c r="N72" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O72" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P72">
-        <v>30.458388</v>
+        <v>30.17767461</v>
       </c>
       <c r="Q72">
-        <v>74.453514</v>
+        <v>74.17723581</v>
       </c>
       <c r="R72" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S72">
-        <v>10000</v>
+        <v>34275</v>
       </c>
     </row>
     <row r="73" spans="1:19">
@@ -4897,52 +4972,52 @@
         <v>21</v>
       </c>
       <c r="D73" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E73" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F73">
-        <v>1607</v>
+        <v>522</v>
       </c>
       <c r="G73" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H73">
-        <v>30.4726737</v>
+        <v>30.007285</v>
       </c>
       <c r="I73">
-        <v>74.5049465</v>
+        <v>74.126166</v>
       </c>
       <c r="J73" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K73">
-        <v>869</v>
+        <v>407</v>
       </c>
       <c r="L73" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M73" t="s">
         <v>21</v>
       </c>
       <c r="N73" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O73" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P73">
-        <v>30.458388</v>
+        <v>30.126927</v>
       </c>
       <c r="Q73">
-        <v>74.453514</v>
+        <v>74.161942</v>
       </c>
       <c r="R73" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S73">
-        <v>10000</v>
+        <v>28245</v>
       </c>
     </row>
     <row r="74" spans="1:19">
@@ -4956,52 +5031,52 @@
         <v>21</v>
       </c>
       <c r="D74" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E74" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F74">
-        <v>1607</v>
+        <v>523</v>
       </c>
       <c r="G74" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H74">
-        <v>30.4726737</v>
+        <v>30.039412</v>
       </c>
       <c r="I74">
-        <v>74.5049465</v>
+        <v>73.954567</v>
       </c>
       <c r="J74" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K74">
-        <v>871</v>
+        <v>407</v>
       </c>
       <c r="L74" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M74" t="s">
         <v>21</v>
       </c>
       <c r="N74" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O74" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P74">
-        <v>30.458388</v>
+        <v>30.126927</v>
       </c>
       <c r="Q74">
-        <v>74.453514</v>
+        <v>74.161942</v>
       </c>
       <c r="R74" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S74">
-        <v>30720</v>
+        <v>12854</v>
       </c>
     </row>
     <row r="75" spans="1:19">
@@ -5015,52 +5090,52 @@
         <v>21</v>
       </c>
       <c r="D75" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E75" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F75">
-        <v>1607</v>
+        <v>524</v>
       </c>
       <c r="G75" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H75">
-        <v>30.4726737</v>
+        <v>30.012837</v>
       </c>
       <c r="I75">
-        <v>74.5049465</v>
+        <v>74.432883</v>
       </c>
       <c r="J75" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K75">
-        <v>873</v>
+        <v>397</v>
       </c>
       <c r="L75" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M75" t="s">
         <v>21</v>
       </c>
       <c r="N75" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O75" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P75">
-        <v>30.458388</v>
+        <v>30.0974593</v>
       </c>
       <c r="Q75">
-        <v>74.453514</v>
+        <v>74.206666</v>
       </c>
       <c r="R75" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S75">
-        <v>29640</v>
+        <v>74081</v>
       </c>
     </row>
     <row r="76" spans="1:19">
@@ -5074,52 +5149,52 @@
         <v>21</v>
       </c>
       <c r="D76" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E76" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F76">
-        <v>1607</v>
+        <v>525</v>
       </c>
       <c r="G76" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H76">
-        <v>30.4726737</v>
+        <v>30.127701</v>
       </c>
       <c r="I76">
-        <v>74.5049465</v>
+        <v>74.06368999999999</v>
       </c>
       <c r="J76" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K76">
-        <v>874</v>
+        <v>407</v>
       </c>
       <c r="L76" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M76" t="s">
         <v>21</v>
       </c>
       <c r="N76" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O76" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P76">
-        <v>30.458388</v>
+        <v>30.126927</v>
       </c>
       <c r="Q76">
-        <v>74.453514</v>
+        <v>74.161942</v>
       </c>
       <c r="R76" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S76">
-        <v>28460</v>
+        <v>21311</v>
       </c>
     </row>
     <row r="77" spans="1:19">
@@ -5133,52 +5208,52 @@
         <v>21</v>
       </c>
       <c r="D77" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E77" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F77">
-        <v>1607</v>
+        <v>526</v>
       </c>
       <c r="G77" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H77">
-        <v>30.4726737</v>
+        <v>29.98347</v>
       </c>
       <c r="I77">
-        <v>74.5049465</v>
+        <v>74.283652</v>
       </c>
       <c r="J77" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K77">
-        <v>877</v>
+        <v>394</v>
       </c>
       <c r="L77" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M77" t="s">
         <v>21</v>
       </c>
       <c r="N77" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O77" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P77">
-        <v>30.458388</v>
+        <v>30.08793156</v>
       </c>
       <c r="Q77">
-        <v>74.453514</v>
+        <v>74.20908439</v>
       </c>
       <c r="R77" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S77">
-        <v>15353</v>
+        <v>30310</v>
       </c>
     </row>
     <row r="78" spans="1:19">
@@ -5192,52 +5267,52 @@
         <v>21</v>
       </c>
       <c r="D78" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E78" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F78">
-        <v>1607</v>
+        <v>526</v>
       </c>
       <c r="G78" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H78">
-        <v>30.4726737</v>
+        <v>29.98347</v>
       </c>
       <c r="I78">
-        <v>74.5049465</v>
+        <v>74.283652</v>
       </c>
       <c r="J78" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K78">
-        <v>878</v>
+        <v>395</v>
       </c>
       <c r="L78" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M78" t="s">
         <v>21</v>
       </c>
       <c r="N78" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O78" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P78">
-        <v>30.458388</v>
+        <v>30.08675444</v>
       </c>
       <c r="Q78">
-        <v>74.453514</v>
+        <v>74.20888524</v>
       </c>
       <c r="R78" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S78">
-        <v>20480</v>
+        <v>3784</v>
       </c>
     </row>
     <row r="79" spans="1:19">
@@ -5251,52 +5326,52 @@
         <v>21</v>
       </c>
       <c r="D79" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E79" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F79">
-        <v>1607</v>
+        <v>527</v>
       </c>
       <c r="G79" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H79">
-        <v>30.4726737</v>
+        <v>30.216512</v>
       </c>
       <c r="I79">
-        <v>74.5049465</v>
+        <v>74.269492</v>
       </c>
       <c r="J79" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K79">
-        <v>879</v>
+        <v>401</v>
       </c>
       <c r="L79" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M79" t="s">
         <v>21</v>
       </c>
       <c r="N79" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O79" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P79">
-        <v>30.458388</v>
+        <v>30.17081207</v>
       </c>
       <c r="Q79">
-        <v>74.453514</v>
+        <v>74.18179719</v>
       </c>
       <c r="R79" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S79">
-        <v>20480</v>
+        <v>32401</v>
       </c>
     </row>
     <row r="80" spans="1:19">
@@ -5310,52 +5385,52 @@
         <v>21</v>
       </c>
       <c r="D80" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E80" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F80">
-        <v>1607</v>
+        <v>528</v>
       </c>
       <c r="G80" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H80">
-        <v>30.4726737</v>
+        <v>30.132598</v>
       </c>
       <c r="I80">
-        <v>74.5049465</v>
+        <v>74.343463</v>
       </c>
       <c r="J80" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K80">
-        <v>880</v>
+        <v>407</v>
       </c>
       <c r="L80" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M80" t="s">
         <v>21</v>
       </c>
       <c r="N80" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="O80" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P80">
-        <v>30.458388</v>
+        <v>30.126927</v>
       </c>
       <c r="Q80">
-        <v>74.453514</v>
+        <v>74.161942</v>
       </c>
       <c r="R80" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S80">
-        <v>15360</v>
+        <v>73685</v>
       </c>
     </row>
     <row r="81" spans="1:19">
@@ -5369,52 +5444,52 @@
         <v>21</v>
       </c>
       <c r="D81" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E81" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F81">
-        <v>1660</v>
+        <v>529</v>
       </c>
       <c r="G81" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H81">
-        <v>30.2397029</v>
+        <v>30.065633</v>
       </c>
       <c r="I81">
-        <v>74.2953411</v>
+        <v>73.98462499999999</v>
       </c>
       <c r="J81" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K81">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="L81" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M81" t="s">
         <v>21</v>
       </c>
       <c r="N81" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O81" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P81">
-        <v>30.17081207</v>
+        <v>30.126927</v>
       </c>
       <c r="Q81">
-        <v>74.18179719</v>
+        <v>74.161942</v>
       </c>
       <c r="R81" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S81">
-        <v>1314.5</v>
+        <v>34208</v>
       </c>
     </row>
     <row r="82" spans="1:19">
@@ -5428,52 +5503,52 @@
         <v>21</v>
       </c>
       <c r="D82" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E82" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F82">
-        <v>1660</v>
+        <v>530</v>
       </c>
       <c r="G82" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H82">
-        <v>30.2397029</v>
+        <v>29.956267</v>
       </c>
       <c r="I82">
-        <v>74.2953411</v>
+        <v>74.332578</v>
       </c>
       <c r="J82" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K82">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="L82" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M82" t="s">
         <v>21</v>
       </c>
       <c r="N82" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="O82" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P82">
-        <v>30.16991135</v>
+        <v>30.08793156</v>
       </c>
       <c r="Q82">
-        <v>74.18230296</v>
+        <v>74.20908439</v>
       </c>
       <c r="R82" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S82">
-        <v>52394.5</v>
+        <v>17701</v>
       </c>
     </row>
     <row r="83" spans="1:19">
@@ -5487,52 +5562,52 @@
         <v>21</v>
       </c>
       <c r="D83" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E83" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F83">
-        <v>2153</v>
+        <v>531</v>
       </c>
       <c r="G83" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H83">
-        <v>31.3953454</v>
+        <v>30.224829</v>
       </c>
       <c r="I83">
-        <v>74.6222925</v>
+        <v>74.12361199999999</v>
       </c>
       <c r="J83" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K83">
-        <v>2</v>
+        <v>400</v>
       </c>
       <c r="L83" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="M83" t="s">
         <v>21</v>
       </c>
       <c r="N83" t="s">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="O83" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P83">
-        <v>31.45335</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q83">
-        <v>74.46541999999999</v>
+        <v>74.16401603</v>
       </c>
       <c r="R83" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="S83">
-        <v>150000</v>
+        <v>54819.5</v>
       </c>
     </row>
     <row r="84" spans="1:19">
@@ -5546,52 +5621,2825 @@
         <v>21</v>
       </c>
       <c r="D84" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E84" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F84">
-        <v>2153</v>
+        <v>532</v>
       </c>
       <c r="G84" t="s">
         <v>80</v>
       </c>
       <c r="H84">
-        <v>31.3953454</v>
+        <v>30.178444</v>
       </c>
       <c r="I84">
-        <v>74.6222925</v>
+        <v>74.065141</v>
       </c>
       <c r="J84" t="s">
+        <v>110</v>
+      </c>
+      <c r="K84">
+        <v>407</v>
+      </c>
+      <c r="L84" t="s">
+        <v>111</v>
+      </c>
+      <c r="M84" t="s">
+        <v>21</v>
+      </c>
+      <c r="N84" t="s">
+        <v>24</v>
+      </c>
+      <c r="O84" t="s">
+        <v>29</v>
+      </c>
+      <c r="P84">
+        <v>30.126927</v>
+      </c>
+      <c r="Q84">
+        <v>74.161942</v>
+      </c>
+      <c r="R84" t="s">
+        <v>112</v>
+      </c>
+      <c r="S84">
+        <v>37768</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19">
+      <c r="A85" t="s">
+        <v>19</v>
+      </c>
+      <c r="B85" t="s">
+        <v>20</v>
+      </c>
+      <c r="C85" t="s">
+        <v>21</v>
+      </c>
+      <c r="D85" t="s">
+        <v>24</v>
+      </c>
+      <c r="E85" t="s">
+        <v>29</v>
+      </c>
+      <c r="F85">
+        <v>533</v>
+      </c>
+      <c r="G85" t="s">
         <v>81</v>
       </c>
-      <c r="K84">
-        <v>4</v>
-      </c>
-      <c r="L84" t="s">
+      <c r="H85">
+        <v>30.196706</v>
+      </c>
+      <c r="I85">
+        <v>74.04839699999999</v>
+      </c>
+      <c r="J85" t="s">
+        <v>110</v>
+      </c>
+      <c r="K85">
+        <v>407</v>
+      </c>
+      <c r="L85" t="s">
+        <v>111</v>
+      </c>
+      <c r="M85" t="s">
+        <v>21</v>
+      </c>
+      <c r="N85" t="s">
+        <v>24</v>
+      </c>
+      <c r="O85" t="s">
+        <v>29</v>
+      </c>
+      <c r="P85">
+        <v>30.126927</v>
+      </c>
+      <c r="Q85">
+        <v>74.161942</v>
+      </c>
+      <c r="R85" t="s">
+        <v>112</v>
+      </c>
+      <c r="S85">
+        <v>29874.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19">
+      <c r="A86" t="s">
+        <v>19</v>
+      </c>
+      <c r="B86" t="s">
+        <v>20</v>
+      </c>
+      <c r="C86" t="s">
+        <v>21</v>
+      </c>
+      <c r="D86" t="s">
+        <v>24</v>
+      </c>
+      <c r="E86" t="s">
+        <v>29</v>
+      </c>
+      <c r="F86">
+        <v>534</v>
+      </c>
+      <c r="G86" t="s">
         <v>82</v>
       </c>
-      <c r="M84" t="s">
-        <v>21</v>
-      </c>
-      <c r="N84" t="s">
+      <c r="H86">
+        <v>30.035803</v>
+      </c>
+      <c r="I86">
+        <v>74.111367</v>
+      </c>
+      <c r="J86" t="s">
+        <v>110</v>
+      </c>
+      <c r="K86">
+        <v>407</v>
+      </c>
+      <c r="L86" t="s">
+        <v>111</v>
+      </c>
+      <c r="M86" t="s">
+        <v>21</v>
+      </c>
+      <c r="N86" t="s">
+        <v>24</v>
+      </c>
+      <c r="O86" t="s">
+        <v>29</v>
+      </c>
+      <c r="P86">
+        <v>30.126927</v>
+      </c>
+      <c r="Q86">
+        <v>74.161942</v>
+      </c>
+      <c r="R86" t="s">
+        <v>112</v>
+      </c>
+      <c r="S86">
+        <v>56983.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19">
+      <c r="A87" t="s">
+        <v>19</v>
+      </c>
+      <c r="B87" t="s">
+        <v>20</v>
+      </c>
+      <c r="C87" t="s">
+        <v>21</v>
+      </c>
+      <c r="D87" t="s">
+        <v>24</v>
+      </c>
+      <c r="E87" t="s">
+        <v>29</v>
+      </c>
+      <c r="F87">
+        <v>535</v>
+      </c>
+      <c r="G87" t="s">
         <v>83</v>
       </c>
-      <c r="O84" t="s">
+      <c r="H87">
+        <v>30.131281</v>
+      </c>
+      <c r="I87">
+        <v>74.103374</v>
+      </c>
+      <c r="J87" t="s">
+        <v>110</v>
+      </c>
+      <c r="K87">
+        <v>407</v>
+      </c>
+      <c r="L87" t="s">
+        <v>111</v>
+      </c>
+      <c r="M87" t="s">
+        <v>21</v>
+      </c>
+      <c r="N87" t="s">
+        <v>24</v>
+      </c>
+      <c r="O87" t="s">
+        <v>29</v>
+      </c>
+      <c r="P87">
+        <v>30.126927</v>
+      </c>
+      <c r="Q87">
+        <v>74.161942</v>
+      </c>
+      <c r="R87" t="s">
+        <v>112</v>
+      </c>
+      <c r="S87">
+        <v>23195.5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19">
+      <c r="A88" t="s">
+        <v>19</v>
+      </c>
+      <c r="B88" t="s">
+        <v>20</v>
+      </c>
+      <c r="C88" t="s">
+        <v>21</v>
+      </c>
+      <c r="D88" t="s">
+        <v>24</v>
+      </c>
+      <c r="E88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F88">
+        <v>536</v>
+      </c>
+      <c r="G88" t="s">
+        <v>84</v>
+      </c>
+      <c r="H88">
+        <v>30.027734</v>
+      </c>
+      <c r="I88">
+        <v>74.36728100000001</v>
+      </c>
+      <c r="J88" t="s">
+        <v>110</v>
+      </c>
+      <c r="K88">
+        <v>394</v>
+      </c>
+      <c r="L88" t="s">
+        <v>111</v>
+      </c>
+      <c r="M88" t="s">
+        <v>21</v>
+      </c>
+      <c r="N88" t="s">
+        <v>24</v>
+      </c>
+      <c r="O88" t="s">
+        <v>29</v>
+      </c>
+      <c r="P88">
+        <v>30.08793156</v>
+      </c>
+      <c r="Q88">
+        <v>74.20908439</v>
+      </c>
+      <c r="R88" t="s">
+        <v>112</v>
+      </c>
+      <c r="S88">
+        <v>71340</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19">
+      <c r="A89" t="s">
+        <v>19</v>
+      </c>
+      <c r="B89" t="s">
+        <v>20</v>
+      </c>
+      <c r="C89" t="s">
+        <v>21</v>
+      </c>
+      <c r="D89" t="s">
+        <v>24</v>
+      </c>
+      <c r="E89" t="s">
+        <v>29</v>
+      </c>
+      <c r="F89">
+        <v>536</v>
+      </c>
+      <c r="G89" t="s">
+        <v>84</v>
+      </c>
+      <c r="H89">
+        <v>30.027734</v>
+      </c>
+      <c r="I89">
+        <v>74.36728100000001</v>
+      </c>
+      <c r="J89" t="s">
+        <v>110</v>
+      </c>
+      <c r="K89">
+        <v>397</v>
+      </c>
+      <c r="L89" t="s">
+        <v>111</v>
+      </c>
+      <c r="M89" t="s">
+        <v>21</v>
+      </c>
+      <c r="N89" t="s">
+        <v>24</v>
+      </c>
+      <c r="O89" t="s">
+        <v>29</v>
+      </c>
+      <c r="P89">
+        <v>30.0974593</v>
+      </c>
+      <c r="Q89">
+        <v>74.206666</v>
+      </c>
+      <c r="R89" t="s">
+        <v>112</v>
+      </c>
+      <c r="S89">
+        <v>36210</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19">
+      <c r="A90" t="s">
+        <v>19</v>
+      </c>
+      <c r="B90" t="s">
+        <v>20</v>
+      </c>
+      <c r="C90" t="s">
+        <v>21</v>
+      </c>
+      <c r="D90" t="s">
+        <v>24</v>
+      </c>
+      <c r="E90" t="s">
+        <v>29</v>
+      </c>
+      <c r="F90">
+        <v>537</v>
+      </c>
+      <c r="G90" t="s">
+        <v>85</v>
+      </c>
+      <c r="H90">
+        <v>29.951208</v>
+      </c>
+      <c r="I90">
+        <v>74.380385</v>
+      </c>
+      <c r="J90" t="s">
+        <v>110</v>
+      </c>
+      <c r="K90">
+        <v>394</v>
+      </c>
+      <c r="L90" t="s">
+        <v>111</v>
+      </c>
+      <c r="M90" t="s">
+        <v>21</v>
+      </c>
+      <c r="N90" t="s">
+        <v>24</v>
+      </c>
+      <c r="O90" t="s">
+        <v>29</v>
+      </c>
+      <c r="P90">
+        <v>30.08793156</v>
+      </c>
+      <c r="Q90">
+        <v>74.20908439</v>
+      </c>
+      <c r="R90" t="s">
+        <v>112</v>
+      </c>
+      <c r="S90">
+        <v>43549</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19">
+      <c r="A91" t="s">
+        <v>19</v>
+      </c>
+      <c r="B91" t="s">
+        <v>20</v>
+      </c>
+      <c r="C91" t="s">
+        <v>21</v>
+      </c>
+      <c r="D91" t="s">
+        <v>24</v>
+      </c>
+      <c r="E91" t="s">
+        <v>29</v>
+      </c>
+      <c r="F91">
+        <v>538</v>
+      </c>
+      <c r="G91" t="s">
+        <v>86</v>
+      </c>
+      <c r="H91">
+        <v>30.029455</v>
+      </c>
+      <c r="I91">
+        <v>74.077962</v>
+      </c>
+      <c r="J91" t="s">
+        <v>110</v>
+      </c>
+      <c r="K91">
+        <v>407</v>
+      </c>
+      <c r="L91" t="s">
+        <v>111</v>
+      </c>
+      <c r="M91" t="s">
+        <v>21</v>
+      </c>
+      <c r="N91" t="s">
+        <v>24</v>
+      </c>
+      <c r="O91" t="s">
+        <v>29</v>
+      </c>
+      <c r="P91">
+        <v>30.126927</v>
+      </c>
+      <c r="Q91">
+        <v>74.161942</v>
+      </c>
+      <c r="R91" t="s">
+        <v>112</v>
+      </c>
+      <c r="S91">
+        <v>57368</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19">
+      <c r="A92" t="s">
+        <v>19</v>
+      </c>
+      <c r="B92" t="s">
+        <v>20</v>
+      </c>
+      <c r="C92" t="s">
+        <v>21</v>
+      </c>
+      <c r="D92" t="s">
+        <v>24</v>
+      </c>
+      <c r="E92" t="s">
+        <v>29</v>
+      </c>
+      <c r="F92">
+        <v>540</v>
+      </c>
+      <c r="G92" t="s">
+        <v>87</v>
+      </c>
+      <c r="H92">
+        <v>29.983545</v>
+      </c>
+      <c r="I92">
+        <v>74.173574</v>
+      </c>
+      <c r="J92" t="s">
+        <v>110</v>
+      </c>
+      <c r="K92">
+        <v>407</v>
+      </c>
+      <c r="L92" t="s">
+        <v>111</v>
+      </c>
+      <c r="M92" t="s">
+        <v>21</v>
+      </c>
+      <c r="N92" t="s">
+        <v>24</v>
+      </c>
+      <c r="O92" t="s">
+        <v>29</v>
+      </c>
+      <c r="P92">
+        <v>30.126927</v>
+      </c>
+      <c r="Q92">
+        <v>74.161942</v>
+      </c>
+      <c r="R92" t="s">
+        <v>112</v>
+      </c>
+      <c r="S92">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19">
+      <c r="A93" t="s">
+        <v>19</v>
+      </c>
+      <c r="B93" t="s">
+        <v>20</v>
+      </c>
+      <c r="C93" t="s">
+        <v>21</v>
+      </c>
+      <c r="D93" t="s">
+        <v>24</v>
+      </c>
+      <c r="E93" t="s">
+        <v>29</v>
+      </c>
+      <c r="F93">
+        <v>541</v>
+      </c>
+      <c r="G93" t="s">
+        <v>88</v>
+      </c>
+      <c r="H93">
+        <v>30.254422</v>
+      </c>
+      <c r="I93">
+        <v>74.126414</v>
+      </c>
+      <c r="J93" t="s">
+        <v>110</v>
+      </c>
+      <c r="K93">
+        <v>400</v>
+      </c>
+      <c r="L93" t="s">
+        <v>111</v>
+      </c>
+      <c r="M93" t="s">
+        <v>21</v>
+      </c>
+      <c r="N93" t="s">
+        <v>24</v>
+      </c>
+      <c r="O93" t="s">
+        <v>29</v>
+      </c>
+      <c r="P93">
+        <v>30.15809938</v>
+      </c>
+      <c r="Q93">
+        <v>74.16401603</v>
+      </c>
+      <c r="R93" t="s">
+        <v>112</v>
+      </c>
+      <c r="S93">
+        <v>29195</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19">
+      <c r="A94" t="s">
+        <v>19</v>
+      </c>
+      <c r="B94" t="s">
+        <v>20</v>
+      </c>
+      <c r="C94" t="s">
+        <v>21</v>
+      </c>
+      <c r="D94" t="s">
+        <v>24</v>
+      </c>
+      <c r="E94" t="s">
+        <v>29</v>
+      </c>
+      <c r="F94">
+        <v>542</v>
+      </c>
+      <c r="G94" t="s">
+        <v>89</v>
+      </c>
+      <c r="H94">
+        <v>30.247905</v>
+      </c>
+      <c r="I94">
+        <v>74.129536</v>
+      </c>
+      <c r="J94" t="s">
+        <v>110</v>
+      </c>
+      <c r="K94">
+        <v>400</v>
+      </c>
+      <c r="L94" t="s">
+        <v>111</v>
+      </c>
+      <c r="M94" t="s">
+        <v>21</v>
+      </c>
+      <c r="N94" t="s">
+        <v>24</v>
+      </c>
+      <c r="O94" t="s">
+        <v>29</v>
+      </c>
+      <c r="P94">
+        <v>30.15809938</v>
+      </c>
+      <c r="Q94">
+        <v>74.16401603</v>
+      </c>
+      <c r="R94" t="s">
+        <v>112</v>
+      </c>
+      <c r="S94">
+        <v>26795</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19">
+      <c r="A95" t="s">
+        <v>19</v>
+      </c>
+      <c r="B95" t="s">
+        <v>20</v>
+      </c>
+      <c r="C95" t="s">
+        <v>21</v>
+      </c>
+      <c r="D95" t="s">
+        <v>24</v>
+      </c>
+      <c r="E95" t="s">
+        <v>29</v>
+      </c>
+      <c r="F95">
+        <v>543</v>
+      </c>
+      <c r="G95" t="s">
+        <v>90</v>
+      </c>
+      <c r="H95">
+        <v>30.25374</v>
+      </c>
+      <c r="I95">
+        <v>74.122122</v>
+      </c>
+      <c r="J95" t="s">
+        <v>110</v>
+      </c>
+      <c r="K95">
+        <v>400</v>
+      </c>
+      <c r="L95" t="s">
+        <v>111</v>
+      </c>
+      <c r="M95" t="s">
+        <v>21</v>
+      </c>
+      <c r="N95" t="s">
+        <v>24</v>
+      </c>
+      <c r="O95" t="s">
+        <v>29</v>
+      </c>
+      <c r="P95">
+        <v>30.15809938</v>
+      </c>
+      <c r="Q95">
+        <v>74.16401603</v>
+      </c>
+      <c r="R95" t="s">
+        <v>112</v>
+      </c>
+      <c r="S95">
+        <v>7950</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19">
+      <c r="A96" t="s">
+        <v>19</v>
+      </c>
+      <c r="B96" t="s">
+        <v>20</v>
+      </c>
+      <c r="C96" t="s">
+        <v>21</v>
+      </c>
+      <c r="D96" t="s">
+        <v>24</v>
+      </c>
+      <c r="E96" t="s">
+        <v>29</v>
+      </c>
+      <c r="F96">
+        <v>545</v>
+      </c>
+      <c r="G96" t="s">
+        <v>91</v>
+      </c>
+      <c r="H96">
+        <v>29.975306</v>
+      </c>
+      <c r="I96">
+        <v>74.164011</v>
+      </c>
+      <c r="J96" t="s">
+        <v>110</v>
+      </c>
+      <c r="K96">
+        <v>407</v>
+      </c>
+      <c r="L96" t="s">
+        <v>111</v>
+      </c>
+      <c r="M96" t="s">
+        <v>21</v>
+      </c>
+      <c r="N96" t="s">
+        <v>24</v>
+      </c>
+      <c r="O96" t="s">
+        <v>29</v>
+      </c>
+      <c r="P96">
+        <v>30.126927</v>
+      </c>
+      <c r="Q96">
+        <v>74.161942</v>
+      </c>
+      <c r="R96" t="s">
+        <v>112</v>
+      </c>
+      <c r="S96">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19">
+      <c r="A97" t="s">
+        <v>19</v>
+      </c>
+      <c r="B97" t="s">
+        <v>20</v>
+      </c>
+      <c r="C97" t="s">
+        <v>21</v>
+      </c>
+      <c r="D97" t="s">
+        <v>24</v>
+      </c>
+      <c r="E97" t="s">
+        <v>29</v>
+      </c>
+      <c r="F97">
+        <v>546</v>
+      </c>
+      <c r="G97" t="s">
+        <v>92</v>
+      </c>
+      <c r="H97">
+        <v>30.144184</v>
+      </c>
+      <c r="I97">
+        <v>74.122771</v>
+      </c>
+      <c r="J97" t="s">
+        <v>110</v>
+      </c>
+      <c r="K97">
+        <v>407</v>
+      </c>
+      <c r="L97" t="s">
+        <v>111</v>
+      </c>
+      <c r="M97" t="s">
+        <v>21</v>
+      </c>
+      <c r="N97" t="s">
+        <v>24</v>
+      </c>
+      <c r="O97" t="s">
+        <v>29</v>
+      </c>
+      <c r="P97">
+        <v>30.126927</v>
+      </c>
+      <c r="Q97">
+        <v>74.161942</v>
+      </c>
+      <c r="R97" t="s">
+        <v>112</v>
+      </c>
+      <c r="S97">
+        <v>12630.5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19">
+      <c r="A98" t="s">
+        <v>19</v>
+      </c>
+      <c r="B98" t="s">
+        <v>20</v>
+      </c>
+      <c r="C98" t="s">
+        <v>21</v>
+      </c>
+      <c r="D98" t="s">
+        <v>24</v>
+      </c>
+      <c r="E98" t="s">
+        <v>29</v>
+      </c>
+      <c r="F98">
+        <v>547</v>
+      </c>
+      <c r="G98" t="s">
+        <v>93</v>
+      </c>
+      <c r="H98">
+        <v>30.161715</v>
+      </c>
+      <c r="I98">
+        <v>73.987483</v>
+      </c>
+      <c r="J98" t="s">
+        <v>110</v>
+      </c>
+      <c r="K98">
+        <v>407</v>
+      </c>
+      <c r="L98" t="s">
+        <v>111</v>
+      </c>
+      <c r="M98" t="s">
+        <v>21</v>
+      </c>
+      <c r="N98" t="s">
+        <v>24</v>
+      </c>
+      <c r="O98" t="s">
+        <v>29</v>
+      </c>
+      <c r="P98">
+        <v>30.126927</v>
+      </c>
+      <c r="Q98">
+        <v>74.161942</v>
+      </c>
+      <c r="R98" t="s">
+        <v>112</v>
+      </c>
+      <c r="S98">
+        <v>13803</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19">
+      <c r="A99" t="s">
+        <v>19</v>
+      </c>
+      <c r="B99" t="s">
+        <v>20</v>
+      </c>
+      <c r="C99" t="s">
+        <v>21</v>
+      </c>
+      <c r="D99" t="s">
+        <v>24</v>
+      </c>
+      <c r="E99" t="s">
+        <v>29</v>
+      </c>
+      <c r="F99">
+        <v>548</v>
+      </c>
+      <c r="G99" t="s">
+        <v>94</v>
+      </c>
+      <c r="H99">
+        <v>30.21135</v>
+      </c>
+      <c r="I99">
+        <v>74.02397999999999</v>
+      </c>
+      <c r="J99" t="s">
+        <v>110</v>
+      </c>
+      <c r="K99">
+        <v>400</v>
+      </c>
+      <c r="L99" t="s">
+        <v>111</v>
+      </c>
+      <c r="M99" t="s">
+        <v>21</v>
+      </c>
+      <c r="N99" t="s">
+        <v>24</v>
+      </c>
+      <c r="O99" t="s">
+        <v>29</v>
+      </c>
+      <c r="P99">
+        <v>30.15809938</v>
+      </c>
+      <c r="Q99">
+        <v>74.16401603</v>
+      </c>
+      <c r="R99" t="s">
+        <v>112</v>
+      </c>
+      <c r="S99">
+        <v>9145</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19">
+      <c r="A100" t="s">
+        <v>19</v>
+      </c>
+      <c r="B100" t="s">
+        <v>20</v>
+      </c>
+      <c r="C100" t="s">
+        <v>21</v>
+      </c>
+      <c r="D100" t="s">
+        <v>24</v>
+      </c>
+      <c r="E100" t="s">
+        <v>29</v>
+      </c>
+      <c r="F100">
+        <v>549</v>
+      </c>
+      <c r="G100" t="s">
+        <v>95</v>
+      </c>
+      <c r="H100">
+        <v>30.296726</v>
+      </c>
+      <c r="I100">
+        <v>74.263169</v>
+      </c>
+      <c r="J100" t="s">
+        <v>110</v>
+      </c>
+      <c r="K100">
+        <v>401</v>
+      </c>
+      <c r="L100" t="s">
+        <v>111</v>
+      </c>
+      <c r="M100" t="s">
+        <v>21</v>
+      </c>
+      <c r="N100" t="s">
+        <v>24</v>
+      </c>
+      <c r="O100" t="s">
+        <v>29</v>
+      </c>
+      <c r="P100">
+        <v>30.17081207</v>
+      </c>
+      <c r="Q100">
+        <v>74.18179719</v>
+      </c>
+      <c r="R100" t="s">
+        <v>112</v>
+      </c>
+      <c r="S100">
+        <v>17622.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19">
+      <c r="A101" t="s">
+        <v>19</v>
+      </c>
+      <c r="B101" t="s">
+        <v>20</v>
+      </c>
+      <c r="C101" t="s">
+        <v>21</v>
+      </c>
+      <c r="D101" t="s">
+        <v>24</v>
+      </c>
+      <c r="E101" t="s">
+        <v>29</v>
+      </c>
+      <c r="F101">
+        <v>550</v>
+      </c>
+      <c r="G101" t="s">
+        <v>96</v>
+      </c>
+      <c r="H101">
+        <v>30.285139</v>
+      </c>
+      <c r="I101">
+        <v>74.172681</v>
+      </c>
+      <c r="J101" t="s">
+        <v>110</v>
+      </c>
+      <c r="K101">
+        <v>402</v>
+      </c>
+      <c r="L101" t="s">
+        <v>111</v>
+      </c>
+      <c r="M101" t="s">
+        <v>21</v>
+      </c>
+      <c r="N101" t="s">
+        <v>24</v>
+      </c>
+      <c r="O101" t="s">
+        <v>29</v>
+      </c>
+      <c r="P101">
+        <v>30.17767461</v>
+      </c>
+      <c r="Q101">
+        <v>74.17723581</v>
+      </c>
+      <c r="R101" t="s">
+        <v>112</v>
+      </c>
+      <c r="S101">
+        <v>42685</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19">
+      <c r="A102" t="s">
+        <v>19</v>
+      </c>
+      <c r="B102" t="s">
+        <v>20</v>
+      </c>
+      <c r="C102" t="s">
+        <v>21</v>
+      </c>
+      <c r="D102" t="s">
+        <v>24</v>
+      </c>
+      <c r="E102" t="s">
+        <v>29</v>
+      </c>
+      <c r="F102">
+        <v>551</v>
+      </c>
+      <c r="G102" t="s">
+        <v>97</v>
+      </c>
+      <c r="H102">
+        <v>30.260814</v>
+      </c>
+      <c r="I102">
+        <v>74.269329</v>
+      </c>
+      <c r="J102" t="s">
+        <v>110</v>
+      </c>
+      <c r="K102">
+        <v>401</v>
+      </c>
+      <c r="L102" t="s">
+        <v>111</v>
+      </c>
+      <c r="M102" t="s">
+        <v>21</v>
+      </c>
+      <c r="N102" t="s">
+        <v>24</v>
+      </c>
+      <c r="O102" t="s">
+        <v>29</v>
+      </c>
+      <c r="P102">
+        <v>30.17081207</v>
+      </c>
+      <c r="Q102">
+        <v>74.18179719</v>
+      </c>
+      <c r="R102" t="s">
+        <v>112</v>
+      </c>
+      <c r="S102">
+        <v>56502.5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19">
+      <c r="A103" t="s">
+        <v>19</v>
+      </c>
+      <c r="B103" t="s">
+        <v>20</v>
+      </c>
+      <c r="C103" t="s">
+        <v>21</v>
+      </c>
+      <c r="D103" t="s">
+        <v>24</v>
+      </c>
+      <c r="E103" t="s">
+        <v>29</v>
+      </c>
+      <c r="F103">
+        <v>552</v>
+      </c>
+      <c r="G103" t="s">
+        <v>98</v>
+      </c>
+      <c r="H103">
+        <v>30.290503</v>
+      </c>
+      <c r="I103">
+        <v>74.220803</v>
+      </c>
+      <c r="J103" t="s">
+        <v>110</v>
+      </c>
+      <c r="K103">
+        <v>401</v>
+      </c>
+      <c r="L103" t="s">
+        <v>111</v>
+      </c>
+      <c r="M103" t="s">
+        <v>21</v>
+      </c>
+      <c r="N103" t="s">
+        <v>24</v>
+      </c>
+      <c r="O103" t="s">
+        <v>29</v>
+      </c>
+      <c r="P103">
+        <v>30.17081207</v>
+      </c>
+      <c r="Q103">
+        <v>74.18179719</v>
+      </c>
+      <c r="R103" t="s">
+        <v>112</v>
+      </c>
+      <c r="S103">
+        <v>43110</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19">
+      <c r="A104" t="s">
+        <v>19</v>
+      </c>
+      <c r="B104" t="s">
+        <v>20</v>
+      </c>
+      <c r="C104" t="s">
+        <v>21</v>
+      </c>
+      <c r="D104" t="s">
+        <v>25</v>
+      </c>
+      <c r="E104" t="s">
+        <v>30</v>
+      </c>
+      <c r="F104">
+        <v>1046</v>
+      </c>
+      <c r="G104" t="s">
+        <v>99</v>
+      </c>
+      <c r="H104">
+        <v>31.425406</v>
+      </c>
+      <c r="I104">
+        <v>75.719528</v>
+      </c>
+      <c r="J104" t="s">
+        <v>110</v>
+      </c>
+      <c r="K104">
+        <v>625</v>
+      </c>
+      <c r="L104" t="s">
+        <v>111</v>
+      </c>
+      <c r="M104" t="s">
+        <v>21</v>
+      </c>
+      <c r="N104" t="s">
+        <v>25</v>
+      </c>
+      <c r="O104" t="s">
+        <v>30</v>
+      </c>
+      <c r="P104">
+        <v>31.408658</v>
+      </c>
+      <c r="Q104">
+        <v>75.685958</v>
+      </c>
+      <c r="R104" t="s">
+        <v>112</v>
+      </c>
+      <c r="S104">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19">
+      <c r="A105" t="s">
+        <v>19</v>
+      </c>
+      <c r="B105" t="s">
+        <v>20</v>
+      </c>
+      <c r="C105" t="s">
+        <v>21</v>
+      </c>
+      <c r="D105" t="s">
+        <v>22</v>
+      </c>
+      <c r="E105" t="s">
+        <v>31</v>
+      </c>
+      <c r="F105">
+        <v>54</v>
+      </c>
+      <c r="G105" t="s">
+        <v>100</v>
+      </c>
+      <c r="H105">
+        <v>31.6139708</v>
+      </c>
+      <c r="I105">
+        <v>75.3268413</v>
+      </c>
+      <c r="J105" t="s">
+        <v>110</v>
+      </c>
+      <c r="K105">
+        <v>21</v>
+      </c>
+      <c r="L105" t="s">
+        <v>111</v>
+      </c>
+      <c r="M105" t="s">
+        <v>21</v>
+      </c>
+      <c r="N105" t="s">
+        <v>22</v>
+      </c>
+      <c r="O105" t="s">
+        <v>31</v>
+      </c>
+      <c r="P105">
+        <v>31.6647538</v>
+      </c>
+      <c r="Q105">
+        <v>75.234335</v>
+      </c>
+      <c r="R105" t="s">
+        <v>112</v>
+      </c>
+      <c r="S105">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19">
+      <c r="A106" t="s">
+        <v>19</v>
+      </c>
+      <c r="B106" t="s">
+        <v>20</v>
+      </c>
+      <c r="C106" t="s">
+        <v>21</v>
+      </c>
+      <c r="D106" t="s">
+        <v>22</v>
+      </c>
+      <c r="E106" t="s">
+        <v>31</v>
+      </c>
+      <c r="F106">
+        <v>54</v>
+      </c>
+      <c r="G106" t="s">
+        <v>100</v>
+      </c>
+      <c r="H106">
+        <v>31.6139708</v>
+      </c>
+      <c r="I106">
+        <v>75.3268413</v>
+      </c>
+      <c r="J106" t="s">
+        <v>110</v>
+      </c>
+      <c r="K106">
+        <v>29</v>
+      </c>
+      <c r="L106" t="s">
+        <v>111</v>
+      </c>
+      <c r="M106" t="s">
+        <v>21</v>
+      </c>
+      <c r="N106" t="s">
+        <v>22</v>
+      </c>
+      <c r="O106" t="s">
+        <v>31</v>
+      </c>
+      <c r="P106">
+        <v>31.561626</v>
+      </c>
+      <c r="Q106">
+        <v>75.140022</v>
+      </c>
+      <c r="R106" t="s">
+        <v>112</v>
+      </c>
+      <c r="S106">
+        <v>31832.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19">
+      <c r="A107" t="s">
+        <v>19</v>
+      </c>
+      <c r="B107" t="s">
+        <v>20</v>
+      </c>
+      <c r="C107" t="s">
+        <v>21</v>
+      </c>
+      <c r="D107" t="s">
+        <v>22</v>
+      </c>
+      <c r="E107" t="s">
+        <v>31</v>
+      </c>
+      <c r="F107">
+        <v>54</v>
+      </c>
+      <c r="G107" t="s">
+        <v>100</v>
+      </c>
+      <c r="H107">
+        <v>31.6139708</v>
+      </c>
+      <c r="I107">
+        <v>75.3268413</v>
+      </c>
+      <c r="J107" t="s">
+        <v>110</v>
+      </c>
+      <c r="K107">
+        <v>37</v>
+      </c>
+      <c r="L107" t="s">
+        <v>111</v>
+      </c>
+      <c r="M107" t="s">
+        <v>21</v>
+      </c>
+      <c r="N107" t="s">
+        <v>22</v>
+      </c>
+      <c r="O107" t="s">
+        <v>31</v>
+      </c>
+      <c r="P107">
+        <v>31.5547</v>
+      </c>
+      <c r="Q107">
+        <v>75.18429</v>
+      </c>
+      <c r="R107" t="s">
+        <v>112</v>
+      </c>
+      <c r="S107">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19">
+      <c r="A108" t="s">
+        <v>19</v>
+      </c>
+      <c r="B108" t="s">
+        <v>20</v>
+      </c>
+      <c r="C108" t="s">
+        <v>21</v>
+      </c>
+      <c r="D108" t="s">
+        <v>22</v>
+      </c>
+      <c r="E108" t="s">
+        <v>31</v>
+      </c>
+      <c r="F108">
+        <v>54</v>
+      </c>
+      <c r="G108" t="s">
+        <v>100</v>
+      </c>
+      <c r="H108">
+        <v>31.6139708</v>
+      </c>
+      <c r="I108">
+        <v>75.3268413</v>
+      </c>
+      <c r="J108" t="s">
+        <v>110</v>
+      </c>
+      <c r="K108">
+        <v>44</v>
+      </c>
+      <c r="L108" t="s">
+        <v>111</v>
+      </c>
+      <c r="M108" t="s">
+        <v>21</v>
+      </c>
+      <c r="N108" t="s">
+        <v>22</v>
+      </c>
+      <c r="O108" t="s">
+        <v>31</v>
+      </c>
+      <c r="P108">
+        <v>31.51572</v>
+      </c>
+      <c r="Q108">
+        <v>75.28874</v>
+      </c>
+      <c r="R108" t="s">
+        <v>112</v>
+      </c>
+      <c r="S108">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19">
+      <c r="A109" t="s">
+        <v>19</v>
+      </c>
+      <c r="B109" t="s">
+        <v>20</v>
+      </c>
+      <c r="C109" t="s">
+        <v>21</v>
+      </c>
+      <c r="D109" t="s">
+        <v>22</v>
+      </c>
+      <c r="E109" t="s">
+        <v>31</v>
+      </c>
+      <c r="F109">
+        <v>55</v>
+      </c>
+      <c r="G109" t="s">
+        <v>101</v>
+      </c>
+      <c r="H109">
+        <v>31.5988078</v>
+      </c>
+      <c r="I109">
+        <v>75.2009982</v>
+      </c>
+      <c r="J109" t="s">
+        <v>110</v>
+      </c>
+      <c r="K109">
+        <v>29</v>
+      </c>
+      <c r="L109" t="s">
+        <v>111</v>
+      </c>
+      <c r="M109" t="s">
+        <v>21</v>
+      </c>
+      <c r="N109" t="s">
+        <v>22</v>
+      </c>
+      <c r="O109" t="s">
+        <v>31</v>
+      </c>
+      <c r="P109">
+        <v>31.561626</v>
+      </c>
+      <c r="Q109">
+        <v>75.140022</v>
+      </c>
+      <c r="R109" t="s">
+        <v>112</v>
+      </c>
+      <c r="S109">
+        <v>17174.5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19">
+      <c r="A110" t="s">
+        <v>19</v>
+      </c>
+      <c r="B110" t="s">
+        <v>20</v>
+      </c>
+      <c r="C110" t="s">
+        <v>21</v>
+      </c>
+      <c r="D110" t="s">
+        <v>22</v>
+      </c>
+      <c r="E110" t="s">
+        <v>31</v>
+      </c>
+      <c r="F110">
+        <v>56</v>
+      </c>
+      <c r="G110" t="s">
+        <v>102</v>
+      </c>
+      <c r="H110">
+        <v>31.5495084</v>
+      </c>
+      <c r="I110">
+        <v>75.1740551</v>
+      </c>
+      <c r="J110" t="s">
+        <v>110</v>
+      </c>
+      <c r="K110">
+        <v>29</v>
+      </c>
+      <c r="L110" t="s">
+        <v>111</v>
+      </c>
+      <c r="M110" t="s">
+        <v>21</v>
+      </c>
+      <c r="N110" t="s">
+        <v>22</v>
+      </c>
+      <c r="O110" t="s">
+        <v>31</v>
+      </c>
+      <c r="P110">
+        <v>31.561626</v>
+      </c>
+      <c r="Q110">
+        <v>75.140022</v>
+      </c>
+      <c r="R110" t="s">
+        <v>112</v>
+      </c>
+      <c r="S110">
+        <v>25993</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19">
+      <c r="A111" t="s">
+        <v>19</v>
+      </c>
+      <c r="B111" t="s">
+        <v>20</v>
+      </c>
+      <c r="C111" t="s">
+        <v>21</v>
+      </c>
+      <c r="D111" t="s">
+        <v>22</v>
+      </c>
+      <c r="E111" t="s">
+        <v>31</v>
+      </c>
+      <c r="F111">
+        <v>57</v>
+      </c>
+      <c r="G111" t="s">
+        <v>103</v>
+      </c>
+      <c r="H111">
+        <v>31.5394842</v>
+      </c>
+      <c r="I111">
+        <v>75.24014649999999</v>
+      </c>
+      <c r="J111" t="s">
+        <v>110</v>
+      </c>
+      <c r="K111">
+        <v>19</v>
+      </c>
+      <c r="L111" t="s">
+        <v>111</v>
+      </c>
+      <c r="M111" t="s">
+        <v>21</v>
+      </c>
+      <c r="N111" t="s">
+        <v>22</v>
+      </c>
+      <c r="O111" t="s">
+        <v>31</v>
+      </c>
+      <c r="P111">
+        <v>31.543266</v>
+      </c>
+      <c r="Q111">
+        <v>75.21952</v>
+      </c>
+      <c r="R111" t="s">
+        <v>112</v>
+      </c>
+      <c r="S111">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19">
+      <c r="A112" t="s">
+        <v>19</v>
+      </c>
+      <c r="B112" t="s">
+        <v>20</v>
+      </c>
+      <c r="C112" t="s">
+        <v>21</v>
+      </c>
+      <c r="D112" t="s">
+        <v>22</v>
+      </c>
+      <c r="E112" t="s">
+        <v>31</v>
+      </c>
+      <c r="F112">
+        <v>57</v>
+      </c>
+      <c r="G112" t="s">
+        <v>103</v>
+      </c>
+      <c r="H112">
+        <v>31.5394842</v>
+      </c>
+      <c r="I112">
+        <v>75.24014649999999</v>
+      </c>
+      <c r="J112" t="s">
+        <v>110</v>
+      </c>
+      <c r="K112">
+        <v>20</v>
+      </c>
+      <c r="L112" t="s">
+        <v>111</v>
+      </c>
+      <c r="M112" t="s">
+        <v>21</v>
+      </c>
+      <c r="N112" t="s">
+        <v>22</v>
+      </c>
+      <c r="O112" t="s">
+        <v>31</v>
+      </c>
+      <c r="P112">
+        <v>31.543724</v>
+      </c>
+      <c r="Q112">
+        <v>75.21528600000001</v>
+      </c>
+      <c r="R112" t="s">
+        <v>112</v>
+      </c>
+      <c r="S112">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19">
+      <c r="A113" t="s">
+        <v>19</v>
+      </c>
+      <c r="B113" t="s">
+        <v>20</v>
+      </c>
+      <c r="C113" t="s">
+        <v>21</v>
+      </c>
+      <c r="D113" t="s">
+        <v>22</v>
+      </c>
+      <c r="E113" t="s">
+        <v>31</v>
+      </c>
+      <c r="F113">
+        <v>57</v>
+      </c>
+      <c r="G113" t="s">
+        <v>103</v>
+      </c>
+      <c r="H113">
+        <v>31.5394842</v>
+      </c>
+      <c r="I113">
+        <v>75.24014649999999</v>
+      </c>
+      <c r="J113" t="s">
+        <v>110</v>
+      </c>
+      <c r="K113">
         <v>27</v>
       </c>
-      <c r="P84">
+      <c r="L113" t="s">
+        <v>111</v>
+      </c>
+      <c r="M113" t="s">
+        <v>21</v>
+      </c>
+      <c r="N113" t="s">
+        <v>22</v>
+      </c>
+      <c r="O113" t="s">
+        <v>31</v>
+      </c>
+      <c r="P113">
+        <v>31.539066</v>
+      </c>
+      <c r="Q113">
+        <v>75.244698</v>
+      </c>
+      <c r="R113" t="s">
+        <v>112</v>
+      </c>
+      <c r="S113">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19">
+      <c r="A114" t="s">
+        <v>19</v>
+      </c>
+      <c r="B114" t="s">
+        <v>20</v>
+      </c>
+      <c r="C114" t="s">
+        <v>21</v>
+      </c>
+      <c r="D114" t="s">
+        <v>22</v>
+      </c>
+      <c r="E114" t="s">
+        <v>31</v>
+      </c>
+      <c r="F114">
+        <v>57</v>
+      </c>
+      <c r="G114" t="s">
+        <v>103</v>
+      </c>
+      <c r="H114">
+        <v>31.5394842</v>
+      </c>
+      <c r="I114">
+        <v>75.24014649999999</v>
+      </c>
+      <c r="J114" t="s">
+        <v>110</v>
+      </c>
+      <c r="K114">
+        <v>28</v>
+      </c>
+      <c r="L114" t="s">
+        <v>111</v>
+      </c>
+      <c r="M114" t="s">
+        <v>21</v>
+      </c>
+      <c r="N114" t="s">
+        <v>22</v>
+      </c>
+      <c r="O114" t="s">
+        <v>31</v>
+      </c>
+      <c r="P114">
+        <v>31.539066</v>
+      </c>
+      <c r="Q114">
+        <v>75.244698</v>
+      </c>
+      <c r="R114" t="s">
+        <v>112</v>
+      </c>
+      <c r="S114">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19">
+      <c r="A115" t="s">
+        <v>19</v>
+      </c>
+      <c r="B115" t="s">
+        <v>20</v>
+      </c>
+      <c r="C115" t="s">
+        <v>21</v>
+      </c>
+      <c r="D115" t="s">
+        <v>22</v>
+      </c>
+      <c r="E115" t="s">
+        <v>31</v>
+      </c>
+      <c r="F115">
+        <v>57</v>
+      </c>
+      <c r="G115" t="s">
+        <v>103</v>
+      </c>
+      <c r="H115">
+        <v>31.5394842</v>
+      </c>
+      <c r="I115">
+        <v>75.24014649999999</v>
+      </c>
+      <c r="J115" t="s">
+        <v>110</v>
+      </c>
+      <c r="K115">
+        <v>36</v>
+      </c>
+      <c r="L115" t="s">
+        <v>111</v>
+      </c>
+      <c r="M115" t="s">
+        <v>21</v>
+      </c>
+      <c r="N115" t="s">
+        <v>22</v>
+      </c>
+      <c r="O115" t="s">
+        <v>31</v>
+      </c>
+      <c r="P115">
+        <v>31.5547</v>
+      </c>
+      <c r="Q115">
+        <v>75.18429</v>
+      </c>
+      <c r="R115" t="s">
+        <v>112</v>
+      </c>
+      <c r="S115">
+        <v>17870</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19">
+      <c r="A116" t="s">
+        <v>19</v>
+      </c>
+      <c r="B116" t="s">
+        <v>20</v>
+      </c>
+      <c r="C116" t="s">
+        <v>21</v>
+      </c>
+      <c r="D116" t="s">
+        <v>22</v>
+      </c>
+      <c r="E116" t="s">
+        <v>31</v>
+      </c>
+      <c r="F116">
+        <v>57</v>
+      </c>
+      <c r="G116" t="s">
+        <v>103</v>
+      </c>
+      <c r="H116">
+        <v>31.5394842</v>
+      </c>
+      <c r="I116">
+        <v>75.24014649999999</v>
+      </c>
+      <c r="J116" t="s">
+        <v>110</v>
+      </c>
+      <c r="K116">
+        <v>37</v>
+      </c>
+      <c r="L116" t="s">
+        <v>111</v>
+      </c>
+      <c r="M116" t="s">
+        <v>21</v>
+      </c>
+      <c r="N116" t="s">
+        <v>22</v>
+      </c>
+      <c r="O116" t="s">
+        <v>31</v>
+      </c>
+      <c r="P116">
+        <v>31.5547</v>
+      </c>
+      <c r="Q116">
+        <v>75.18429</v>
+      </c>
+      <c r="R116" t="s">
+        <v>112</v>
+      </c>
+      <c r="S116">
+        <v>38457</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19">
+      <c r="A117" t="s">
+        <v>19</v>
+      </c>
+      <c r="B117" t="s">
+        <v>20</v>
+      </c>
+      <c r="C117" t="s">
+        <v>21</v>
+      </c>
+      <c r="D117" t="s">
+        <v>22</v>
+      </c>
+      <c r="E117" t="s">
+        <v>31</v>
+      </c>
+      <c r="F117">
+        <v>57</v>
+      </c>
+      <c r="G117" t="s">
+        <v>103</v>
+      </c>
+      <c r="H117">
+        <v>31.5394842</v>
+      </c>
+      <c r="I117">
+        <v>75.24014649999999</v>
+      </c>
+      <c r="J117" t="s">
+        <v>110</v>
+      </c>
+      <c r="K117">
+        <v>43</v>
+      </c>
+      <c r="L117" t="s">
+        <v>111</v>
+      </c>
+      <c r="M117" t="s">
+        <v>21</v>
+      </c>
+      <c r="N117" t="s">
+        <v>22</v>
+      </c>
+      <c r="O117" t="s">
+        <v>31</v>
+      </c>
+      <c r="P117">
+        <v>31.53422</v>
+      </c>
+      <c r="Q117">
+        <v>75.2328</v>
+      </c>
+      <c r="R117" t="s">
+        <v>112</v>
+      </c>
+      <c r="S117">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19">
+      <c r="A118" t="s">
+        <v>19</v>
+      </c>
+      <c r="B118" t="s">
+        <v>20</v>
+      </c>
+      <c r="C118" t="s">
+        <v>21</v>
+      </c>
+      <c r="D118" t="s">
+        <v>22</v>
+      </c>
+      <c r="E118" t="s">
+        <v>31</v>
+      </c>
+      <c r="F118">
+        <v>58</v>
+      </c>
+      <c r="G118" t="s">
+        <v>104</v>
+      </c>
+      <c r="H118">
+        <v>31.57488036</v>
+      </c>
+      <c r="I118">
+        <v>75.28466821000001</v>
+      </c>
+      <c r="J118" t="s">
+        <v>110</v>
+      </c>
+      <c r="K118">
+        <v>17</v>
+      </c>
+      <c r="L118" t="s">
+        <v>111</v>
+      </c>
+      <c r="M118" t="s">
+        <v>21</v>
+      </c>
+      <c r="N118" t="s">
+        <v>22</v>
+      </c>
+      <c r="O118" t="s">
+        <v>31</v>
+      </c>
+      <c r="P118">
+        <v>31.52691932</v>
+      </c>
+      <c r="Q118">
+        <v>75.26848901</v>
+      </c>
+      <c r="R118" t="s">
+        <v>112</v>
+      </c>
+      <c r="S118">
+        <v>17500</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19">
+      <c r="A119" t="s">
+        <v>19</v>
+      </c>
+      <c r="B119" t="s">
+        <v>20</v>
+      </c>
+      <c r="C119" t="s">
+        <v>21</v>
+      </c>
+      <c r="D119" t="s">
+        <v>22</v>
+      </c>
+      <c r="E119" t="s">
+        <v>31</v>
+      </c>
+      <c r="F119">
+        <v>58</v>
+      </c>
+      <c r="G119" t="s">
+        <v>104</v>
+      </c>
+      <c r="H119">
+        <v>31.57488036</v>
+      </c>
+      <c r="I119">
+        <v>75.28466821000001</v>
+      </c>
+      <c r="J119" t="s">
+        <v>110</v>
+      </c>
+      <c r="K119">
+        <v>18</v>
+      </c>
+      <c r="L119" t="s">
+        <v>111</v>
+      </c>
+      <c r="M119" t="s">
+        <v>21</v>
+      </c>
+      <c r="N119" t="s">
+        <v>22</v>
+      </c>
+      <c r="O119" t="s">
+        <v>31</v>
+      </c>
+      <c r="P119">
+        <v>31.52693009</v>
+      </c>
+      <c r="Q119">
+        <v>75.26852979</v>
+      </c>
+      <c r="R119" t="s">
+        <v>112</v>
+      </c>
+      <c r="S119">
+        <v>17500</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19">
+      <c r="A120" t="s">
+        <v>19</v>
+      </c>
+      <c r="B120" t="s">
+        <v>20</v>
+      </c>
+      <c r="C120" t="s">
+        <v>21</v>
+      </c>
+      <c r="D120" t="s">
+        <v>22</v>
+      </c>
+      <c r="E120" t="s">
+        <v>31</v>
+      </c>
+      <c r="F120">
+        <v>58</v>
+      </c>
+      <c r="G120" t="s">
+        <v>104</v>
+      </c>
+      <c r="H120">
+        <v>31.57488036</v>
+      </c>
+      <c r="I120">
+        <v>75.28466821000001</v>
+      </c>
+      <c r="J120" t="s">
+        <v>110</v>
+      </c>
+      <c r="K120">
+        <v>35</v>
+      </c>
+      <c r="L120" t="s">
+        <v>111</v>
+      </c>
+      <c r="M120" t="s">
+        <v>21</v>
+      </c>
+      <c r="N120" t="s">
+        <v>22</v>
+      </c>
+      <c r="O120" t="s">
+        <v>31</v>
+      </c>
+      <c r="P120">
+        <v>31.55489</v>
+      </c>
+      <c r="Q120">
+        <v>75.18541999999999</v>
+      </c>
+      <c r="R120" t="s">
+        <v>112</v>
+      </c>
+      <c r="S120">
+        <v>7070</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19">
+      <c r="A121" t="s">
+        <v>19</v>
+      </c>
+      <c r="B121" t="s">
+        <v>20</v>
+      </c>
+      <c r="C121" t="s">
+        <v>21</v>
+      </c>
+      <c r="D121" t="s">
+        <v>22</v>
+      </c>
+      <c r="E121" t="s">
+        <v>31</v>
+      </c>
+      <c r="F121">
+        <v>58</v>
+      </c>
+      <c r="G121" t="s">
+        <v>104</v>
+      </c>
+      <c r="H121">
+        <v>31.57488036</v>
+      </c>
+      <c r="I121">
+        <v>75.28466821000001</v>
+      </c>
+      <c r="J121" t="s">
+        <v>110</v>
+      </c>
+      <c r="K121">
+        <v>37</v>
+      </c>
+      <c r="L121" t="s">
+        <v>111</v>
+      </c>
+      <c r="M121" t="s">
+        <v>21</v>
+      </c>
+      <c r="N121" t="s">
+        <v>22</v>
+      </c>
+      <c r="O121" t="s">
+        <v>31</v>
+      </c>
+      <c r="P121">
+        <v>31.5547</v>
+      </c>
+      <c r="Q121">
+        <v>75.18429</v>
+      </c>
+      <c r="R121" t="s">
+        <v>112</v>
+      </c>
+      <c r="S121">
+        <v>90831</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19">
+      <c r="A122" t="s">
+        <v>19</v>
+      </c>
+      <c r="B122" t="s">
+        <v>20</v>
+      </c>
+      <c r="C122" t="s">
+        <v>21</v>
+      </c>
+      <c r="D122" t="s">
+        <v>22</v>
+      </c>
+      <c r="E122" t="s">
+        <v>32</v>
+      </c>
+      <c r="F122">
+        <v>23</v>
+      </c>
+      <c r="G122" t="s">
+        <v>105</v>
+      </c>
+      <c r="H122">
+        <v>31.7398221</v>
+      </c>
+      <c r="I122">
+        <v>74.6072853</v>
+      </c>
+      <c r="J122" t="s">
+        <v>110</v>
+      </c>
+      <c r="K122">
+        <v>5</v>
+      </c>
+      <c r="L122" t="s">
+        <v>111</v>
+      </c>
+      <c r="M122" t="s">
+        <v>21</v>
+      </c>
+      <c r="N122" t="s">
+        <v>22</v>
+      </c>
+      <c r="O122" t="s">
+        <v>32</v>
+      </c>
+      <c r="P122">
+        <v>31.800077</v>
+      </c>
+      <c r="Q122">
+        <v>74.588493</v>
+      </c>
+      <c r="R122" t="s">
+        <v>112</v>
+      </c>
+      <c r="S122">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19">
+      <c r="A123" t="s">
+        <v>19</v>
+      </c>
+      <c r="B123" t="s">
+        <v>20</v>
+      </c>
+      <c r="C123" t="s">
+        <v>21</v>
+      </c>
+      <c r="D123" t="s">
+        <v>22</v>
+      </c>
+      <c r="E123" t="s">
+        <v>32</v>
+      </c>
+      <c r="F123">
+        <v>24</v>
+      </c>
+      <c r="G123" t="s">
+        <v>106</v>
+      </c>
+      <c r="H123">
+        <v>31.70149744</v>
+      </c>
+      <c r="I123">
+        <v>74.65969907</v>
+      </c>
+      <c r="J123" t="s">
+        <v>110</v>
+      </c>
+      <c r="K123">
+        <v>11</v>
+      </c>
+      <c r="L123" t="s">
+        <v>111</v>
+      </c>
+      <c r="M123" t="s">
+        <v>21</v>
+      </c>
+      <c r="N123" t="s">
+        <v>22</v>
+      </c>
+      <c r="O123" t="s">
+        <v>32</v>
+      </c>
+      <c r="P123">
+        <v>31.70219884</v>
+      </c>
+      <c r="Q123">
+        <v>74.68916134</v>
+      </c>
+      <c r="R123" t="s">
+        <v>112</v>
+      </c>
+      <c r="S123">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19">
+      <c r="A124" t="s">
+        <v>19</v>
+      </c>
+      <c r="B124" t="s">
+        <v>20</v>
+      </c>
+      <c r="C124" t="s">
+        <v>21</v>
+      </c>
+      <c r="D124" t="s">
+        <v>22</v>
+      </c>
+      <c r="E124" t="s">
+        <v>32</v>
+      </c>
+      <c r="F124">
+        <v>24</v>
+      </c>
+      <c r="G124" t="s">
+        <v>106</v>
+      </c>
+      <c r="H124">
+        <v>31.70149744</v>
+      </c>
+      <c r="I124">
+        <v>74.65969907</v>
+      </c>
+      <c r="J124" t="s">
+        <v>110</v>
+      </c>
+      <c r="K124">
+        <v>12</v>
+      </c>
+      <c r="L124" t="s">
+        <v>111</v>
+      </c>
+      <c r="M124" t="s">
+        <v>21</v>
+      </c>
+      <c r="N124" t="s">
+        <v>22</v>
+      </c>
+      <c r="O124" t="s">
+        <v>32</v>
+      </c>
+      <c r="P124">
+        <v>31.703294</v>
+      </c>
+      <c r="Q124">
+        <v>74.69096380000001</v>
+      </c>
+      <c r="R124" t="s">
+        <v>112</v>
+      </c>
+      <c r="S124">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19">
+      <c r="A125" t="s">
+        <v>19</v>
+      </c>
+      <c r="B125" t="s">
+        <v>20</v>
+      </c>
+      <c r="C125" t="s">
+        <v>21</v>
+      </c>
+      <c r="D125" t="s">
+        <v>22</v>
+      </c>
+      <c r="E125" t="s">
+        <v>33</v>
+      </c>
+      <c r="F125">
+        <v>36</v>
+      </c>
+      <c r="G125" t="s">
+        <v>107</v>
+      </c>
+      <c r="H125">
+        <v>31.5710787</v>
+      </c>
+      <c r="I125">
+        <v>75.0424861</v>
+      </c>
+      <c r="J125" t="s">
+        <v>110</v>
+      </c>
+      <c r="K125">
+        <v>13</v>
+      </c>
+      <c r="L125" t="s">
+        <v>111</v>
+      </c>
+      <c r="M125" t="s">
+        <v>21</v>
+      </c>
+      <c r="N125" t="s">
+        <v>22</v>
+      </c>
+      <c r="O125" t="s">
+        <v>33</v>
+      </c>
+      <c r="P125">
+        <v>31.56972149</v>
+      </c>
+      <c r="Q125">
+        <v>75.09414523</v>
+      </c>
+      <c r="R125" t="s">
+        <v>112</v>
+      </c>
+      <c r="S125">
+        <v>5511</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19">
+      <c r="A126" t="s">
+        <v>19</v>
+      </c>
+      <c r="B126" t="s">
+        <v>20</v>
+      </c>
+      <c r="C126" t="s">
+        <v>21</v>
+      </c>
+      <c r="D126" t="s">
+        <v>22</v>
+      </c>
+      <c r="E126" t="s">
+        <v>33</v>
+      </c>
+      <c r="F126">
+        <v>36</v>
+      </c>
+      <c r="G126" t="s">
+        <v>107</v>
+      </c>
+      <c r="H126">
+        <v>31.5710787</v>
+      </c>
+      <c r="I126">
+        <v>75.0424861</v>
+      </c>
+      <c r="J126" t="s">
+        <v>110</v>
+      </c>
+      <c r="K126">
+        <v>14</v>
+      </c>
+      <c r="L126" t="s">
+        <v>111</v>
+      </c>
+      <c r="M126" t="s">
+        <v>21</v>
+      </c>
+      <c r="N126" t="s">
+        <v>22</v>
+      </c>
+      <c r="O126" t="s">
+        <v>33</v>
+      </c>
+      <c r="P126">
         <v>31.45335</v>
       </c>
-      <c r="Q84">
+      <c r="Q126">
         <v>74.46541999999999</v>
       </c>
-      <c r="R84" t="s">
-        <v>87</v>
-      </c>
-      <c r="S84">
-        <v>150000</v>
+      <c r="R126" t="s">
+        <v>112</v>
+      </c>
+      <c r="S126">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19">
+      <c r="A127" t="s">
+        <v>19</v>
+      </c>
+      <c r="B127" t="s">
+        <v>20</v>
+      </c>
+      <c r="C127" t="s">
+        <v>21</v>
+      </c>
+      <c r="D127" t="s">
+        <v>22</v>
+      </c>
+      <c r="E127" t="s">
+        <v>33</v>
+      </c>
+      <c r="F127">
+        <v>36</v>
+      </c>
+      <c r="G127" t="s">
+        <v>107</v>
+      </c>
+      <c r="H127">
+        <v>31.5710787</v>
+      </c>
+      <c r="I127">
+        <v>75.0424861</v>
+      </c>
+      <c r="J127" t="s">
+        <v>110</v>
+      </c>
+      <c r="K127">
+        <v>30</v>
+      </c>
+      <c r="L127" t="s">
+        <v>111</v>
+      </c>
+      <c r="M127" t="s">
+        <v>21</v>
+      </c>
+      <c r="N127" t="s">
+        <v>22</v>
+      </c>
+      <c r="O127" t="s">
+        <v>33</v>
+      </c>
+      <c r="P127">
+        <v>31.571434</v>
+      </c>
+      <c r="Q127">
+        <v>75.048013</v>
+      </c>
+      <c r="R127" t="s">
+        <v>112</v>
+      </c>
+      <c r="S127">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19">
+      <c r="A128" t="s">
+        <v>19</v>
+      </c>
+      <c r="B128" t="s">
+        <v>20</v>
+      </c>
+      <c r="C128" t="s">
+        <v>21</v>
+      </c>
+      <c r="D128" t="s">
+        <v>22</v>
+      </c>
+      <c r="E128" t="s">
+        <v>33</v>
+      </c>
+      <c r="F128">
+        <v>36</v>
+      </c>
+      <c r="G128" t="s">
+        <v>107</v>
+      </c>
+      <c r="H128">
+        <v>31.5710787</v>
+      </c>
+      <c r="I128">
+        <v>75.0424861</v>
+      </c>
+      <c r="J128" t="s">
+        <v>110</v>
+      </c>
+      <c r="K128">
+        <v>31</v>
+      </c>
+      <c r="L128" t="s">
+        <v>111</v>
+      </c>
+      <c r="M128" t="s">
+        <v>21</v>
+      </c>
+      <c r="N128" t="s">
+        <v>22</v>
+      </c>
+      <c r="O128" t="s">
+        <v>33</v>
+      </c>
+      <c r="P128">
+        <v>31.583519</v>
+      </c>
+      <c r="Q128">
+        <v>75.049741</v>
+      </c>
+      <c r="R128" t="s">
+        <v>112</v>
+      </c>
+      <c r="S128">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19">
+      <c r="A129" t="s">
+        <v>19</v>
+      </c>
+      <c r="B129" t="s">
+        <v>20</v>
+      </c>
+      <c r="C129" t="s">
+        <v>21</v>
+      </c>
+      <c r="D129" t="s">
+        <v>22</v>
+      </c>
+      <c r="E129" t="s">
+        <v>33</v>
+      </c>
+      <c r="F129">
+        <v>36</v>
+      </c>
+      <c r="G129" t="s">
+        <v>107</v>
+      </c>
+      <c r="H129">
+        <v>31.5710787</v>
+      </c>
+      <c r="I129">
+        <v>75.0424861</v>
+      </c>
+      <c r="J129" t="s">
+        <v>110</v>
+      </c>
+      <c r="K129">
+        <v>34</v>
+      </c>
+      <c r="L129" t="s">
+        <v>111</v>
+      </c>
+      <c r="M129" t="s">
+        <v>21</v>
+      </c>
+      <c r="N129" t="s">
+        <v>22</v>
+      </c>
+      <c r="O129" t="s">
+        <v>33</v>
+      </c>
+      <c r="P129">
+        <v>31.34177</v>
+      </c>
+      <c r="Q129">
+        <v>75.02247</v>
+      </c>
+      <c r="R129" t="s">
+        <v>112</v>
+      </c>
+      <c r="S129">
+        <v>5100</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19">
+      <c r="A130" t="s">
+        <v>19</v>
+      </c>
+      <c r="B130" t="s">
+        <v>20</v>
+      </c>
+      <c r="C130" t="s">
+        <v>21</v>
+      </c>
+      <c r="D130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E130" t="s">
+        <v>33</v>
+      </c>
+      <c r="F130">
+        <v>38</v>
+      </c>
+      <c r="G130" t="s">
+        <v>108</v>
+      </c>
+      <c r="H130">
+        <v>31.55596</v>
+      </c>
+      <c r="I130">
+        <v>75.1401267</v>
+      </c>
+      <c r="J130" t="s">
+        <v>110</v>
+      </c>
+      <c r="K130">
+        <v>13</v>
+      </c>
+      <c r="L130" t="s">
+        <v>111</v>
+      </c>
+      <c r="M130" t="s">
+        <v>21</v>
+      </c>
+      <c r="N130" t="s">
+        <v>22</v>
+      </c>
+      <c r="O130" t="s">
+        <v>33</v>
+      </c>
+      <c r="P130">
+        <v>31.56972149</v>
+      </c>
+      <c r="Q130">
+        <v>75.09414523</v>
+      </c>
+      <c r="R130" t="s">
+        <v>112</v>
+      </c>
+      <c r="S130">
+        <v>88347</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19">
+      <c r="A131" t="s">
+        <v>19</v>
+      </c>
+      <c r="B131" t="s">
+        <v>20</v>
+      </c>
+      <c r="C131" t="s">
+        <v>21</v>
+      </c>
+      <c r="D131" t="s">
+        <v>22</v>
+      </c>
+      <c r="E131" t="s">
+        <v>33</v>
+      </c>
+      <c r="F131">
+        <v>40</v>
+      </c>
+      <c r="G131" t="s">
+        <v>109</v>
+      </c>
+      <c r="H131">
+        <v>31.592672</v>
+      </c>
+      <c r="I131">
+        <v>75.12929200000001</v>
+      </c>
+      <c r="J131" t="s">
+        <v>110</v>
+      </c>
+      <c r="K131">
+        <v>13</v>
+      </c>
+      <c r="L131" t="s">
+        <v>111</v>
+      </c>
+      <c r="M131" t="s">
+        <v>21</v>
+      </c>
+      <c r="N131" t="s">
+        <v>22</v>
+      </c>
+      <c r="O131" t="s">
+        <v>33</v>
+      </c>
+      <c r="P131">
+        <v>31.56972149</v>
+      </c>
+      <c r="Q131">
+        <v>75.09414523</v>
+      </c>
+      <c r="R131" t="s">
+        <v>112</v>
+      </c>
+      <c r="S131">
+        <v>11142</v>
       </c>
     </row>
   </sheetData>

--- a/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_Pre12.xlsx
+++ b/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_Pre12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1579" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="88">
   <si>
     <t>Scenario</t>
   </si>
@@ -79,58 +79,172 @@
     <t>PC</t>
   </si>
   <si>
-    <t>Haryana</t>
-  </si>
-  <si>
-    <t>AMRITSAR</t>
+    <t>Punjab</t>
+  </si>
+  <si>
+    <t>FAZILKA</t>
+  </si>
+  <si>
+    <t>JALANDHAR</t>
   </si>
   <si>
     <t>MALERKOTLA</t>
   </si>
   <si>
-    <t>FAZILKA</t>
-  </si>
-  <si>
-    <t>JALANDHAR</t>
-  </si>
-  <si>
-    <t>AJNALA</t>
+    <t>Abohar</t>
+  </si>
+  <si>
+    <t>ADAMPUR</t>
   </si>
   <si>
     <t>AHMEDGARH</t>
   </si>
   <si>
-    <t>MAJITHA</t>
-  </si>
-  <si>
-    <t>Abohar</t>
-  </si>
-  <si>
-    <t>ADAMPUR</t>
-  </si>
-  <si>
-    <t>RAYYA</t>
-  </si>
-  <si>
-    <t>CHOGAWAN</t>
-  </si>
-  <si>
-    <t>JANDIALA</t>
-  </si>
-  <si>
-    <t>AJNALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>CHAK SAKANDAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>CHAKDOGRA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>CHAMIARI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KHATRAI KALAN GRAIN MARKET</t>
+    <t>ABOHAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BAHADUR KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BAHAAW WALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BUKENWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BALLUANA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BHAAGU GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>CHANNAN KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>CHURHI WALA DHANNA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DEEWAN KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DHABA KOKARIYA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DHARANGWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DHINGANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DODHEWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DUTARANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>GADA DOB GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>GHALLU GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>GOBINDGARH GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JANDWALA MEERA SANGLA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JHUMIYANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JHURAD KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KALAR KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHUMBAN GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHUPAYA SARWAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KULAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KUNDAL GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MALOOKPURA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MAUJGARH GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>NARAINPURA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>NIHAL KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>PANJKOSI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>PATRE WALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>RUKANPURA KHUI KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>SAIDANWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>SITO GUNO GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>VAJIDPUR BHOMA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>WAREYAM KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>Bhadoo Waxing Plant</t>
+  </si>
+  <si>
+    <t>P.S. Waxing Plant</t>
+  </si>
+  <si>
+    <t>Sandhu waxing plant</t>
+  </si>
+  <si>
+    <t>Sri Ram cotton &amp; oil mill</t>
+  </si>
+  <si>
+    <t>Near Mandir</t>
+  </si>
+  <si>
+    <t>Near Gurdwara Sahib</t>
+  </si>
+  <si>
+    <t>Dera Jhangi wala</t>
+  </si>
+  <si>
+    <t>Near Jandwala Meera Sangla purchase center</t>
+  </si>
+  <si>
+    <t>GHARHIANA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MAMMU KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MURADWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KUHADIANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAMPUR  </t>
   </si>
   <si>
     <t>BHIKHAMPUR BEGOWAL</t>
@@ -155,195 +269,6 @@
   </si>
   <si>
     <t>UMARPURA (NATHUMAJRA)</t>
-  </si>
-  <si>
-    <t>DHADDE GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KATHUNANGAL GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MAJITHA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>SOHIAN KALAN GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>ABOHAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BAHADUR KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BAHAAW WALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BUKENWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BALLUANA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BHAAGU GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>CHANNAN KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>CHURHI WALA DHANNA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DEEWAN KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DHABA KOKARIYA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DHARANGWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DHINGANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DODHEWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DUTARANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>GADA DOB GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>GHALLU GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>GOBINDGARH GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JANDWALA MEERA SANGLA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JHUMIYANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JHURAD KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KALAR KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KHUMBAN GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KHUPAYA SARWAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KULAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KUNDAL GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MALOOKPURA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MAUJGARH GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>NARAINPURA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>NIHAL KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>PANJKOSI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>PATRE WALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>RUKANPURA KHUI KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>SAIDANWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>SITO GUNO GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>VAJIDPUR BHOMA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>WAREYAM KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>Bhadoo Waxing Plant</t>
-  </si>
-  <si>
-    <t>P.S. Waxing Plant</t>
-  </si>
-  <si>
-    <t>Sandhu waxing plant</t>
-  </si>
-  <si>
-    <t>Sri Ram cotton &amp; oil mill</t>
-  </si>
-  <si>
-    <t>Near Mandir</t>
-  </si>
-  <si>
-    <t>Near Gurdwara Sahib</t>
-  </si>
-  <si>
-    <t>Dera Jhangi wala</t>
-  </si>
-  <si>
-    <t>Near Jandwala Meera Sangla purchase center</t>
-  </si>
-  <si>
-    <t>GHARHIANA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MAMMU KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MURADWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KUHADIANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAMPUR  </t>
-  </si>
-  <si>
-    <t>BUTALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KAALEKE GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KHALCHIYA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>RAYYA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>SATHEALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BHILOWAL GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>CHOGAWAN GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JANDIALA GURU GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>TANGRA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JABBOWAL GRAIN MARKET</t>
   </si>
   <si>
     <t>Depot</t>
@@ -710,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S131"/>
+  <dimension ref="A1:S88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -786,28 +711,28 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>501</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H2">
-        <v>31.83562081</v>
+        <v>30.156605</v>
       </c>
       <c r="I2">
-        <v>74.75035127</v>
+        <v>74.19572100000001</v>
       </c>
       <c r="J2" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>396</v>
       </c>
       <c r="L2" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M2" t="s">
         <v>21</v>
@@ -816,19 +741,19 @@
         <v>22</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P2">
-        <v>31.81488868</v>
+        <v>30.15881226</v>
       </c>
       <c r="Q2">
-        <v>74.76977281000001</v>
+        <v>74.18214294000001</v>
       </c>
       <c r="R2" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S2">
-        <v>160000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -845,28 +770,28 @@
         <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>501</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H3">
-        <v>31.83562081</v>
+        <v>30.156605</v>
       </c>
       <c r="I3">
-        <v>74.75035127</v>
+        <v>74.19572100000001</v>
       </c>
       <c r="J3" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>398</v>
       </c>
       <c r="L3" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M3" t="s">
         <v>21</v>
@@ -875,19 +800,19 @@
         <v>22</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P3">
-        <v>31.45335</v>
+        <v>30.15894356</v>
       </c>
       <c r="Q3">
-        <v>74.46541999999999</v>
+        <v>74.18094151</v>
       </c>
       <c r="R3" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S3">
-        <v>132250</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -904,28 +829,28 @@
         <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>501</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H4">
-        <v>31.83562081</v>
+        <v>30.156605</v>
       </c>
       <c r="I4">
-        <v>74.75035127</v>
+        <v>74.19572100000001</v>
       </c>
       <c r="J4" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K4">
-        <v>23</v>
+        <v>399</v>
       </c>
       <c r="L4" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M4" t="s">
         <v>21</v>
@@ -934,19 +859,19 @@
         <v>22</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>31.781936</v>
+        <v>30.15848535</v>
       </c>
       <c r="Q4">
-        <v>74.76758049999999</v>
+        <v>74.18085842000001</v>
       </c>
       <c r="R4" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S4">
-        <v>139400</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -963,28 +888,28 @@
         <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>501</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H5">
-        <v>31.84430551</v>
+        <v>30.156605</v>
       </c>
       <c r="I5">
-        <v>74.91208039999999</v>
+        <v>74.19572100000001</v>
       </c>
       <c r="J5" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>400</v>
       </c>
       <c r="L5" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M5" t="s">
         <v>21</v>
@@ -993,19 +918,19 @@
         <v>22</v>
       </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P5">
-        <v>31.8529346</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q5">
-        <v>74.91584450000001</v>
+        <v>74.16401603</v>
       </c>
       <c r="R5" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S5">
-        <v>50000</v>
+        <v>145397</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1022,28 +947,28 @@
         <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>501</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H6">
-        <v>31.8895439</v>
+        <v>30.156605</v>
       </c>
       <c r="I6">
-        <v>74.7119419</v>
+        <v>74.19572100000001</v>
       </c>
       <c r="J6" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>403</v>
       </c>
       <c r="L6" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M6" t="s">
         <v>21</v>
@@ -1052,19 +977,19 @@
         <v>22</v>
       </c>
       <c r="O6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P6">
-        <v>31.45335</v>
+        <v>30.1689126</v>
       </c>
       <c r="Q6">
-        <v>74.46541999999999</v>
+        <v>74.183232</v>
       </c>
       <c r="R6" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S6">
-        <v>17750</v>
+        <v>31477</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1081,28 +1006,28 @@
         <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>501</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H7">
-        <v>31.86063083</v>
+        <v>30.156605</v>
       </c>
       <c r="I7">
-        <v>74.81790506999999</v>
+        <v>74.19572100000001</v>
       </c>
       <c r="J7" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K7">
-        <v>23</v>
+        <v>405</v>
       </c>
       <c r="L7" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M7" t="s">
         <v>21</v>
@@ -1111,19 +1036,19 @@
         <v>22</v>
       </c>
       <c r="O7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P7">
-        <v>31.781936</v>
+        <v>30.15857797</v>
       </c>
       <c r="Q7">
-        <v>74.76758049999999</v>
+        <v>74.18315728</v>
       </c>
       <c r="R7" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S7">
-        <v>12425</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1140,28 +1065,28 @@
         <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>502</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H8">
-        <v>31.819463</v>
+        <v>30.099748</v>
       </c>
       <c r="I8">
-        <v>74.8593226</v>
+        <v>74.34759699999999</v>
       </c>
       <c r="J8" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K8">
-        <v>23</v>
+        <v>407</v>
       </c>
       <c r="L8" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M8" t="s">
         <v>21</v>
@@ -1170,19 +1095,19 @@
         <v>22</v>
       </c>
       <c r="O8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P8">
-        <v>31.781936</v>
+        <v>30.126927</v>
       </c>
       <c r="Q8">
-        <v>74.76758049999999</v>
+        <v>74.161942</v>
       </c>
       <c r="R8" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S8">
-        <v>98175</v>
+        <v>71835.5</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1196,52 +1121,52 @@
         <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>1322</v>
+        <v>503</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H9">
-        <v>30.67924</v>
+        <v>30.028699</v>
       </c>
       <c r="I9">
-        <v>75.84139999999999</v>
+        <v>74.197309</v>
       </c>
       <c r="J9" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K9">
-        <v>864</v>
+        <v>404</v>
       </c>
       <c r="L9" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M9" t="s">
         <v>21</v>
       </c>
       <c r="N9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P9">
-        <v>30.458388</v>
+        <v>30.10552983</v>
       </c>
       <c r="Q9">
-        <v>74.453514</v>
+        <v>74.18014506</v>
       </c>
       <c r="R9" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S9">
-        <v>197630</v>
+        <v>73538.5</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1255,52 +1180,52 @@
         <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>1322</v>
+        <v>503</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H10">
-        <v>30.67924</v>
+        <v>30.028699</v>
       </c>
       <c r="I10">
-        <v>75.84139999999999</v>
+        <v>74.197309</v>
       </c>
       <c r="J10" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K10">
-        <v>865</v>
+        <v>407</v>
       </c>
       <c r="L10" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M10" t="s">
         <v>21</v>
       </c>
       <c r="N10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P10">
-        <v>30.458388</v>
+        <v>30.126927</v>
       </c>
       <c r="Q10">
-        <v>74.453514</v>
+        <v>74.161942</v>
       </c>
       <c r="R10" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S10">
-        <v>16680</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1314,52 +1239,52 @@
         <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F11">
-        <v>1322</v>
+        <v>505</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H11">
-        <v>30.67924</v>
+        <v>30.162859</v>
       </c>
       <c r="I11">
-        <v>75.84139999999999</v>
+        <v>73.991192</v>
       </c>
       <c r="J11" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K11">
-        <v>866</v>
+        <v>407</v>
       </c>
       <c r="L11" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M11" t="s">
         <v>21</v>
       </c>
       <c r="N11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P11">
-        <v>30.458388</v>
+        <v>30.126927</v>
       </c>
       <c r="Q11">
-        <v>74.453514</v>
+        <v>74.161942</v>
       </c>
       <c r="R11" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S11">
-        <v>42630</v>
+        <v>37309</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1373,52 +1298,52 @@
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>1322</v>
+        <v>506</v>
       </c>
       <c r="G12" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H12">
-        <v>30.67924</v>
+        <v>30.16948</v>
       </c>
       <c r="I12">
-        <v>75.84139999999999</v>
+        <v>74.28432100000001</v>
       </c>
       <c r="J12" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K12">
-        <v>868</v>
+        <v>403</v>
       </c>
       <c r="L12" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M12" t="s">
         <v>21</v>
       </c>
       <c r="N12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P12">
-        <v>30.458388</v>
+        <v>30.1689126</v>
       </c>
       <c r="Q12">
-        <v>74.453514</v>
+        <v>74.183232</v>
       </c>
       <c r="R12" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S12">
-        <v>10000</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1432,52 +1357,52 @@
         <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>1322</v>
+        <v>506</v>
       </c>
       <c r="G13" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H13">
-        <v>30.67924</v>
+        <v>30.16948</v>
       </c>
       <c r="I13">
-        <v>75.84139999999999</v>
+        <v>74.28432100000001</v>
       </c>
       <c r="J13" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K13">
-        <v>869</v>
+        <v>406</v>
       </c>
       <c r="L13" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M13" t="s">
         <v>21</v>
       </c>
       <c r="N13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P13">
-        <v>30.458388</v>
+        <v>30.16991135</v>
       </c>
       <c r="Q13">
-        <v>74.453514</v>
+        <v>74.18230296</v>
       </c>
       <c r="R13" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S13">
-        <v>10000</v>
+        <v>15202.5</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1491,52 +1416,52 @@
         <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F14">
-        <v>1322</v>
+        <v>507</v>
       </c>
       <c r="G14" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H14">
-        <v>30.67924</v>
+        <v>30.034436</v>
       </c>
       <c r="I14">
-        <v>75.84139999999999</v>
+        <v>74.233859</v>
       </c>
       <c r="J14" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K14">
-        <v>870</v>
+        <v>395</v>
       </c>
       <c r="L14" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M14" t="s">
         <v>21</v>
       </c>
       <c r="N14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P14">
-        <v>30.458388</v>
+        <v>30.08675444</v>
       </c>
       <c r="Q14">
-        <v>74.453514</v>
+        <v>74.20888524</v>
       </c>
       <c r="R14" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S14">
-        <v>10000</v>
+        <v>49766</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -1550,52 +1475,52 @@
         <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F15">
-        <v>1322</v>
+        <v>508</v>
       </c>
       <c r="G15" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H15">
-        <v>30.67924</v>
+        <v>30.182524</v>
       </c>
       <c r="I15">
-        <v>75.84139999999999</v>
+        <v>74.326095</v>
       </c>
       <c r="J15" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K15">
-        <v>871</v>
+        <v>406</v>
       </c>
       <c r="L15" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M15" t="s">
         <v>21</v>
       </c>
       <c r="N15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P15">
-        <v>30.458388</v>
+        <v>30.16991135</v>
       </c>
       <c r="Q15">
-        <v>74.453514</v>
+        <v>74.18230296</v>
       </c>
       <c r="R15" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S15">
-        <v>30720</v>
+        <v>41707.5</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -1609,52 +1534,52 @@
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F16">
-        <v>1322</v>
+        <v>509</v>
       </c>
       <c r="G16" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H16">
-        <v>30.67924</v>
+        <v>30.199756</v>
       </c>
       <c r="I16">
-        <v>75.84139999999999</v>
+        <v>74.108656</v>
       </c>
       <c r="J16" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K16">
-        <v>872</v>
+        <v>400</v>
       </c>
       <c r="L16" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M16" t="s">
         <v>21</v>
       </c>
       <c r="N16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P16">
-        <v>30.458388</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q16">
-        <v>74.453514</v>
+        <v>74.16401603</v>
       </c>
       <c r="R16" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S16">
-        <v>1080</v>
+        <v>18038</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -1668,52 +1593,52 @@
         <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F17">
-        <v>1322</v>
+        <v>510</v>
       </c>
       <c r="G17" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H17">
-        <v>30.67924</v>
+        <v>30.113508</v>
       </c>
       <c r="I17">
-        <v>75.84139999999999</v>
+        <v>73.989543</v>
       </c>
       <c r="J17" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K17">
-        <v>873</v>
+        <v>407</v>
       </c>
       <c r="L17" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M17" t="s">
         <v>21</v>
       </c>
       <c r="N17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P17">
-        <v>30.458388</v>
+        <v>30.126927</v>
       </c>
       <c r="Q17">
-        <v>74.453514</v>
+        <v>74.161942</v>
       </c>
       <c r="R17" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S17">
-        <v>29640</v>
+        <v>44568.5</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -1727,52 +1652,52 @@
         <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F18">
-        <v>1322</v>
+        <v>511</v>
       </c>
       <c r="G18" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H18">
-        <v>30.67924</v>
+        <v>30.122605</v>
       </c>
       <c r="I18">
-        <v>75.84139999999999</v>
+        <v>74.328892</v>
       </c>
       <c r="J18" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K18">
-        <v>877</v>
+        <v>407</v>
       </c>
       <c r="L18" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M18" t="s">
         <v>21</v>
       </c>
       <c r="N18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P18">
-        <v>30.458388</v>
+        <v>30.126927</v>
       </c>
       <c r="Q18">
-        <v>74.453514</v>
+        <v>74.161942</v>
       </c>
       <c r="R18" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S18">
-        <v>9950</v>
+        <v>25216</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -1786,52 +1711,52 @@
         <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F19">
-        <v>1323</v>
+        <v>512</v>
       </c>
       <c r="G19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H19">
-        <v>30.61296</v>
+        <v>30.237206</v>
       </c>
       <c r="I19">
-        <v>75.84106</v>
+        <v>74.23982700000001</v>
       </c>
       <c r="J19" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K19">
-        <v>867</v>
+        <v>401</v>
       </c>
       <c r="L19" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M19" t="s">
         <v>21</v>
       </c>
       <c r="N19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P19">
-        <v>30.458388</v>
+        <v>30.17081207</v>
       </c>
       <c r="Q19">
-        <v>74.453514</v>
+        <v>74.18179719</v>
       </c>
       <c r="R19" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S19">
-        <v>10000</v>
+        <v>44802</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -1845,52 +1770,52 @@
         <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F20">
-        <v>1323</v>
+        <v>513</v>
       </c>
       <c r="G20" t="s">
         <v>39</v>
       </c>
       <c r="H20">
-        <v>30.61296</v>
+        <v>30.023582</v>
       </c>
       <c r="I20">
-        <v>75.84106</v>
+        <v>74.04262799999999</v>
       </c>
       <c r="J20" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K20">
-        <v>875</v>
+        <v>407</v>
       </c>
       <c r="L20" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M20" t="s">
         <v>21</v>
       </c>
       <c r="N20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P20">
-        <v>30.458388</v>
+        <v>30.126927</v>
       </c>
       <c r="Q20">
-        <v>74.453514</v>
+        <v>74.161942</v>
       </c>
       <c r="R20" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S20">
-        <v>5000</v>
+        <v>30276.5</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -1904,52 +1829,52 @@
         <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F21">
-        <v>1323</v>
+        <v>514</v>
       </c>
       <c r="G21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H21">
-        <v>30.61296</v>
+        <v>29.960526</v>
       </c>
       <c r="I21">
-        <v>75.84106</v>
+        <v>74.219824</v>
       </c>
       <c r="J21" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K21">
-        <v>876</v>
+        <v>404</v>
       </c>
       <c r="L21" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M21" t="s">
         <v>21</v>
       </c>
       <c r="N21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P21">
-        <v>30.458388</v>
+        <v>30.10552983</v>
       </c>
       <c r="Q21">
-        <v>74.453514</v>
+        <v>74.18014506</v>
       </c>
       <c r="R21" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S21">
-        <v>5000</v>
+        <v>19961.5</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -1963,52 +1888,52 @@
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F22">
-        <v>1323</v>
+        <v>515</v>
       </c>
       <c r="G22" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H22">
-        <v>30.61296</v>
+        <v>30.082625</v>
       </c>
       <c r="I22">
-        <v>75.84106</v>
+        <v>74.288794</v>
       </c>
       <c r="J22" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K22">
-        <v>878</v>
+        <v>397</v>
       </c>
       <c r="L22" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M22" t="s">
         <v>21</v>
       </c>
       <c r="N22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P22">
-        <v>30.458388</v>
+        <v>30.0974593</v>
       </c>
       <c r="Q22">
-        <v>74.453514</v>
+        <v>74.206666</v>
       </c>
       <c r="R22" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S22">
-        <v>20480</v>
+        <v>9709</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -2022,52 +1947,52 @@
         <v>21</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E23" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F23">
-        <v>1323</v>
+        <v>515</v>
       </c>
       <c r="G23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H23">
-        <v>30.61296</v>
+        <v>30.082625</v>
       </c>
       <c r="I23">
-        <v>75.84106</v>
+        <v>74.288794</v>
       </c>
       <c r="J23" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K23">
-        <v>879</v>
+        <v>407</v>
       </c>
       <c r="L23" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M23" t="s">
         <v>21</v>
       </c>
       <c r="N23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O23" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P23">
-        <v>30.458388</v>
+        <v>30.126927</v>
       </c>
       <c r="Q23">
-        <v>74.453514</v>
+        <v>74.161942</v>
       </c>
       <c r="R23" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S23">
-        <v>18000</v>
+        <v>54672</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -2081,52 +2006,52 @@
         <v>21</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F24">
-        <v>1324</v>
+        <v>516</v>
       </c>
       <c r="G24" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H24">
-        <v>30.59296</v>
+        <v>30.221432</v>
       </c>
       <c r="I24">
-        <v>75.78903</v>
+        <v>74.35153099999999</v>
       </c>
       <c r="J24" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K24">
-        <v>864</v>
+        <v>401</v>
       </c>
       <c r="L24" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M24" t="s">
         <v>21</v>
       </c>
       <c r="N24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P24">
-        <v>30.458388</v>
+        <v>30.17081207</v>
       </c>
       <c r="Q24">
-        <v>74.453514</v>
+        <v>74.18179719</v>
       </c>
       <c r="R24" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S24">
-        <v>41830</v>
+        <v>13755.5</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -2140,52 +2065,52 @@
         <v>21</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F25">
-        <v>1325</v>
+        <v>516</v>
       </c>
       <c r="G25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H25">
-        <v>30.61907</v>
+        <v>30.221432</v>
       </c>
       <c r="I25">
-        <v>75.8098</v>
+        <v>74.35153099999999</v>
       </c>
       <c r="J25" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K25">
-        <v>864</v>
+        <v>406</v>
       </c>
       <c r="L25" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M25" t="s">
         <v>21</v>
       </c>
       <c r="N25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P25">
-        <v>30.458388</v>
+        <v>30.16991135</v>
       </c>
       <c r="Q25">
-        <v>74.453514</v>
+        <v>74.18230296</v>
       </c>
       <c r="R25" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S25">
-        <v>55220</v>
+        <v>6714.5</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -2199,52 +2124,52 @@
         <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F26">
-        <v>1326</v>
+        <v>517</v>
       </c>
       <c r="G26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H26">
-        <v>30.60582</v>
+        <v>30.254598</v>
       </c>
       <c r="I26">
-        <v>75.87558</v>
+        <v>74.124285</v>
       </c>
       <c r="J26" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K26">
-        <v>866</v>
+        <v>400</v>
       </c>
       <c r="L26" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M26" t="s">
         <v>21</v>
       </c>
       <c r="N26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P26">
-        <v>30.458388</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q26">
-        <v>74.453514</v>
+        <v>74.16401603</v>
       </c>
       <c r="R26" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S26">
-        <v>13140</v>
+        <v>39817.5</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -2258,52 +2183,52 @@
         <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F27">
-        <v>1326</v>
+        <v>518</v>
       </c>
       <c r="G27" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H27">
-        <v>30.60582</v>
+        <v>30.173582</v>
       </c>
       <c r="I27">
-        <v>75.87558</v>
+        <v>74.250483</v>
       </c>
       <c r="J27" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K27">
-        <v>874</v>
+        <v>406</v>
       </c>
       <c r="L27" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M27" t="s">
         <v>21</v>
       </c>
       <c r="N27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P27">
-        <v>30.458388</v>
+        <v>30.16991135</v>
       </c>
       <c r="Q27">
-        <v>74.453514</v>
+        <v>74.18230296</v>
       </c>
       <c r="R27" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S27">
-        <v>28460</v>
+        <v>10375.5</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -2317,52 +2242,52 @@
         <v>21</v>
       </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F28">
-        <v>1326</v>
+        <v>520</v>
       </c>
       <c r="G28" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H28">
-        <v>30.60582</v>
+        <v>30.21019</v>
       </c>
       <c r="I28">
-        <v>75.87558</v>
+        <v>74.024728</v>
       </c>
       <c r="J28" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K28">
-        <v>879</v>
+        <v>400</v>
       </c>
       <c r="L28" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M28" t="s">
         <v>21</v>
       </c>
       <c r="N28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P28">
-        <v>30.458388</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q28">
-        <v>74.453514</v>
+        <v>74.16401603</v>
       </c>
       <c r="R28" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S28">
-        <v>2480</v>
+        <v>72343</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -2376,52 +2301,52 @@
         <v>21</v>
       </c>
       <c r="D29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F29">
-        <v>1327</v>
+        <v>520</v>
       </c>
       <c r="G29" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H29">
-        <v>30.62411</v>
+        <v>30.21019</v>
       </c>
       <c r="I29">
-        <v>75.75073</v>
+        <v>74.024728</v>
       </c>
       <c r="J29" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K29">
-        <v>866</v>
+        <v>407</v>
       </c>
       <c r="L29" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M29" t="s">
         <v>21</v>
       </c>
       <c r="N29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P29">
-        <v>30.458388</v>
+        <v>30.126927</v>
       </c>
       <c r="Q29">
-        <v>74.453514</v>
+        <v>74.161942</v>
       </c>
       <c r="R29" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S29">
-        <v>59240</v>
+        <v>28606.5</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -2435,52 +2360,52 @@
         <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F30">
-        <v>1328</v>
+        <v>521</v>
       </c>
       <c r="G30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H30">
-        <v>30.58776</v>
+        <v>30.257887</v>
       </c>
       <c r="I30">
-        <v>75.81787</v>
+        <v>74.185624</v>
       </c>
       <c r="J30" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K30">
-        <v>866</v>
+        <v>401</v>
       </c>
       <c r="L30" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M30" t="s">
         <v>21</v>
       </c>
       <c r="N30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P30">
-        <v>30.458388</v>
+        <v>30.17081207</v>
       </c>
       <c r="Q30">
-        <v>74.453514</v>
+        <v>74.18179719</v>
       </c>
       <c r="R30" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S30">
-        <v>11670</v>
+        <v>2347.5</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -2494,52 +2419,52 @@
         <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F31">
-        <v>1328</v>
+        <v>521</v>
       </c>
       <c r="G31" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H31">
-        <v>30.58776</v>
+        <v>30.257887</v>
       </c>
       <c r="I31">
-        <v>75.81787</v>
+        <v>74.185624</v>
       </c>
       <c r="J31" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K31">
-        <v>880</v>
+        <v>402</v>
       </c>
       <c r="L31" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M31" t="s">
         <v>21</v>
       </c>
       <c r="N31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P31">
-        <v>30.458388</v>
+        <v>30.17767461</v>
       </c>
       <c r="Q31">
-        <v>74.453514</v>
+        <v>74.17723581</v>
       </c>
       <c r="R31" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S31">
-        <v>15360</v>
+        <v>34275</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -2553,52 +2478,52 @@
         <v>21</v>
       </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E32" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F32">
-        <v>1329</v>
+        <v>522</v>
       </c>
       <c r="G32" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H32">
-        <v>30.669134</v>
+        <v>30.007285</v>
       </c>
       <c r="I32">
-        <v>75.877723</v>
+        <v>74.126166</v>
       </c>
       <c r="J32" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K32">
-        <v>877</v>
+        <v>407</v>
       </c>
       <c r="L32" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M32" t="s">
         <v>21</v>
       </c>
       <c r="N32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O32" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P32">
-        <v>30.458388</v>
+        <v>30.126927</v>
       </c>
       <c r="Q32">
-        <v>74.453514</v>
+        <v>74.161942</v>
       </c>
       <c r="R32" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S32">
-        <v>10530</v>
+        <v>28245</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -2612,52 +2537,52 @@
         <v>21</v>
       </c>
       <c r="D33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E33" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F33">
-        <v>1330</v>
+        <v>523</v>
       </c>
       <c r="G33" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H33">
-        <v>30.651445</v>
+        <v>30.039412</v>
       </c>
       <c r="I33">
-        <v>75.890028</v>
+        <v>73.954567</v>
       </c>
       <c r="J33" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K33">
-        <v>872</v>
+        <v>407</v>
       </c>
       <c r="L33" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M33" t="s">
         <v>21</v>
       </c>
       <c r="N33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O33" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P33">
-        <v>30.458388</v>
+        <v>30.126927</v>
       </c>
       <c r="Q33">
-        <v>74.453514</v>
+        <v>74.161942</v>
       </c>
       <c r="R33" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S33">
-        <v>29640</v>
+        <v>12854</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -2674,28 +2599,28 @@
         <v>22</v>
       </c>
       <c r="E34" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F34">
-        <v>43</v>
+        <v>524</v>
       </c>
       <c r="G34" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H34">
-        <v>31.6939305</v>
+        <v>30.012837</v>
       </c>
       <c r="I34">
-        <v>75.09889200000001</v>
+        <v>74.432883</v>
       </c>
       <c r="J34" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K34">
-        <v>38</v>
+        <v>397</v>
       </c>
       <c r="L34" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M34" t="s">
         <v>21</v>
@@ -2704,19 +2629,19 @@
         <v>22</v>
       </c>
       <c r="O34" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P34">
-        <v>31.43316</v>
+        <v>30.0974593</v>
       </c>
       <c r="Q34">
-        <v>75.00457</v>
+        <v>74.206666</v>
       </c>
       <c r="R34" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S34">
-        <v>35025</v>
+        <v>74081</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -2733,28 +2658,28 @@
         <v>22</v>
       </c>
       <c r="E35" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F35">
-        <v>44</v>
+        <v>525</v>
       </c>
       <c r="G35" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H35">
-        <v>31.7224291</v>
+        <v>30.127701</v>
       </c>
       <c r="I35">
-        <v>75.02844</v>
+        <v>74.06368999999999</v>
       </c>
       <c r="J35" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K35">
-        <v>38</v>
+        <v>407</v>
       </c>
       <c r="L35" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M35" t="s">
         <v>21</v>
@@ -2763,19 +2688,19 @@
         <v>22</v>
       </c>
       <c r="O35" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P35">
-        <v>31.43316</v>
+        <v>30.126927</v>
       </c>
       <c r="Q35">
-        <v>75.00457</v>
+        <v>74.161942</v>
       </c>
       <c r="R35" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S35">
-        <v>52002</v>
+        <v>21311</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -2792,28 +2717,28 @@
         <v>22</v>
       </c>
       <c r="E36" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F36">
-        <v>45</v>
+        <v>526</v>
       </c>
       <c r="G36" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H36">
-        <v>31.7521051</v>
+        <v>29.98347</v>
       </c>
       <c r="I36">
-        <v>74.9515121</v>
+        <v>74.283652</v>
       </c>
       <c r="J36" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K36">
-        <v>15</v>
+        <v>394</v>
       </c>
       <c r="L36" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M36" t="s">
         <v>21</v>
@@ -2822,19 +2747,19 @@
         <v>22</v>
       </c>
       <c r="O36" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P36">
-        <v>31.70744121</v>
+        <v>30.08793156</v>
       </c>
       <c r="Q36">
-        <v>74.92578249</v>
+        <v>74.20908439</v>
       </c>
       <c r="R36" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S36">
-        <v>137745</v>
+        <v>30310</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -2851,28 +2776,28 @@
         <v>22</v>
       </c>
       <c r="E37" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F37">
-        <v>45</v>
+        <v>526</v>
       </c>
       <c r="G37" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H37">
-        <v>31.7521051</v>
+        <v>29.98347</v>
       </c>
       <c r="I37">
-        <v>74.9515121</v>
+        <v>74.283652</v>
       </c>
       <c r="J37" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K37">
-        <v>16</v>
+        <v>395</v>
       </c>
       <c r="L37" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M37" t="s">
         <v>21</v>
@@ -2881,19 +2806,19 @@
         <v>22</v>
       </c>
       <c r="O37" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P37">
-        <v>31.70744121</v>
+        <v>30.08675444</v>
       </c>
       <c r="Q37">
-        <v>74.92578249</v>
+        <v>74.20888524</v>
       </c>
       <c r="R37" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S37">
-        <v>120000</v>
+        <v>3784</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -2910,28 +2835,28 @@
         <v>22</v>
       </c>
       <c r="E38" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F38">
-        <v>45</v>
+        <v>527</v>
       </c>
       <c r="G38" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H38">
-        <v>31.7521051</v>
+        <v>30.216512</v>
       </c>
       <c r="I38">
-        <v>74.9515121</v>
+        <v>74.269492</v>
       </c>
       <c r="J38" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K38">
-        <v>38</v>
+        <v>401</v>
       </c>
       <c r="L38" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M38" t="s">
         <v>21</v>
@@ -2940,19 +2865,19 @@
         <v>22</v>
       </c>
       <c r="O38" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P38">
-        <v>31.43316</v>
+        <v>30.17081207</v>
       </c>
       <c r="Q38">
-        <v>75.00457</v>
+        <v>74.18179719</v>
       </c>
       <c r="R38" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S38">
-        <v>12973</v>
+        <v>32401</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -2969,28 +2894,28 @@
         <v>22</v>
       </c>
       <c r="E39" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F39">
-        <v>45</v>
+        <v>528</v>
       </c>
       <c r="G39" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H39">
-        <v>31.7521051</v>
+        <v>30.132598</v>
       </c>
       <c r="I39">
-        <v>74.9515121</v>
+        <v>74.343463</v>
       </c>
       <c r="J39" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K39">
-        <v>39</v>
+        <v>407</v>
       </c>
       <c r="L39" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M39" t="s">
         <v>21</v>
@@ -2999,19 +2924,19 @@
         <v>22</v>
       </c>
       <c r="O39" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P39">
-        <v>31.43316</v>
+        <v>30.126927</v>
       </c>
       <c r="Q39">
-        <v>75.00457</v>
+        <v>74.161942</v>
       </c>
       <c r="R39" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S39">
-        <v>50000</v>
+        <v>73685</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -3028,28 +2953,28 @@
         <v>22</v>
       </c>
       <c r="E40" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F40">
-        <v>46</v>
+        <v>529</v>
       </c>
       <c r="G40" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H40">
-        <v>31.7478304</v>
+        <v>30.065633</v>
       </c>
       <c r="I40">
-        <v>74.9068102</v>
+        <v>73.98462499999999</v>
       </c>
       <c r="J40" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K40">
-        <v>15</v>
+        <v>407</v>
       </c>
       <c r="L40" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M40" t="s">
         <v>21</v>
@@ -3058,19 +2983,19 @@
         <v>22</v>
       </c>
       <c r="O40" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P40">
-        <v>31.70744121</v>
+        <v>30.126927</v>
       </c>
       <c r="Q40">
-        <v>74.92578249</v>
+        <v>74.161942</v>
       </c>
       <c r="R40" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S40">
-        <v>42255</v>
+        <v>34208</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -3087,28 +3012,28 @@
         <v>22</v>
       </c>
       <c r="E41" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F41">
-        <v>46</v>
+        <v>530</v>
       </c>
       <c r="G41" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H41">
-        <v>31.7478304</v>
+        <v>29.956267</v>
       </c>
       <c r="I41">
-        <v>74.9068102</v>
+        <v>74.332578</v>
       </c>
       <c r="J41" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K41">
-        <v>45</v>
+        <v>394</v>
       </c>
       <c r="L41" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M41" t="s">
         <v>21</v>
@@ -3117,19 +3042,19 @@
         <v>22</v>
       </c>
       <c r="O41" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P41">
-        <v>31.48214</v>
+        <v>30.08793156</v>
       </c>
       <c r="Q41">
-        <v>74.55329999999999</v>
+        <v>74.20908439</v>
       </c>
       <c r="R41" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S41">
-        <v>25000</v>
+        <v>17701</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -3146,28 +3071,28 @@
         <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F42">
-        <v>46</v>
+        <v>531</v>
       </c>
       <c r="G42" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H42">
-        <v>31.7478304</v>
+        <v>30.224829</v>
       </c>
       <c r="I42">
-        <v>74.9068102</v>
+        <v>74.12361199999999</v>
       </c>
       <c r="J42" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K42">
-        <v>46</v>
+        <v>400</v>
       </c>
       <c r="L42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M42" t="s">
         <v>21</v>
@@ -3176,19 +3101,19 @@
         <v>22</v>
       </c>
       <c r="O42" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P42">
-        <v>31.48214</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q42">
-        <v>74.55329999999999</v>
+        <v>74.16401603</v>
       </c>
       <c r="R42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S42">
-        <v>25000</v>
+        <v>54819.5</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -3202,52 +3127,52 @@
         <v>21</v>
       </c>
       <c r="D43" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F43">
-        <v>501</v>
+        <v>532</v>
       </c>
       <c r="G43" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H43">
-        <v>30.156605</v>
+        <v>30.178444</v>
       </c>
       <c r="I43">
-        <v>74.19572100000001</v>
+        <v>74.065141</v>
       </c>
       <c r="J43" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K43">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="L43" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M43" t="s">
         <v>21</v>
       </c>
       <c r="N43" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O43" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P43">
-        <v>30.15881226</v>
+        <v>30.126927</v>
       </c>
       <c r="Q43">
-        <v>74.18214294000001</v>
+        <v>74.161942</v>
       </c>
       <c r="R43" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S43">
-        <v>90000</v>
+        <v>37768</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -3261,52 +3186,52 @@
         <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F44">
-        <v>501</v>
+        <v>533</v>
       </c>
       <c r="G44" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H44">
-        <v>30.156605</v>
+        <v>30.196706</v>
       </c>
       <c r="I44">
-        <v>74.19572100000001</v>
+        <v>74.04839699999999</v>
       </c>
       <c r="J44" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K44">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="L44" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M44" t="s">
         <v>21</v>
       </c>
       <c r="N44" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O44" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P44">
-        <v>30.15894356</v>
+        <v>30.126927</v>
       </c>
       <c r="Q44">
-        <v>74.18094151</v>
+        <v>74.161942</v>
       </c>
       <c r="R44" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S44">
-        <v>60000</v>
+        <v>29874.5</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -3320,52 +3245,52 @@
         <v>21</v>
       </c>
       <c r="D45" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F45">
-        <v>501</v>
+        <v>534</v>
       </c>
       <c r="G45" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H45">
-        <v>30.156605</v>
+        <v>30.035803</v>
       </c>
       <c r="I45">
-        <v>74.19572100000001</v>
+        <v>74.111367</v>
       </c>
       <c r="J45" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K45">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="L45" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M45" t="s">
         <v>21</v>
       </c>
       <c r="N45" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O45" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P45">
-        <v>30.15848535</v>
+        <v>30.126927</v>
       </c>
       <c r="Q45">
-        <v>74.18085842000001</v>
+        <v>74.161942</v>
       </c>
       <c r="R45" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S45">
-        <v>120000</v>
+        <v>56983.5</v>
       </c>
     </row>
     <row r="46" spans="1:19">
@@ -3379,52 +3304,52 @@
         <v>21</v>
       </c>
       <c r="D46" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F46">
-        <v>501</v>
+        <v>535</v>
       </c>
       <c r="G46" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H46">
-        <v>30.156605</v>
+        <v>30.131281</v>
       </c>
       <c r="I46">
-        <v>74.19572100000001</v>
+        <v>74.103374</v>
       </c>
       <c r="J46" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K46">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="L46" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M46" t="s">
         <v>21</v>
       </c>
       <c r="N46" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O46" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P46">
-        <v>30.15809938</v>
+        <v>30.126927</v>
       </c>
       <c r="Q46">
-        <v>74.16401603</v>
+        <v>74.161942</v>
       </c>
       <c r="R46" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S46">
-        <v>145397</v>
+        <v>23195.5</v>
       </c>
     </row>
     <row r="47" spans="1:19">
@@ -3438,52 +3363,52 @@
         <v>21</v>
       </c>
       <c r="D47" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F47">
-        <v>501</v>
+        <v>536</v>
       </c>
       <c r="G47" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H47">
-        <v>30.156605</v>
+        <v>30.027734</v>
       </c>
       <c r="I47">
-        <v>74.19572100000001</v>
+        <v>74.36728100000001</v>
       </c>
       <c r="J47" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K47">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="L47" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M47" t="s">
         <v>21</v>
       </c>
       <c r="N47" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O47" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P47">
-        <v>30.1689126</v>
+        <v>30.08793156</v>
       </c>
       <c r="Q47">
-        <v>74.183232</v>
+        <v>74.20908439</v>
       </c>
       <c r="R47" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S47">
-        <v>31477</v>
+        <v>71340</v>
       </c>
     </row>
     <row r="48" spans="1:19">
@@ -3497,52 +3422,52 @@
         <v>21</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E48" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F48">
-        <v>501</v>
+        <v>536</v>
       </c>
       <c r="G48" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H48">
-        <v>30.156605</v>
+        <v>30.027734</v>
       </c>
       <c r="I48">
-        <v>74.19572100000001</v>
+        <v>74.36728100000001</v>
       </c>
       <c r="J48" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K48">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="L48" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M48" t="s">
         <v>21</v>
       </c>
       <c r="N48" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O48" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P48">
-        <v>30.15857797</v>
+        <v>30.0974593</v>
       </c>
       <c r="Q48">
-        <v>74.18315728</v>
+        <v>74.206666</v>
       </c>
       <c r="R48" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S48">
-        <v>150000</v>
+        <v>36210</v>
       </c>
     </row>
     <row r="49" spans="1:19">
@@ -3556,52 +3481,52 @@
         <v>21</v>
       </c>
       <c r="D49" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E49" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F49">
-        <v>502</v>
+        <v>537</v>
       </c>
       <c r="G49" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="H49">
-        <v>30.099748</v>
+        <v>29.951208</v>
       </c>
       <c r="I49">
-        <v>74.34759699999999</v>
+        <v>74.380385</v>
       </c>
       <c r="J49" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K49">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="L49" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M49" t="s">
         <v>21</v>
       </c>
       <c r="N49" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O49" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P49">
-        <v>30.126927</v>
+        <v>30.08793156</v>
       </c>
       <c r="Q49">
-        <v>74.161942</v>
+        <v>74.20908439</v>
       </c>
       <c r="R49" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S49">
-        <v>71835.5</v>
+        <v>43549</v>
       </c>
     </row>
     <row r="50" spans="1:19">
@@ -3615,52 +3540,52 @@
         <v>21</v>
       </c>
       <c r="D50" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E50" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F50">
-        <v>503</v>
+        <v>538</v>
       </c>
       <c r="G50" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="H50">
-        <v>30.028699</v>
+        <v>30.029455</v>
       </c>
       <c r="I50">
-        <v>74.197309</v>
+        <v>74.077962</v>
       </c>
       <c r="J50" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K50">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="L50" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M50" t="s">
         <v>21</v>
       </c>
       <c r="N50" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O50" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P50">
-        <v>30.10552983</v>
+        <v>30.126927</v>
       </c>
       <c r="Q50">
-        <v>74.18014506</v>
+        <v>74.161942</v>
       </c>
       <c r="R50" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S50">
-        <v>73538.5</v>
+        <v>57368</v>
       </c>
     </row>
     <row r="51" spans="1:19">
@@ -3674,40 +3599,40 @@
         <v>21</v>
       </c>
       <c r="D51" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E51" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F51">
-        <v>503</v>
+        <v>540</v>
       </c>
       <c r="G51" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="H51">
-        <v>30.028699</v>
+        <v>29.983545</v>
       </c>
       <c r="I51">
-        <v>74.197309</v>
+        <v>74.173574</v>
       </c>
       <c r="J51" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K51">
         <v>407</v>
       </c>
       <c r="L51" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M51" t="s">
         <v>21</v>
       </c>
       <c r="N51" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O51" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P51">
         <v>30.126927</v>
@@ -3716,10 +3641,10 @@
         <v>74.161942</v>
       </c>
       <c r="R51" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S51">
-        <v>322</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="52" spans="1:19">
@@ -3733,52 +3658,52 @@
         <v>21</v>
       </c>
       <c r="D52" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E52" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F52">
-        <v>505</v>
+        <v>541</v>
       </c>
       <c r="G52" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="H52">
-        <v>30.162859</v>
+        <v>30.254422</v>
       </c>
       <c r="I52">
-        <v>73.991192</v>
+        <v>74.126414</v>
       </c>
       <c r="J52" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K52">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="L52" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M52" t="s">
         <v>21</v>
       </c>
       <c r="N52" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O52" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P52">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q52">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="R52" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S52">
-        <v>37309</v>
+        <v>29195</v>
       </c>
     </row>
     <row r="53" spans="1:19">
@@ -3792,52 +3717,52 @@
         <v>21</v>
       </c>
       <c r="D53" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E53" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F53">
-        <v>506</v>
+        <v>542</v>
       </c>
       <c r="G53" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="H53">
-        <v>30.16948</v>
+        <v>30.247905</v>
       </c>
       <c r="I53">
-        <v>74.28432100000001</v>
+        <v>74.129536</v>
       </c>
       <c r="J53" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K53">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="L53" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M53" t="s">
         <v>21</v>
       </c>
       <c r="N53" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O53" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P53">
-        <v>30.1689126</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q53">
-        <v>74.183232</v>
+        <v>74.16401603</v>
       </c>
       <c r="R53" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S53">
-        <v>2823</v>
+        <v>26795</v>
       </c>
     </row>
     <row r="54" spans="1:19">
@@ -3851,52 +3776,52 @@
         <v>21</v>
       </c>
       <c r="D54" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E54" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F54">
-        <v>506</v>
+        <v>543</v>
       </c>
       <c r="G54" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="H54">
-        <v>30.16948</v>
+        <v>30.25374</v>
       </c>
       <c r="I54">
-        <v>74.28432100000001</v>
+        <v>74.122122</v>
       </c>
       <c r="J54" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K54">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="L54" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M54" t="s">
         <v>21</v>
       </c>
       <c r="N54" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O54" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P54">
-        <v>30.16991135</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q54">
-        <v>74.18230296</v>
+        <v>74.16401603</v>
       </c>
       <c r="R54" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S54">
-        <v>15202.5</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="55" spans="1:19">
@@ -3910,52 +3835,52 @@
         <v>21</v>
       </c>
       <c r="D55" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E55" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F55">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="G55" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H55">
-        <v>30.034436</v>
+        <v>29.975306</v>
       </c>
       <c r="I55">
-        <v>74.233859</v>
+        <v>74.164011</v>
       </c>
       <c r="J55" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K55">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="L55" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M55" t="s">
         <v>21</v>
       </c>
       <c r="N55" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O55" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P55">
-        <v>30.08675444</v>
+        <v>30.126927</v>
       </c>
       <c r="Q55">
-        <v>74.20888524</v>
+        <v>74.161942</v>
       </c>
       <c r="R55" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S55">
-        <v>49766</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="56" spans="1:19">
@@ -3969,52 +3894,52 @@
         <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E56" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F56">
-        <v>508</v>
+        <v>546</v>
       </c>
       <c r="G56" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="H56">
-        <v>30.182524</v>
+        <v>30.144184</v>
       </c>
       <c r="I56">
-        <v>74.326095</v>
+        <v>74.122771</v>
       </c>
       <c r="J56" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K56">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L56" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M56" t="s">
         <v>21</v>
       </c>
       <c r="N56" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O56" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P56">
-        <v>30.16991135</v>
+        <v>30.126927</v>
       </c>
       <c r="Q56">
-        <v>74.18230296</v>
+        <v>74.161942</v>
       </c>
       <c r="R56" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S56">
-        <v>41707.5</v>
+        <v>12630.5</v>
       </c>
     </row>
     <row r="57" spans="1:19">
@@ -4028,52 +3953,52 @@
         <v>21</v>
       </c>
       <c r="D57" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E57" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F57">
-        <v>509</v>
+        <v>547</v>
       </c>
       <c r="G57" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H57">
-        <v>30.199756</v>
+        <v>30.161715</v>
       </c>
       <c r="I57">
-        <v>74.108656</v>
+        <v>73.987483</v>
       </c>
       <c r="J57" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K57">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="L57" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M57" t="s">
         <v>21</v>
       </c>
       <c r="N57" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O57" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P57">
-        <v>30.15809938</v>
+        <v>30.126927</v>
       </c>
       <c r="Q57">
-        <v>74.16401603</v>
+        <v>74.161942</v>
       </c>
       <c r="R57" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S57">
-        <v>18038</v>
+        <v>13803</v>
       </c>
     </row>
     <row r="58" spans="1:19">
@@ -4087,52 +4012,52 @@
         <v>21</v>
       </c>
       <c r="D58" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E58" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F58">
-        <v>510</v>
+        <v>548</v>
       </c>
       <c r="G58" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H58">
-        <v>30.113508</v>
+        <v>30.21135</v>
       </c>
       <c r="I58">
-        <v>73.989543</v>
+        <v>74.02397999999999</v>
       </c>
       <c r="J58" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K58">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="L58" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M58" t="s">
         <v>21</v>
       </c>
       <c r="N58" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O58" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P58">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="Q58">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="R58" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S58">
-        <v>44568.5</v>
+        <v>9145</v>
       </c>
     </row>
     <row r="59" spans="1:19">
@@ -4146,52 +4071,52 @@
         <v>21</v>
       </c>
       <c r="D59" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E59" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F59">
-        <v>511</v>
+        <v>549</v>
       </c>
       <c r="G59" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H59">
-        <v>30.122605</v>
+        <v>30.296726</v>
       </c>
       <c r="I59">
-        <v>74.328892</v>
+        <v>74.263169</v>
       </c>
       <c r="J59" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K59">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="L59" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M59" t="s">
         <v>21</v>
       </c>
       <c r="N59" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O59" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P59">
-        <v>30.126927</v>
+        <v>30.17081207</v>
       </c>
       <c r="Q59">
-        <v>74.161942</v>
+        <v>74.18179719</v>
       </c>
       <c r="R59" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S59">
-        <v>25216</v>
+        <v>17622.5</v>
       </c>
     </row>
     <row r="60" spans="1:19">
@@ -4205,52 +4130,52 @@
         <v>21</v>
       </c>
       <c r="D60" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E60" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F60">
-        <v>512</v>
+        <v>550</v>
       </c>
       <c r="G60" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="H60">
-        <v>30.237206</v>
+        <v>30.285139</v>
       </c>
       <c r="I60">
-        <v>74.23982700000001</v>
+        <v>74.172681</v>
       </c>
       <c r="J60" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K60">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L60" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M60" t="s">
         <v>21</v>
       </c>
       <c r="N60" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O60" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P60">
-        <v>30.17081207</v>
+        <v>30.17767461</v>
       </c>
       <c r="Q60">
-        <v>74.18179719</v>
+        <v>74.17723581</v>
       </c>
       <c r="R60" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S60">
-        <v>44802</v>
+        <v>42685</v>
       </c>
     </row>
     <row r="61" spans="1:19">
@@ -4264,52 +4189,52 @@
         <v>21</v>
       </c>
       <c r="D61" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E61" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F61">
-        <v>513</v>
+        <v>551</v>
       </c>
       <c r="G61" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="H61">
-        <v>30.023582</v>
+        <v>30.260814</v>
       </c>
       <c r="I61">
-        <v>74.04262799999999</v>
+        <v>74.269329</v>
       </c>
       <c r="J61" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K61">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="L61" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M61" t="s">
         <v>21</v>
       </c>
       <c r="N61" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O61" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P61">
-        <v>30.126927</v>
+        <v>30.17081207</v>
       </c>
       <c r="Q61">
-        <v>74.161942</v>
+        <v>74.18179719</v>
       </c>
       <c r="R61" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S61">
-        <v>30276.5</v>
+        <v>56502.5</v>
       </c>
     </row>
     <row r="62" spans="1:19">
@@ -4323,52 +4248,52 @@
         <v>21</v>
       </c>
       <c r="D62" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E62" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F62">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="G62" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="H62">
-        <v>29.960526</v>
+        <v>30.290503</v>
       </c>
       <c r="I62">
-        <v>74.219824</v>
+        <v>74.220803</v>
       </c>
       <c r="J62" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K62">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="L62" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M62" t="s">
         <v>21</v>
       </c>
       <c r="N62" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O62" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P62">
-        <v>30.10552983</v>
+        <v>30.17081207</v>
       </c>
       <c r="Q62">
-        <v>74.18014506</v>
+        <v>74.18179719</v>
       </c>
       <c r="R62" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S62">
-        <v>19961.5</v>
+        <v>43110</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4382,52 +4307,52 @@
         <v>21</v>
       </c>
       <c r="D63" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E63" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F63">
-        <v>515</v>
+        <v>1046</v>
       </c>
       <c r="G63" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="H63">
-        <v>30.082625</v>
+        <v>31.425406</v>
       </c>
       <c r="I63">
-        <v>74.288794</v>
+        <v>75.719528</v>
       </c>
       <c r="J63" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K63">
-        <v>397</v>
+        <v>625</v>
       </c>
       <c r="L63" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M63" t="s">
         <v>21</v>
       </c>
       <c r="N63" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O63" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P63">
-        <v>30.0974593</v>
+        <v>31.408658</v>
       </c>
       <c r="Q63">
-        <v>74.206666</v>
+        <v>75.685958</v>
       </c>
       <c r="R63" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S63">
-        <v>9709</v>
+        <v>21500</v>
       </c>
     </row>
     <row r="64" spans="1:19">
@@ -4444,28 +4369,28 @@
         <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F64">
-        <v>515</v>
+        <v>1322</v>
       </c>
       <c r="G64" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="H64">
-        <v>30.082625</v>
+        <v>30.67924</v>
       </c>
       <c r="I64">
-        <v>74.288794</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J64" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K64">
-        <v>407</v>
+        <v>864</v>
       </c>
       <c r="L64" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M64" t="s">
         <v>21</v>
@@ -4474,19 +4399,19 @@
         <v>24</v>
       </c>
       <c r="O64" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P64">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q64">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R64" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S64">
-        <v>54672</v>
+        <v>197630</v>
       </c>
     </row>
     <row r="65" spans="1:19">
@@ -4503,28 +4428,28 @@
         <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F65">
-        <v>516</v>
+        <v>1322</v>
       </c>
       <c r="G65" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H65">
-        <v>30.221432</v>
+        <v>30.67924</v>
       </c>
       <c r="I65">
-        <v>74.35153099999999</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J65" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K65">
-        <v>401</v>
+        <v>865</v>
       </c>
       <c r="L65" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M65" t="s">
         <v>21</v>
@@ -4533,19 +4458,19 @@
         <v>24</v>
       </c>
       <c r="O65" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P65">
-        <v>30.17081207</v>
+        <v>30.458388</v>
       </c>
       <c r="Q65">
-        <v>74.18179719</v>
+        <v>74.453514</v>
       </c>
       <c r="R65" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S65">
-        <v>13755.5</v>
+        <v>16680</v>
       </c>
     </row>
     <row r="66" spans="1:19">
@@ -4562,28 +4487,28 @@
         <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F66">
-        <v>516</v>
+        <v>1322</v>
       </c>
       <c r="G66" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="H66">
-        <v>30.221432</v>
+        <v>30.67924</v>
       </c>
       <c r="I66">
-        <v>74.35153099999999</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J66" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K66">
-        <v>406</v>
+        <v>866</v>
       </c>
       <c r="L66" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M66" t="s">
         <v>21</v>
@@ -4592,19 +4517,19 @@
         <v>24</v>
       </c>
       <c r="O66" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P66">
-        <v>30.16991135</v>
+        <v>30.458388</v>
       </c>
       <c r="Q66">
-        <v>74.18230296</v>
+        <v>74.453514</v>
       </c>
       <c r="R66" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S66">
-        <v>6714.5</v>
+        <v>42630</v>
       </c>
     </row>
     <row r="67" spans="1:19">
@@ -4621,28 +4546,28 @@
         <v>24</v>
       </c>
       <c r="E67" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F67">
-        <v>517</v>
+        <v>1322</v>
       </c>
       <c r="G67" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="H67">
-        <v>30.254598</v>
+        <v>30.67924</v>
       </c>
       <c r="I67">
-        <v>74.124285</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J67" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K67">
-        <v>400</v>
+        <v>868</v>
       </c>
       <c r="L67" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M67" t="s">
         <v>21</v>
@@ -4651,19 +4576,19 @@
         <v>24</v>
       </c>
       <c r="O67" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P67">
-        <v>30.15809938</v>
+        <v>30.458388</v>
       </c>
       <c r="Q67">
-        <v>74.16401603</v>
+        <v>74.453514</v>
       </c>
       <c r="R67" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S67">
-        <v>39817.5</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="68" spans="1:19">
@@ -4680,28 +4605,28 @@
         <v>24</v>
       </c>
       <c r="E68" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F68">
-        <v>518</v>
+        <v>1322</v>
       </c>
       <c r="G68" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="H68">
-        <v>30.173582</v>
+        <v>30.67924</v>
       </c>
       <c r="I68">
-        <v>74.250483</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J68" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K68">
-        <v>406</v>
+        <v>869</v>
       </c>
       <c r="L68" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M68" t="s">
         <v>21</v>
@@ -4710,19 +4635,19 @@
         <v>24</v>
       </c>
       <c r="O68" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P68">
-        <v>30.16991135</v>
+        <v>30.458388</v>
       </c>
       <c r="Q68">
-        <v>74.18230296</v>
+        <v>74.453514</v>
       </c>
       <c r="R68" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S68">
-        <v>10375.5</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="69" spans="1:19">
@@ -4739,28 +4664,28 @@
         <v>24</v>
       </c>
       <c r="E69" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F69">
-        <v>520</v>
+        <v>1322</v>
       </c>
       <c r="G69" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="H69">
-        <v>30.21019</v>
+        <v>30.67924</v>
       </c>
       <c r="I69">
-        <v>74.024728</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J69" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K69">
-        <v>400</v>
+        <v>870</v>
       </c>
       <c r="L69" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M69" t="s">
         <v>21</v>
@@ -4769,19 +4694,19 @@
         <v>24</v>
       </c>
       <c r="O69" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P69">
-        <v>30.15809938</v>
+        <v>30.458388</v>
       </c>
       <c r="Q69">
-        <v>74.16401603</v>
+        <v>74.453514</v>
       </c>
       <c r="R69" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S69">
-        <v>72343</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="70" spans="1:19">
@@ -4798,28 +4723,28 @@
         <v>24</v>
       </c>
       <c r="E70" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F70">
-        <v>520</v>
+        <v>1322</v>
       </c>
       <c r="G70" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="H70">
-        <v>30.21019</v>
+        <v>30.67924</v>
       </c>
       <c r="I70">
-        <v>74.024728</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J70" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K70">
-        <v>407</v>
+        <v>871</v>
       </c>
       <c r="L70" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M70" t="s">
         <v>21</v>
@@ -4828,19 +4753,19 @@
         <v>24</v>
       </c>
       <c r="O70" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P70">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q70">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R70" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S70">
-        <v>28606.5</v>
+        <v>30720</v>
       </c>
     </row>
     <row r="71" spans="1:19">
@@ -4857,28 +4782,28 @@
         <v>24</v>
       </c>
       <c r="E71" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F71">
-        <v>521</v>
+        <v>1322</v>
       </c>
       <c r="G71" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="H71">
-        <v>30.257887</v>
+        <v>30.67924</v>
       </c>
       <c r="I71">
-        <v>74.185624</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J71" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K71">
-        <v>401</v>
+        <v>872</v>
       </c>
       <c r="L71" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M71" t="s">
         <v>21</v>
@@ -4887,19 +4812,19 @@
         <v>24</v>
       </c>
       <c r="O71" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P71">
-        <v>30.17081207</v>
+        <v>30.458388</v>
       </c>
       <c r="Q71">
-        <v>74.18179719</v>
+        <v>74.453514</v>
       </c>
       <c r="R71" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S71">
-        <v>2347.5</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="72" spans="1:19">
@@ -4916,28 +4841,28 @@
         <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F72">
-        <v>521</v>
+        <v>1322</v>
       </c>
       <c r="G72" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="H72">
-        <v>30.257887</v>
+        <v>30.67924</v>
       </c>
       <c r="I72">
-        <v>74.185624</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J72" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K72">
-        <v>402</v>
+        <v>873</v>
       </c>
       <c r="L72" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M72" t="s">
         <v>21</v>
@@ -4946,19 +4871,19 @@
         <v>24</v>
       </c>
       <c r="O72" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P72">
-        <v>30.17767461</v>
+        <v>30.458388</v>
       </c>
       <c r="Q72">
-        <v>74.17723581</v>
+        <v>74.453514</v>
       </c>
       <c r="R72" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S72">
-        <v>34275</v>
+        <v>29640</v>
       </c>
     </row>
     <row r="73" spans="1:19">
@@ -4975,28 +4900,28 @@
         <v>24</v>
       </c>
       <c r="E73" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F73">
-        <v>522</v>
+        <v>1322</v>
       </c>
       <c r="G73" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="H73">
-        <v>30.007285</v>
+        <v>30.67924</v>
       </c>
       <c r="I73">
-        <v>74.126166</v>
+        <v>75.84139999999999</v>
       </c>
       <c r="J73" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K73">
-        <v>407</v>
+        <v>877</v>
       </c>
       <c r="L73" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M73" t="s">
         <v>21</v>
@@ -5005,19 +4930,19 @@
         <v>24</v>
       </c>
       <c r="O73" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P73">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q73">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R73" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S73">
-        <v>28245</v>
+        <v>9950</v>
       </c>
     </row>
     <row r="74" spans="1:19">
@@ -5034,28 +4959,28 @@
         <v>24</v>
       </c>
       <c r="E74" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F74">
-        <v>523</v>
+        <v>1323</v>
       </c>
       <c r="G74" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H74">
-        <v>30.039412</v>
+        <v>30.61296</v>
       </c>
       <c r="I74">
-        <v>73.954567</v>
+        <v>75.84106</v>
       </c>
       <c r="J74" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K74">
-        <v>407</v>
+        <v>867</v>
       </c>
       <c r="L74" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M74" t="s">
         <v>21</v>
@@ -5064,19 +4989,19 @@
         <v>24</v>
       </c>
       <c r="O74" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P74">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q74">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R74" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S74">
-        <v>12854</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="75" spans="1:19">
@@ -5093,28 +5018,28 @@
         <v>24</v>
       </c>
       <c r="E75" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F75">
-        <v>524</v>
+        <v>1323</v>
       </c>
       <c r="G75" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H75">
-        <v>30.012837</v>
+        <v>30.61296</v>
       </c>
       <c r="I75">
-        <v>74.432883</v>
+        <v>75.84106</v>
       </c>
       <c r="J75" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K75">
-        <v>397</v>
+        <v>875</v>
       </c>
       <c r="L75" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M75" t="s">
         <v>21</v>
@@ -5123,19 +5048,19 @@
         <v>24</v>
       </c>
       <c r="O75" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P75">
-        <v>30.0974593</v>
+        <v>30.458388</v>
       </c>
       <c r="Q75">
-        <v>74.206666</v>
+        <v>74.453514</v>
       </c>
       <c r="R75" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S75">
-        <v>74081</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="76" spans="1:19">
@@ -5152,28 +5077,28 @@
         <v>24</v>
       </c>
       <c r="E76" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F76">
-        <v>525</v>
+        <v>1323</v>
       </c>
       <c r="G76" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H76">
-        <v>30.127701</v>
+        <v>30.61296</v>
       </c>
       <c r="I76">
-        <v>74.06368999999999</v>
+        <v>75.84106</v>
       </c>
       <c r="J76" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K76">
-        <v>407</v>
+        <v>876</v>
       </c>
       <c r="L76" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M76" t="s">
         <v>21</v>
@@ -5182,19 +5107,19 @@
         <v>24</v>
       </c>
       <c r="O76" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P76">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q76">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R76" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S76">
-        <v>21311</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="77" spans="1:19">
@@ -5211,28 +5136,28 @@
         <v>24</v>
       </c>
       <c r="E77" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F77">
-        <v>526</v>
+        <v>1323</v>
       </c>
       <c r="G77" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H77">
-        <v>29.98347</v>
+        <v>30.61296</v>
       </c>
       <c r="I77">
-        <v>74.283652</v>
+        <v>75.84106</v>
       </c>
       <c r="J77" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K77">
-        <v>394</v>
+        <v>878</v>
       </c>
       <c r="L77" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M77" t="s">
         <v>21</v>
@@ -5241,19 +5166,19 @@
         <v>24</v>
       </c>
       <c r="O77" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P77">
-        <v>30.08793156</v>
+        <v>30.458388</v>
       </c>
       <c r="Q77">
-        <v>74.20908439</v>
+        <v>74.453514</v>
       </c>
       <c r="R77" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S77">
-        <v>30310</v>
+        <v>20480</v>
       </c>
     </row>
     <row r="78" spans="1:19">
@@ -5270,28 +5195,28 @@
         <v>24</v>
       </c>
       <c r="E78" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F78">
-        <v>526</v>
+        <v>1323</v>
       </c>
       <c r="G78" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H78">
-        <v>29.98347</v>
+        <v>30.61296</v>
       </c>
       <c r="I78">
-        <v>74.283652</v>
+        <v>75.84106</v>
       </c>
       <c r="J78" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K78">
-        <v>395</v>
+        <v>879</v>
       </c>
       <c r="L78" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M78" t="s">
         <v>21</v>
@@ -5300,19 +5225,19 @@
         <v>24</v>
       </c>
       <c r="O78" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P78">
-        <v>30.08675444</v>
+        <v>30.458388</v>
       </c>
       <c r="Q78">
-        <v>74.20888524</v>
+        <v>74.453514</v>
       </c>
       <c r="R78" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S78">
-        <v>3784</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="79" spans="1:19">
@@ -5329,28 +5254,28 @@
         <v>24</v>
       </c>
       <c r="E79" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F79">
-        <v>527</v>
+        <v>1324</v>
       </c>
       <c r="G79" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H79">
-        <v>30.216512</v>
+        <v>30.59296</v>
       </c>
       <c r="I79">
-        <v>74.269492</v>
+        <v>75.78903</v>
       </c>
       <c r="J79" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K79">
-        <v>401</v>
+        <v>864</v>
       </c>
       <c r="L79" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M79" t="s">
         <v>21</v>
@@ -5359,19 +5284,19 @@
         <v>24</v>
       </c>
       <c r="O79" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P79">
-        <v>30.17081207</v>
+        <v>30.458388</v>
       </c>
       <c r="Q79">
-        <v>74.18179719</v>
+        <v>74.453514</v>
       </c>
       <c r="R79" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S79">
-        <v>32401</v>
+        <v>41830</v>
       </c>
     </row>
     <row r="80" spans="1:19">
@@ -5388,28 +5313,28 @@
         <v>24</v>
       </c>
       <c r="E80" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F80">
-        <v>528</v>
+        <v>1325</v>
       </c>
       <c r="G80" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H80">
-        <v>30.132598</v>
+        <v>30.61907</v>
       </c>
       <c r="I80">
-        <v>74.343463</v>
+        <v>75.8098</v>
       </c>
       <c r="J80" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K80">
-        <v>407</v>
+        <v>864</v>
       </c>
       <c r="L80" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M80" t="s">
         <v>21</v>
@@ -5418,19 +5343,19 @@
         <v>24</v>
       </c>
       <c r="O80" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P80">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q80">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R80" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S80">
-        <v>73685</v>
+        <v>55220</v>
       </c>
     </row>
     <row r="81" spans="1:19">
@@ -5447,28 +5372,28 @@
         <v>24</v>
       </c>
       <c r="E81" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F81">
-        <v>529</v>
+        <v>1326</v>
       </c>
       <c r="G81" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H81">
-        <v>30.065633</v>
+        <v>30.60582</v>
       </c>
       <c r="I81">
-        <v>73.98462499999999</v>
+        <v>75.87558</v>
       </c>
       <c r="J81" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K81">
-        <v>407</v>
+        <v>866</v>
       </c>
       <c r="L81" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M81" t="s">
         <v>21</v>
@@ -5477,19 +5402,19 @@
         <v>24</v>
       </c>
       <c r="O81" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P81">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q81">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R81" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S81">
-        <v>34208</v>
+        <v>13140</v>
       </c>
     </row>
     <row r="82" spans="1:19">
@@ -5506,28 +5431,28 @@
         <v>24</v>
       </c>
       <c r="E82" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F82">
-        <v>530</v>
+        <v>1326</v>
       </c>
       <c r="G82" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H82">
-        <v>29.956267</v>
+        <v>30.60582</v>
       </c>
       <c r="I82">
-        <v>74.332578</v>
+        <v>75.87558</v>
       </c>
       <c r="J82" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K82">
-        <v>394</v>
+        <v>874</v>
       </c>
       <c r="L82" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M82" t="s">
         <v>21</v>
@@ -5536,19 +5461,19 @@
         <v>24</v>
       </c>
       <c r="O82" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P82">
-        <v>30.08793156</v>
+        <v>30.458388</v>
       </c>
       <c r="Q82">
-        <v>74.20908439</v>
+        <v>74.453514</v>
       </c>
       <c r="R82" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S82">
-        <v>17701</v>
+        <v>28460</v>
       </c>
     </row>
     <row r="83" spans="1:19">
@@ -5565,28 +5490,28 @@
         <v>24</v>
       </c>
       <c r="E83" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F83">
-        <v>531</v>
+        <v>1326</v>
       </c>
       <c r="G83" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H83">
-        <v>30.224829</v>
+        <v>30.60582</v>
       </c>
       <c r="I83">
-        <v>74.12361199999999</v>
+        <v>75.87558</v>
       </c>
       <c r="J83" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K83">
-        <v>400</v>
+        <v>879</v>
       </c>
       <c r="L83" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M83" t="s">
         <v>21</v>
@@ -5595,19 +5520,19 @@
         <v>24</v>
       </c>
       <c r="O83" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P83">
-        <v>30.15809938</v>
+        <v>30.458388</v>
       </c>
       <c r="Q83">
-        <v>74.16401603</v>
+        <v>74.453514</v>
       </c>
       <c r="R83" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S83">
-        <v>54819.5</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="84" spans="1:19">
@@ -5624,28 +5549,28 @@
         <v>24</v>
       </c>
       <c r="E84" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F84">
-        <v>532</v>
+        <v>1327</v>
       </c>
       <c r="G84" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H84">
-        <v>30.178444</v>
+        <v>30.62411</v>
       </c>
       <c r="I84">
-        <v>74.065141</v>
+        <v>75.75073</v>
       </c>
       <c r="J84" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K84">
-        <v>407</v>
+        <v>866</v>
       </c>
       <c r="L84" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M84" t="s">
         <v>21</v>
@@ -5654,19 +5579,19 @@
         <v>24</v>
       </c>
       <c r="O84" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P84">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q84">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R84" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S84">
-        <v>37768</v>
+        <v>59240</v>
       </c>
     </row>
     <row r="85" spans="1:19">
@@ -5683,28 +5608,28 @@
         <v>24</v>
       </c>
       <c r="E85" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F85">
-        <v>533</v>
+        <v>1328</v>
       </c>
       <c r="G85" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H85">
-        <v>30.196706</v>
+        <v>30.58776</v>
       </c>
       <c r="I85">
-        <v>74.04839699999999</v>
+        <v>75.81787</v>
       </c>
       <c r="J85" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K85">
-        <v>407</v>
+        <v>866</v>
       </c>
       <c r="L85" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M85" t="s">
         <v>21</v>
@@ -5713,19 +5638,19 @@
         <v>24</v>
       </c>
       <c r="O85" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P85">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q85">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R85" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S85">
-        <v>29874.5</v>
+        <v>11670</v>
       </c>
     </row>
     <row r="86" spans="1:19">
@@ -5742,28 +5667,28 @@
         <v>24</v>
       </c>
       <c r="E86" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F86">
-        <v>534</v>
+        <v>1328</v>
       </c>
       <c r="G86" t="s">
         <v>82</v>
       </c>
       <c r="H86">
-        <v>30.035803</v>
+        <v>30.58776</v>
       </c>
       <c r="I86">
-        <v>74.111367</v>
+        <v>75.81787</v>
       </c>
       <c r="J86" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K86">
-        <v>407</v>
+        <v>880</v>
       </c>
       <c r="L86" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M86" t="s">
         <v>21</v>
@@ -5772,19 +5697,19 @@
         <v>24</v>
       </c>
       <c r="O86" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P86">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q86">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R86" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S86">
-        <v>56983.5</v>
+        <v>15360</v>
       </c>
     </row>
     <row r="87" spans="1:19">
@@ -5801,28 +5726,28 @@
         <v>24</v>
       </c>
       <c r="E87" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F87">
-        <v>535</v>
+        <v>1329</v>
       </c>
       <c r="G87" t="s">
         <v>83</v>
       </c>
       <c r="H87">
-        <v>30.131281</v>
+        <v>30.669134</v>
       </c>
       <c r="I87">
-        <v>74.103374</v>
+        <v>75.877723</v>
       </c>
       <c r="J87" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K87">
-        <v>407</v>
+        <v>877</v>
       </c>
       <c r="L87" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M87" t="s">
         <v>21</v>
@@ -5831,19 +5756,19 @@
         <v>24</v>
       </c>
       <c r="O87" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P87">
-        <v>30.126927</v>
+        <v>30.458388</v>
       </c>
       <c r="Q87">
-        <v>74.161942</v>
+        <v>74.453514</v>
       </c>
       <c r="R87" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S87">
-        <v>23195.5</v>
+        <v>10530</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -5860,28 +5785,28 @@
         <v>24</v>
       </c>
       <c r="E88" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F88">
-        <v>536</v>
+        <v>1330</v>
       </c>
       <c r="G88" t="s">
         <v>84</v>
       </c>
       <c r="H88">
-        <v>30.027734</v>
+        <v>30.651445</v>
       </c>
       <c r="I88">
-        <v>74.36728100000001</v>
+        <v>75.890028</v>
       </c>
       <c r="J88" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="K88">
-        <v>394</v>
+        <v>872</v>
       </c>
       <c r="L88" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M88" t="s">
         <v>21</v>
@@ -5890,2556 +5815,19 @@
         <v>24</v>
       </c>
       <c r="O88" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P88">
-        <v>30.08793156</v>
+        <v>30.458388</v>
       </c>
       <c r="Q88">
-        <v>74.20908439</v>
+        <v>74.453514</v>
       </c>
       <c r="R88" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="S88">
-        <v>71340</v>
-      </c>
-    </row>
-    <row r="89" spans="1:19">
-      <c r="A89" t="s">
-        <v>19</v>
-      </c>
-      <c r="B89" t="s">
-        <v>20</v>
-      </c>
-      <c r="C89" t="s">
-        <v>21</v>
-      </c>
-      <c r="D89" t="s">
-        <v>24</v>
-      </c>
-      <c r="E89" t="s">
-        <v>29</v>
-      </c>
-      <c r="F89">
-        <v>536</v>
-      </c>
-      <c r="G89" t="s">
-        <v>84</v>
-      </c>
-      <c r="H89">
-        <v>30.027734</v>
-      </c>
-      <c r="I89">
-        <v>74.36728100000001</v>
-      </c>
-      <c r="J89" t="s">
-        <v>110</v>
-      </c>
-      <c r="K89">
-        <v>397</v>
-      </c>
-      <c r="L89" t="s">
-        <v>111</v>
-      </c>
-      <c r="M89" t="s">
-        <v>21</v>
-      </c>
-      <c r="N89" t="s">
-        <v>24</v>
-      </c>
-      <c r="O89" t="s">
-        <v>29</v>
-      </c>
-      <c r="P89">
-        <v>30.0974593</v>
-      </c>
-      <c r="Q89">
-        <v>74.206666</v>
-      </c>
-      <c r="R89" t="s">
-        <v>112</v>
-      </c>
-      <c r="S89">
-        <v>36210</v>
-      </c>
-    </row>
-    <row r="90" spans="1:19">
-      <c r="A90" t="s">
-        <v>19</v>
-      </c>
-      <c r="B90" t="s">
-        <v>20</v>
-      </c>
-      <c r="C90" t="s">
-        <v>21</v>
-      </c>
-      <c r="D90" t="s">
-        <v>24</v>
-      </c>
-      <c r="E90" t="s">
-        <v>29</v>
-      </c>
-      <c r="F90">
-        <v>537</v>
-      </c>
-      <c r="G90" t="s">
-        <v>85</v>
-      </c>
-      <c r="H90">
-        <v>29.951208</v>
-      </c>
-      <c r="I90">
-        <v>74.380385</v>
-      </c>
-      <c r="J90" t="s">
-        <v>110</v>
-      </c>
-      <c r="K90">
-        <v>394</v>
-      </c>
-      <c r="L90" t="s">
-        <v>111</v>
-      </c>
-      <c r="M90" t="s">
-        <v>21</v>
-      </c>
-      <c r="N90" t="s">
-        <v>24</v>
-      </c>
-      <c r="O90" t="s">
-        <v>29</v>
-      </c>
-      <c r="P90">
-        <v>30.08793156</v>
-      </c>
-      <c r="Q90">
-        <v>74.20908439</v>
-      </c>
-      <c r="R90" t="s">
-        <v>112</v>
-      </c>
-      <c r="S90">
-        <v>43549</v>
-      </c>
-    </row>
-    <row r="91" spans="1:19">
-      <c r="A91" t="s">
-        <v>19</v>
-      </c>
-      <c r="B91" t="s">
-        <v>20</v>
-      </c>
-      <c r="C91" t="s">
-        <v>21</v>
-      </c>
-      <c r="D91" t="s">
-        <v>24</v>
-      </c>
-      <c r="E91" t="s">
-        <v>29</v>
-      </c>
-      <c r="F91">
-        <v>538</v>
-      </c>
-      <c r="G91" t="s">
-        <v>86</v>
-      </c>
-      <c r="H91">
-        <v>30.029455</v>
-      </c>
-      <c r="I91">
-        <v>74.077962</v>
-      </c>
-      <c r="J91" t="s">
-        <v>110</v>
-      </c>
-      <c r="K91">
-        <v>407</v>
-      </c>
-      <c r="L91" t="s">
-        <v>111</v>
-      </c>
-      <c r="M91" t="s">
-        <v>21</v>
-      </c>
-      <c r="N91" t="s">
-        <v>24</v>
-      </c>
-      <c r="O91" t="s">
-        <v>29</v>
-      </c>
-      <c r="P91">
-        <v>30.126927</v>
-      </c>
-      <c r="Q91">
-        <v>74.161942</v>
-      </c>
-      <c r="R91" t="s">
-        <v>112</v>
-      </c>
-      <c r="S91">
-        <v>57368</v>
-      </c>
-    </row>
-    <row r="92" spans="1:19">
-      <c r="A92" t="s">
-        <v>19</v>
-      </c>
-      <c r="B92" t="s">
-        <v>20</v>
-      </c>
-      <c r="C92" t="s">
-        <v>21</v>
-      </c>
-      <c r="D92" t="s">
-        <v>24</v>
-      </c>
-      <c r="E92" t="s">
-        <v>29</v>
-      </c>
-      <c r="F92">
-        <v>540</v>
-      </c>
-      <c r="G92" t="s">
-        <v>87</v>
-      </c>
-      <c r="H92">
-        <v>29.983545</v>
-      </c>
-      <c r="I92">
-        <v>74.173574</v>
-      </c>
-      <c r="J92" t="s">
-        <v>110</v>
-      </c>
-      <c r="K92">
-        <v>407</v>
-      </c>
-      <c r="L92" t="s">
-        <v>111</v>
-      </c>
-      <c r="M92" t="s">
-        <v>21</v>
-      </c>
-      <c r="N92" t="s">
-        <v>24</v>
-      </c>
-      <c r="O92" t="s">
-        <v>29</v>
-      </c>
-      <c r="P92">
-        <v>30.126927</v>
-      </c>
-      <c r="Q92">
-        <v>74.161942</v>
-      </c>
-      <c r="R92" t="s">
-        <v>112</v>
-      </c>
-      <c r="S92">
-        <v>2487</v>
-      </c>
-    </row>
-    <row r="93" spans="1:19">
-      <c r="A93" t="s">
-        <v>19</v>
-      </c>
-      <c r="B93" t="s">
-        <v>20</v>
-      </c>
-      <c r="C93" t="s">
-        <v>21</v>
-      </c>
-      <c r="D93" t="s">
-        <v>24</v>
-      </c>
-      <c r="E93" t="s">
-        <v>29</v>
-      </c>
-      <c r="F93">
-        <v>541</v>
-      </c>
-      <c r="G93" t="s">
-        <v>88</v>
-      </c>
-      <c r="H93">
-        <v>30.254422</v>
-      </c>
-      <c r="I93">
-        <v>74.126414</v>
-      </c>
-      <c r="J93" t="s">
-        <v>110</v>
-      </c>
-      <c r="K93">
-        <v>400</v>
-      </c>
-      <c r="L93" t="s">
-        <v>111</v>
-      </c>
-      <c r="M93" t="s">
-        <v>21</v>
-      </c>
-      <c r="N93" t="s">
-        <v>24</v>
-      </c>
-      <c r="O93" t="s">
-        <v>29</v>
-      </c>
-      <c r="P93">
-        <v>30.15809938</v>
-      </c>
-      <c r="Q93">
-        <v>74.16401603</v>
-      </c>
-      <c r="R93" t="s">
-        <v>112</v>
-      </c>
-      <c r="S93">
-        <v>29195</v>
-      </c>
-    </row>
-    <row r="94" spans="1:19">
-      <c r="A94" t="s">
-        <v>19</v>
-      </c>
-      <c r="B94" t="s">
-        <v>20</v>
-      </c>
-      <c r="C94" t="s">
-        <v>21</v>
-      </c>
-      <c r="D94" t="s">
-        <v>24</v>
-      </c>
-      <c r="E94" t="s">
-        <v>29</v>
-      </c>
-      <c r="F94">
-        <v>542</v>
-      </c>
-      <c r="G94" t="s">
-        <v>89</v>
-      </c>
-      <c r="H94">
-        <v>30.247905</v>
-      </c>
-      <c r="I94">
-        <v>74.129536</v>
-      </c>
-      <c r="J94" t="s">
-        <v>110</v>
-      </c>
-      <c r="K94">
-        <v>400</v>
-      </c>
-      <c r="L94" t="s">
-        <v>111</v>
-      </c>
-      <c r="M94" t="s">
-        <v>21</v>
-      </c>
-      <c r="N94" t="s">
-        <v>24</v>
-      </c>
-      <c r="O94" t="s">
-        <v>29</v>
-      </c>
-      <c r="P94">
-        <v>30.15809938</v>
-      </c>
-      <c r="Q94">
-        <v>74.16401603</v>
-      </c>
-      <c r="R94" t="s">
-        <v>112</v>
-      </c>
-      <c r="S94">
-        <v>26795</v>
-      </c>
-    </row>
-    <row r="95" spans="1:19">
-      <c r="A95" t="s">
-        <v>19</v>
-      </c>
-      <c r="B95" t="s">
-        <v>20</v>
-      </c>
-      <c r="C95" t="s">
-        <v>21</v>
-      </c>
-      <c r="D95" t="s">
-        <v>24</v>
-      </c>
-      <c r="E95" t="s">
-        <v>29</v>
-      </c>
-      <c r="F95">
-        <v>543</v>
-      </c>
-      <c r="G95" t="s">
-        <v>90</v>
-      </c>
-      <c r="H95">
-        <v>30.25374</v>
-      </c>
-      <c r="I95">
-        <v>74.122122</v>
-      </c>
-      <c r="J95" t="s">
-        <v>110</v>
-      </c>
-      <c r="K95">
-        <v>400</v>
-      </c>
-      <c r="L95" t="s">
-        <v>111</v>
-      </c>
-      <c r="M95" t="s">
-        <v>21</v>
-      </c>
-      <c r="N95" t="s">
-        <v>24</v>
-      </c>
-      <c r="O95" t="s">
-        <v>29</v>
-      </c>
-      <c r="P95">
-        <v>30.15809938</v>
-      </c>
-      <c r="Q95">
-        <v>74.16401603</v>
-      </c>
-      <c r="R95" t="s">
-        <v>112</v>
-      </c>
-      <c r="S95">
-        <v>7950</v>
-      </c>
-    </row>
-    <row r="96" spans="1:19">
-      <c r="A96" t="s">
-        <v>19</v>
-      </c>
-      <c r="B96" t="s">
-        <v>20</v>
-      </c>
-      <c r="C96" t="s">
-        <v>21</v>
-      </c>
-      <c r="D96" t="s">
-        <v>24</v>
-      </c>
-      <c r="E96" t="s">
-        <v>29</v>
-      </c>
-      <c r="F96">
-        <v>545</v>
-      </c>
-      <c r="G96" t="s">
-        <v>91</v>
-      </c>
-      <c r="H96">
-        <v>29.975306</v>
-      </c>
-      <c r="I96">
-        <v>74.164011</v>
-      </c>
-      <c r="J96" t="s">
-        <v>110</v>
-      </c>
-      <c r="K96">
-        <v>407</v>
-      </c>
-      <c r="L96" t="s">
-        <v>111</v>
-      </c>
-      <c r="M96" t="s">
-        <v>21</v>
-      </c>
-      <c r="N96" t="s">
-        <v>24</v>
-      </c>
-      <c r="O96" t="s">
-        <v>29</v>
-      </c>
-      <c r="P96">
-        <v>30.126927</v>
-      </c>
-      <c r="Q96">
-        <v>74.161942</v>
-      </c>
-      <c r="R96" t="s">
-        <v>112</v>
-      </c>
-      <c r="S96">
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="97" spans="1:19">
-      <c r="A97" t="s">
-        <v>19</v>
-      </c>
-      <c r="B97" t="s">
-        <v>20</v>
-      </c>
-      <c r="C97" t="s">
-        <v>21</v>
-      </c>
-      <c r="D97" t="s">
-        <v>24</v>
-      </c>
-      <c r="E97" t="s">
-        <v>29</v>
-      </c>
-      <c r="F97">
-        <v>546</v>
-      </c>
-      <c r="G97" t="s">
-        <v>92</v>
-      </c>
-      <c r="H97">
-        <v>30.144184</v>
-      </c>
-      <c r="I97">
-        <v>74.122771</v>
-      </c>
-      <c r="J97" t="s">
-        <v>110</v>
-      </c>
-      <c r="K97">
-        <v>407</v>
-      </c>
-      <c r="L97" t="s">
-        <v>111</v>
-      </c>
-      <c r="M97" t="s">
-        <v>21</v>
-      </c>
-      <c r="N97" t="s">
-        <v>24</v>
-      </c>
-      <c r="O97" t="s">
-        <v>29</v>
-      </c>
-      <c r="P97">
-        <v>30.126927</v>
-      </c>
-      <c r="Q97">
-        <v>74.161942</v>
-      </c>
-      <c r="R97" t="s">
-        <v>112</v>
-      </c>
-      <c r="S97">
-        <v>12630.5</v>
-      </c>
-    </row>
-    <row r="98" spans="1:19">
-      <c r="A98" t="s">
-        <v>19</v>
-      </c>
-      <c r="B98" t="s">
-        <v>20</v>
-      </c>
-      <c r="C98" t="s">
-        <v>21</v>
-      </c>
-      <c r="D98" t="s">
-        <v>24</v>
-      </c>
-      <c r="E98" t="s">
-        <v>29</v>
-      </c>
-      <c r="F98">
-        <v>547</v>
-      </c>
-      <c r="G98" t="s">
-        <v>93</v>
-      </c>
-      <c r="H98">
-        <v>30.161715</v>
-      </c>
-      <c r="I98">
-        <v>73.987483</v>
-      </c>
-      <c r="J98" t="s">
-        <v>110</v>
-      </c>
-      <c r="K98">
-        <v>407</v>
-      </c>
-      <c r="L98" t="s">
-        <v>111</v>
-      </c>
-      <c r="M98" t="s">
-        <v>21</v>
-      </c>
-      <c r="N98" t="s">
-        <v>24</v>
-      </c>
-      <c r="O98" t="s">
-        <v>29</v>
-      </c>
-      <c r="P98">
-        <v>30.126927</v>
-      </c>
-      <c r="Q98">
-        <v>74.161942</v>
-      </c>
-      <c r="R98" t="s">
-        <v>112</v>
-      </c>
-      <c r="S98">
-        <v>13803</v>
-      </c>
-    </row>
-    <row r="99" spans="1:19">
-      <c r="A99" t="s">
-        <v>19</v>
-      </c>
-      <c r="B99" t="s">
-        <v>20</v>
-      </c>
-      <c r="C99" t="s">
-        <v>21</v>
-      </c>
-      <c r="D99" t="s">
-        <v>24</v>
-      </c>
-      <c r="E99" t="s">
-        <v>29</v>
-      </c>
-      <c r="F99">
-        <v>548</v>
-      </c>
-      <c r="G99" t="s">
-        <v>94</v>
-      </c>
-      <c r="H99">
-        <v>30.21135</v>
-      </c>
-      <c r="I99">
-        <v>74.02397999999999</v>
-      </c>
-      <c r="J99" t="s">
-        <v>110</v>
-      </c>
-      <c r="K99">
-        <v>400</v>
-      </c>
-      <c r="L99" t="s">
-        <v>111</v>
-      </c>
-      <c r="M99" t="s">
-        <v>21</v>
-      </c>
-      <c r="N99" t="s">
-        <v>24</v>
-      </c>
-      <c r="O99" t="s">
-        <v>29</v>
-      </c>
-      <c r="P99">
-        <v>30.15809938</v>
-      </c>
-      <c r="Q99">
-        <v>74.16401603</v>
-      </c>
-      <c r="R99" t="s">
-        <v>112</v>
-      </c>
-      <c r="S99">
-        <v>9145</v>
-      </c>
-    </row>
-    <row r="100" spans="1:19">
-      <c r="A100" t="s">
-        <v>19</v>
-      </c>
-      <c r="B100" t="s">
-        <v>20</v>
-      </c>
-      <c r="C100" t="s">
-        <v>21</v>
-      </c>
-      <c r="D100" t="s">
-        <v>24</v>
-      </c>
-      <c r="E100" t="s">
-        <v>29</v>
-      </c>
-      <c r="F100">
-        <v>549</v>
-      </c>
-      <c r="G100" t="s">
-        <v>95</v>
-      </c>
-      <c r="H100">
-        <v>30.296726</v>
-      </c>
-      <c r="I100">
-        <v>74.263169</v>
-      </c>
-      <c r="J100" t="s">
-        <v>110</v>
-      </c>
-      <c r="K100">
-        <v>401</v>
-      </c>
-      <c r="L100" t="s">
-        <v>111</v>
-      </c>
-      <c r="M100" t="s">
-        <v>21</v>
-      </c>
-      <c r="N100" t="s">
-        <v>24</v>
-      </c>
-      <c r="O100" t="s">
-        <v>29</v>
-      </c>
-      <c r="P100">
-        <v>30.17081207</v>
-      </c>
-      <c r="Q100">
-        <v>74.18179719</v>
-      </c>
-      <c r="R100" t="s">
-        <v>112</v>
-      </c>
-      <c r="S100">
-        <v>17622.5</v>
-      </c>
-    </row>
-    <row r="101" spans="1:19">
-      <c r="A101" t="s">
-        <v>19</v>
-      </c>
-      <c r="B101" t="s">
-        <v>20</v>
-      </c>
-      <c r="C101" t="s">
-        <v>21</v>
-      </c>
-      <c r="D101" t="s">
-        <v>24</v>
-      </c>
-      <c r="E101" t="s">
-        <v>29</v>
-      </c>
-      <c r="F101">
-        <v>550</v>
-      </c>
-      <c r="G101" t="s">
-        <v>96</v>
-      </c>
-      <c r="H101">
-        <v>30.285139</v>
-      </c>
-      <c r="I101">
-        <v>74.172681</v>
-      </c>
-      <c r="J101" t="s">
-        <v>110</v>
-      </c>
-      <c r="K101">
-        <v>402</v>
-      </c>
-      <c r="L101" t="s">
-        <v>111</v>
-      </c>
-      <c r="M101" t="s">
-        <v>21</v>
-      </c>
-      <c r="N101" t="s">
-        <v>24</v>
-      </c>
-      <c r="O101" t="s">
-        <v>29</v>
-      </c>
-      <c r="P101">
-        <v>30.17767461</v>
-      </c>
-      <c r="Q101">
-        <v>74.17723581</v>
-      </c>
-      <c r="R101" t="s">
-        <v>112</v>
-      </c>
-      <c r="S101">
-        <v>42685</v>
-      </c>
-    </row>
-    <row r="102" spans="1:19">
-      <c r="A102" t="s">
-        <v>19</v>
-      </c>
-      <c r="B102" t="s">
-        <v>20</v>
-      </c>
-      <c r="C102" t="s">
-        <v>21</v>
-      </c>
-      <c r="D102" t="s">
-        <v>24</v>
-      </c>
-      <c r="E102" t="s">
-        <v>29</v>
-      </c>
-      <c r="F102">
-        <v>551</v>
-      </c>
-      <c r="G102" t="s">
-        <v>97</v>
-      </c>
-      <c r="H102">
-        <v>30.260814</v>
-      </c>
-      <c r="I102">
-        <v>74.269329</v>
-      </c>
-      <c r="J102" t="s">
-        <v>110</v>
-      </c>
-      <c r="K102">
-        <v>401</v>
-      </c>
-      <c r="L102" t="s">
-        <v>111</v>
-      </c>
-      <c r="M102" t="s">
-        <v>21</v>
-      </c>
-      <c r="N102" t="s">
-        <v>24</v>
-      </c>
-      <c r="O102" t="s">
-        <v>29</v>
-      </c>
-      <c r="P102">
-        <v>30.17081207</v>
-      </c>
-      <c r="Q102">
-        <v>74.18179719</v>
-      </c>
-      <c r="R102" t="s">
-        <v>112</v>
-      </c>
-      <c r="S102">
-        <v>56502.5</v>
-      </c>
-    </row>
-    <row r="103" spans="1:19">
-      <c r="A103" t="s">
-        <v>19</v>
-      </c>
-      <c r="B103" t="s">
-        <v>20</v>
-      </c>
-      <c r="C103" t="s">
-        <v>21</v>
-      </c>
-      <c r="D103" t="s">
-        <v>24</v>
-      </c>
-      <c r="E103" t="s">
-        <v>29</v>
-      </c>
-      <c r="F103">
-        <v>552</v>
-      </c>
-      <c r="G103" t="s">
-        <v>98</v>
-      </c>
-      <c r="H103">
-        <v>30.290503</v>
-      </c>
-      <c r="I103">
-        <v>74.220803</v>
-      </c>
-      <c r="J103" t="s">
-        <v>110</v>
-      </c>
-      <c r="K103">
-        <v>401</v>
-      </c>
-      <c r="L103" t="s">
-        <v>111</v>
-      </c>
-      <c r="M103" t="s">
-        <v>21</v>
-      </c>
-      <c r="N103" t="s">
-        <v>24</v>
-      </c>
-      <c r="O103" t="s">
-        <v>29</v>
-      </c>
-      <c r="P103">
-        <v>30.17081207</v>
-      </c>
-      <c r="Q103">
-        <v>74.18179719</v>
-      </c>
-      <c r="R103" t="s">
-        <v>112</v>
-      </c>
-      <c r="S103">
-        <v>43110</v>
-      </c>
-    </row>
-    <row r="104" spans="1:19">
-      <c r="A104" t="s">
-        <v>19</v>
-      </c>
-      <c r="B104" t="s">
-        <v>20</v>
-      </c>
-      <c r="C104" t="s">
-        <v>21</v>
-      </c>
-      <c r="D104" t="s">
-        <v>25</v>
-      </c>
-      <c r="E104" t="s">
-        <v>30</v>
-      </c>
-      <c r="F104">
-        <v>1046</v>
-      </c>
-      <c r="G104" t="s">
-        <v>99</v>
-      </c>
-      <c r="H104">
-        <v>31.425406</v>
-      </c>
-      <c r="I104">
-        <v>75.719528</v>
-      </c>
-      <c r="J104" t="s">
-        <v>110</v>
-      </c>
-      <c r="K104">
-        <v>625</v>
-      </c>
-      <c r="L104" t="s">
-        <v>111</v>
-      </c>
-      <c r="M104" t="s">
-        <v>21</v>
-      </c>
-      <c r="N104" t="s">
-        <v>25</v>
-      </c>
-      <c r="O104" t="s">
-        <v>30</v>
-      </c>
-      <c r="P104">
-        <v>31.408658</v>
-      </c>
-      <c r="Q104">
-        <v>75.685958</v>
-      </c>
-      <c r="R104" t="s">
-        <v>112</v>
-      </c>
-      <c r="S104">
-        <v>21500</v>
-      </c>
-    </row>
-    <row r="105" spans="1:19">
-      <c r="A105" t="s">
-        <v>19</v>
-      </c>
-      <c r="B105" t="s">
-        <v>20</v>
-      </c>
-      <c r="C105" t="s">
-        <v>21</v>
-      </c>
-      <c r="D105" t="s">
-        <v>22</v>
-      </c>
-      <c r="E105" t="s">
-        <v>31</v>
-      </c>
-      <c r="F105">
-        <v>54</v>
-      </c>
-      <c r="G105" t="s">
-        <v>100</v>
-      </c>
-      <c r="H105">
-        <v>31.6139708</v>
-      </c>
-      <c r="I105">
-        <v>75.3268413</v>
-      </c>
-      <c r="J105" t="s">
-        <v>110</v>
-      </c>
-      <c r="K105">
-        <v>21</v>
-      </c>
-      <c r="L105" t="s">
-        <v>111</v>
-      </c>
-      <c r="M105" t="s">
-        <v>21</v>
-      </c>
-      <c r="N105" t="s">
-        <v>22</v>
-      </c>
-      <c r="O105" t="s">
-        <v>31</v>
-      </c>
-      <c r="P105">
-        <v>31.6647538</v>
-      </c>
-      <c r="Q105">
-        <v>75.234335</v>
-      </c>
-      <c r="R105" t="s">
-        <v>112</v>
-      </c>
-      <c r="S105">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="106" spans="1:19">
-      <c r="A106" t="s">
-        <v>19</v>
-      </c>
-      <c r="B106" t="s">
-        <v>20</v>
-      </c>
-      <c r="C106" t="s">
-        <v>21</v>
-      </c>
-      <c r="D106" t="s">
-        <v>22</v>
-      </c>
-      <c r="E106" t="s">
-        <v>31</v>
-      </c>
-      <c r="F106">
-        <v>54</v>
-      </c>
-      <c r="G106" t="s">
-        <v>100</v>
-      </c>
-      <c r="H106">
-        <v>31.6139708</v>
-      </c>
-      <c r="I106">
-        <v>75.3268413</v>
-      </c>
-      <c r="J106" t="s">
-        <v>110</v>
-      </c>
-      <c r="K106">
-        <v>29</v>
-      </c>
-      <c r="L106" t="s">
-        <v>111</v>
-      </c>
-      <c r="M106" t="s">
-        <v>21</v>
-      </c>
-      <c r="N106" t="s">
-        <v>22</v>
-      </c>
-      <c r="O106" t="s">
-        <v>31</v>
-      </c>
-      <c r="P106">
-        <v>31.561626</v>
-      </c>
-      <c r="Q106">
-        <v>75.140022</v>
-      </c>
-      <c r="R106" t="s">
-        <v>112</v>
-      </c>
-      <c r="S106">
-        <v>31832.5</v>
-      </c>
-    </row>
-    <row r="107" spans="1:19">
-      <c r="A107" t="s">
-        <v>19</v>
-      </c>
-      <c r="B107" t="s">
-        <v>20</v>
-      </c>
-      <c r="C107" t="s">
-        <v>21</v>
-      </c>
-      <c r="D107" t="s">
-        <v>22</v>
-      </c>
-      <c r="E107" t="s">
-        <v>31</v>
-      </c>
-      <c r="F107">
-        <v>54</v>
-      </c>
-      <c r="G107" t="s">
-        <v>100</v>
-      </c>
-      <c r="H107">
-        <v>31.6139708</v>
-      </c>
-      <c r="I107">
-        <v>75.3268413</v>
-      </c>
-      <c r="J107" t="s">
-        <v>110</v>
-      </c>
-      <c r="K107">
-        <v>37</v>
-      </c>
-      <c r="L107" t="s">
-        <v>111</v>
-      </c>
-      <c r="M107" t="s">
-        <v>21</v>
-      </c>
-      <c r="N107" t="s">
-        <v>22</v>
-      </c>
-      <c r="O107" t="s">
-        <v>31</v>
-      </c>
-      <c r="P107">
-        <v>31.5547</v>
-      </c>
-      <c r="Q107">
-        <v>75.18429</v>
-      </c>
-      <c r="R107" t="s">
-        <v>112</v>
-      </c>
-      <c r="S107">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="108" spans="1:19">
-      <c r="A108" t="s">
-        <v>19</v>
-      </c>
-      <c r="B108" t="s">
-        <v>20</v>
-      </c>
-      <c r="C108" t="s">
-        <v>21</v>
-      </c>
-      <c r="D108" t="s">
-        <v>22</v>
-      </c>
-      <c r="E108" t="s">
-        <v>31</v>
-      </c>
-      <c r="F108">
-        <v>54</v>
-      </c>
-      <c r="G108" t="s">
-        <v>100</v>
-      </c>
-      <c r="H108">
-        <v>31.6139708</v>
-      </c>
-      <c r="I108">
-        <v>75.3268413</v>
-      </c>
-      <c r="J108" t="s">
-        <v>110</v>
-      </c>
-      <c r="K108">
-        <v>44</v>
-      </c>
-      <c r="L108" t="s">
-        <v>111</v>
-      </c>
-      <c r="M108" t="s">
-        <v>21</v>
-      </c>
-      <c r="N108" t="s">
-        <v>22</v>
-      </c>
-      <c r="O108" t="s">
-        <v>31</v>
-      </c>
-      <c r="P108">
-        <v>31.51572</v>
-      </c>
-      <c r="Q108">
-        <v>75.28874</v>
-      </c>
-      <c r="R108" t="s">
-        <v>112</v>
-      </c>
-      <c r="S108">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="109" spans="1:19">
-      <c r="A109" t="s">
-        <v>19</v>
-      </c>
-      <c r="B109" t="s">
-        <v>20</v>
-      </c>
-      <c r="C109" t="s">
-        <v>21</v>
-      </c>
-      <c r="D109" t="s">
-        <v>22</v>
-      </c>
-      <c r="E109" t="s">
-        <v>31</v>
-      </c>
-      <c r="F109">
-        <v>55</v>
-      </c>
-      <c r="G109" t="s">
-        <v>101</v>
-      </c>
-      <c r="H109">
-        <v>31.5988078</v>
-      </c>
-      <c r="I109">
-        <v>75.2009982</v>
-      </c>
-      <c r="J109" t="s">
-        <v>110</v>
-      </c>
-      <c r="K109">
-        <v>29</v>
-      </c>
-      <c r="L109" t="s">
-        <v>111</v>
-      </c>
-      <c r="M109" t="s">
-        <v>21</v>
-      </c>
-      <c r="N109" t="s">
-        <v>22</v>
-      </c>
-      <c r="O109" t="s">
-        <v>31</v>
-      </c>
-      <c r="P109">
-        <v>31.561626</v>
-      </c>
-      <c r="Q109">
-        <v>75.140022</v>
-      </c>
-      <c r="R109" t="s">
-        <v>112</v>
-      </c>
-      <c r="S109">
-        <v>17174.5</v>
-      </c>
-    </row>
-    <row r="110" spans="1:19">
-      <c r="A110" t="s">
-        <v>19</v>
-      </c>
-      <c r="B110" t="s">
-        <v>20</v>
-      </c>
-      <c r="C110" t="s">
-        <v>21</v>
-      </c>
-      <c r="D110" t="s">
-        <v>22</v>
-      </c>
-      <c r="E110" t="s">
-        <v>31</v>
-      </c>
-      <c r="F110">
-        <v>56</v>
-      </c>
-      <c r="G110" t="s">
-        <v>102</v>
-      </c>
-      <c r="H110">
-        <v>31.5495084</v>
-      </c>
-      <c r="I110">
-        <v>75.1740551</v>
-      </c>
-      <c r="J110" t="s">
-        <v>110</v>
-      </c>
-      <c r="K110">
-        <v>29</v>
-      </c>
-      <c r="L110" t="s">
-        <v>111</v>
-      </c>
-      <c r="M110" t="s">
-        <v>21</v>
-      </c>
-      <c r="N110" t="s">
-        <v>22</v>
-      </c>
-      <c r="O110" t="s">
-        <v>31</v>
-      </c>
-      <c r="P110">
-        <v>31.561626</v>
-      </c>
-      <c r="Q110">
-        <v>75.140022</v>
-      </c>
-      <c r="R110" t="s">
-        <v>112</v>
-      </c>
-      <c r="S110">
-        <v>25993</v>
-      </c>
-    </row>
-    <row r="111" spans="1:19">
-      <c r="A111" t="s">
-        <v>19</v>
-      </c>
-      <c r="B111" t="s">
-        <v>20</v>
-      </c>
-      <c r="C111" t="s">
-        <v>21</v>
-      </c>
-      <c r="D111" t="s">
-        <v>22</v>
-      </c>
-      <c r="E111" t="s">
-        <v>31</v>
-      </c>
-      <c r="F111">
-        <v>57</v>
-      </c>
-      <c r="G111" t="s">
-        <v>103</v>
-      </c>
-      <c r="H111">
-        <v>31.5394842</v>
-      </c>
-      <c r="I111">
-        <v>75.24014649999999</v>
-      </c>
-      <c r="J111" t="s">
-        <v>110</v>
-      </c>
-      <c r="K111">
-        <v>19</v>
-      </c>
-      <c r="L111" t="s">
-        <v>111</v>
-      </c>
-      <c r="M111" t="s">
-        <v>21</v>
-      </c>
-      <c r="N111" t="s">
-        <v>22</v>
-      </c>
-      <c r="O111" t="s">
-        <v>31</v>
-      </c>
-      <c r="P111">
-        <v>31.543266</v>
-      </c>
-      <c r="Q111">
-        <v>75.21952</v>
-      </c>
-      <c r="R111" t="s">
-        <v>112</v>
-      </c>
-      <c r="S111">
-        <v>190000</v>
-      </c>
-    </row>
-    <row r="112" spans="1:19">
-      <c r="A112" t="s">
-        <v>19</v>
-      </c>
-      <c r="B112" t="s">
-        <v>20</v>
-      </c>
-      <c r="C112" t="s">
-        <v>21</v>
-      </c>
-      <c r="D112" t="s">
-        <v>22</v>
-      </c>
-      <c r="E112" t="s">
-        <v>31</v>
-      </c>
-      <c r="F112">
-        <v>57</v>
-      </c>
-      <c r="G112" t="s">
-        <v>103</v>
-      </c>
-      <c r="H112">
-        <v>31.5394842</v>
-      </c>
-      <c r="I112">
-        <v>75.24014649999999</v>
-      </c>
-      <c r="J112" t="s">
-        <v>110</v>
-      </c>
-      <c r="K112">
-        <v>20</v>
-      </c>
-      <c r="L112" t="s">
-        <v>111</v>
-      </c>
-      <c r="M112" t="s">
-        <v>21</v>
-      </c>
-      <c r="N112" t="s">
-        <v>22</v>
-      </c>
-      <c r="O112" t="s">
-        <v>31</v>
-      </c>
-      <c r="P112">
-        <v>31.543724</v>
-      </c>
-      <c r="Q112">
-        <v>75.21528600000001</v>
-      </c>
-      <c r="R112" t="s">
-        <v>112</v>
-      </c>
-      <c r="S112">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="113" spans="1:19">
-      <c r="A113" t="s">
-        <v>19</v>
-      </c>
-      <c r="B113" t="s">
-        <v>20</v>
-      </c>
-      <c r="C113" t="s">
-        <v>21</v>
-      </c>
-      <c r="D113" t="s">
-        <v>22</v>
-      </c>
-      <c r="E113" t="s">
-        <v>31</v>
-      </c>
-      <c r="F113">
-        <v>57</v>
-      </c>
-      <c r="G113" t="s">
-        <v>103</v>
-      </c>
-      <c r="H113">
-        <v>31.5394842</v>
-      </c>
-      <c r="I113">
-        <v>75.24014649999999</v>
-      </c>
-      <c r="J113" t="s">
-        <v>110</v>
-      </c>
-      <c r="K113">
-        <v>27</v>
-      </c>
-      <c r="L113" t="s">
-        <v>111</v>
-      </c>
-      <c r="M113" t="s">
-        <v>21</v>
-      </c>
-      <c r="N113" t="s">
-        <v>22</v>
-      </c>
-      <c r="O113" t="s">
-        <v>31</v>
-      </c>
-      <c r="P113">
-        <v>31.539066</v>
-      </c>
-      <c r="Q113">
-        <v>75.244698</v>
-      </c>
-      <c r="R113" t="s">
-        <v>112</v>
-      </c>
-      <c r="S113">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="114" spans="1:19">
-      <c r="A114" t="s">
-        <v>19</v>
-      </c>
-      <c r="B114" t="s">
-        <v>20</v>
-      </c>
-      <c r="C114" t="s">
-        <v>21</v>
-      </c>
-      <c r="D114" t="s">
-        <v>22</v>
-      </c>
-      <c r="E114" t="s">
-        <v>31</v>
-      </c>
-      <c r="F114">
-        <v>57</v>
-      </c>
-      <c r="G114" t="s">
-        <v>103</v>
-      </c>
-      <c r="H114">
-        <v>31.5394842</v>
-      </c>
-      <c r="I114">
-        <v>75.24014649999999</v>
-      </c>
-      <c r="J114" t="s">
-        <v>110</v>
-      </c>
-      <c r="K114">
-        <v>28</v>
-      </c>
-      <c r="L114" t="s">
-        <v>111</v>
-      </c>
-      <c r="M114" t="s">
-        <v>21</v>
-      </c>
-      <c r="N114" t="s">
-        <v>22</v>
-      </c>
-      <c r="O114" t="s">
-        <v>31</v>
-      </c>
-      <c r="P114">
-        <v>31.539066</v>
-      </c>
-      <c r="Q114">
-        <v>75.244698</v>
-      </c>
-      <c r="R114" t="s">
-        <v>112</v>
-      </c>
-      <c r="S114">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="115" spans="1:19">
-      <c r="A115" t="s">
-        <v>19</v>
-      </c>
-      <c r="B115" t="s">
-        <v>20</v>
-      </c>
-      <c r="C115" t="s">
-        <v>21</v>
-      </c>
-      <c r="D115" t="s">
-        <v>22</v>
-      </c>
-      <c r="E115" t="s">
-        <v>31</v>
-      </c>
-      <c r="F115">
-        <v>57</v>
-      </c>
-      <c r="G115" t="s">
-        <v>103</v>
-      </c>
-      <c r="H115">
-        <v>31.5394842</v>
-      </c>
-      <c r="I115">
-        <v>75.24014649999999</v>
-      </c>
-      <c r="J115" t="s">
-        <v>110</v>
-      </c>
-      <c r="K115">
-        <v>36</v>
-      </c>
-      <c r="L115" t="s">
-        <v>111</v>
-      </c>
-      <c r="M115" t="s">
-        <v>21</v>
-      </c>
-      <c r="N115" t="s">
-        <v>22</v>
-      </c>
-      <c r="O115" t="s">
-        <v>31</v>
-      </c>
-      <c r="P115">
-        <v>31.5547</v>
-      </c>
-      <c r="Q115">
-        <v>75.18429</v>
-      </c>
-      <c r="R115" t="s">
-        <v>112</v>
-      </c>
-      <c r="S115">
-        <v>17870</v>
-      </c>
-    </row>
-    <row r="116" spans="1:19">
-      <c r="A116" t="s">
-        <v>19</v>
-      </c>
-      <c r="B116" t="s">
-        <v>20</v>
-      </c>
-      <c r="C116" t="s">
-        <v>21</v>
-      </c>
-      <c r="D116" t="s">
-        <v>22</v>
-      </c>
-      <c r="E116" t="s">
-        <v>31</v>
-      </c>
-      <c r="F116">
-        <v>57</v>
-      </c>
-      <c r="G116" t="s">
-        <v>103</v>
-      </c>
-      <c r="H116">
-        <v>31.5394842</v>
-      </c>
-      <c r="I116">
-        <v>75.24014649999999</v>
-      </c>
-      <c r="J116" t="s">
-        <v>110</v>
-      </c>
-      <c r="K116">
-        <v>37</v>
-      </c>
-      <c r="L116" t="s">
-        <v>111</v>
-      </c>
-      <c r="M116" t="s">
-        <v>21</v>
-      </c>
-      <c r="N116" t="s">
-        <v>22</v>
-      </c>
-      <c r="O116" t="s">
-        <v>31</v>
-      </c>
-      <c r="P116">
-        <v>31.5547</v>
-      </c>
-      <c r="Q116">
-        <v>75.18429</v>
-      </c>
-      <c r="R116" t="s">
-        <v>112</v>
-      </c>
-      <c r="S116">
-        <v>38457</v>
-      </c>
-    </row>
-    <row r="117" spans="1:19">
-      <c r="A117" t="s">
-        <v>19</v>
-      </c>
-      <c r="B117" t="s">
-        <v>20</v>
-      </c>
-      <c r="C117" t="s">
-        <v>21</v>
-      </c>
-      <c r="D117" t="s">
-        <v>22</v>
-      </c>
-      <c r="E117" t="s">
-        <v>31</v>
-      </c>
-      <c r="F117">
-        <v>57</v>
-      </c>
-      <c r="G117" t="s">
-        <v>103</v>
-      </c>
-      <c r="H117">
-        <v>31.5394842</v>
-      </c>
-      <c r="I117">
-        <v>75.24014649999999</v>
-      </c>
-      <c r="J117" t="s">
-        <v>110</v>
-      </c>
-      <c r="K117">
-        <v>43</v>
-      </c>
-      <c r="L117" t="s">
-        <v>111</v>
-      </c>
-      <c r="M117" t="s">
-        <v>21</v>
-      </c>
-      <c r="N117" t="s">
-        <v>22</v>
-      </c>
-      <c r="O117" t="s">
-        <v>31</v>
-      </c>
-      <c r="P117">
-        <v>31.53422</v>
-      </c>
-      <c r="Q117">
-        <v>75.2328</v>
-      </c>
-      <c r="R117" t="s">
-        <v>112</v>
-      </c>
-      <c r="S117">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="118" spans="1:19">
-      <c r="A118" t="s">
-        <v>19</v>
-      </c>
-      <c r="B118" t="s">
-        <v>20</v>
-      </c>
-      <c r="C118" t="s">
-        <v>21</v>
-      </c>
-      <c r="D118" t="s">
-        <v>22</v>
-      </c>
-      <c r="E118" t="s">
-        <v>31</v>
-      </c>
-      <c r="F118">
-        <v>58</v>
-      </c>
-      <c r="G118" t="s">
-        <v>104</v>
-      </c>
-      <c r="H118">
-        <v>31.57488036</v>
-      </c>
-      <c r="I118">
-        <v>75.28466821000001</v>
-      </c>
-      <c r="J118" t="s">
-        <v>110</v>
-      </c>
-      <c r="K118">
-        <v>17</v>
-      </c>
-      <c r="L118" t="s">
-        <v>111</v>
-      </c>
-      <c r="M118" t="s">
-        <v>21</v>
-      </c>
-      <c r="N118" t="s">
-        <v>22</v>
-      </c>
-      <c r="O118" t="s">
-        <v>31</v>
-      </c>
-      <c r="P118">
-        <v>31.52691932</v>
-      </c>
-      <c r="Q118">
-        <v>75.26848901</v>
-      </c>
-      <c r="R118" t="s">
-        <v>112</v>
-      </c>
-      <c r="S118">
-        <v>17500</v>
-      </c>
-    </row>
-    <row r="119" spans="1:19">
-      <c r="A119" t="s">
-        <v>19</v>
-      </c>
-      <c r="B119" t="s">
-        <v>20</v>
-      </c>
-      <c r="C119" t="s">
-        <v>21</v>
-      </c>
-      <c r="D119" t="s">
-        <v>22</v>
-      </c>
-      <c r="E119" t="s">
-        <v>31</v>
-      </c>
-      <c r="F119">
-        <v>58</v>
-      </c>
-      <c r="G119" t="s">
-        <v>104</v>
-      </c>
-      <c r="H119">
-        <v>31.57488036</v>
-      </c>
-      <c r="I119">
-        <v>75.28466821000001</v>
-      </c>
-      <c r="J119" t="s">
-        <v>110</v>
-      </c>
-      <c r="K119">
-        <v>18</v>
-      </c>
-      <c r="L119" t="s">
-        <v>111</v>
-      </c>
-      <c r="M119" t="s">
-        <v>21</v>
-      </c>
-      <c r="N119" t="s">
-        <v>22</v>
-      </c>
-      <c r="O119" t="s">
-        <v>31</v>
-      </c>
-      <c r="P119">
-        <v>31.52693009</v>
-      </c>
-      <c r="Q119">
-        <v>75.26852979</v>
-      </c>
-      <c r="R119" t="s">
-        <v>112</v>
-      </c>
-      <c r="S119">
-        <v>17500</v>
-      </c>
-    </row>
-    <row r="120" spans="1:19">
-      <c r="A120" t="s">
-        <v>19</v>
-      </c>
-      <c r="B120" t="s">
-        <v>20</v>
-      </c>
-      <c r="C120" t="s">
-        <v>21</v>
-      </c>
-      <c r="D120" t="s">
-        <v>22</v>
-      </c>
-      <c r="E120" t="s">
-        <v>31</v>
-      </c>
-      <c r="F120">
-        <v>58</v>
-      </c>
-      <c r="G120" t="s">
-        <v>104</v>
-      </c>
-      <c r="H120">
-        <v>31.57488036</v>
-      </c>
-      <c r="I120">
-        <v>75.28466821000001</v>
-      </c>
-      <c r="J120" t="s">
-        <v>110</v>
-      </c>
-      <c r="K120">
-        <v>35</v>
-      </c>
-      <c r="L120" t="s">
-        <v>111</v>
-      </c>
-      <c r="M120" t="s">
-        <v>21</v>
-      </c>
-      <c r="N120" t="s">
-        <v>22</v>
-      </c>
-      <c r="O120" t="s">
-        <v>31</v>
-      </c>
-      <c r="P120">
-        <v>31.55489</v>
-      </c>
-      <c r="Q120">
-        <v>75.18541999999999</v>
-      </c>
-      <c r="R120" t="s">
-        <v>112</v>
-      </c>
-      <c r="S120">
-        <v>7070</v>
-      </c>
-    </row>
-    <row r="121" spans="1:19">
-      <c r="A121" t="s">
-        <v>19</v>
-      </c>
-      <c r="B121" t="s">
-        <v>20</v>
-      </c>
-      <c r="C121" t="s">
-        <v>21</v>
-      </c>
-      <c r="D121" t="s">
-        <v>22</v>
-      </c>
-      <c r="E121" t="s">
-        <v>31</v>
-      </c>
-      <c r="F121">
-        <v>58</v>
-      </c>
-      <c r="G121" t="s">
-        <v>104</v>
-      </c>
-      <c r="H121">
-        <v>31.57488036</v>
-      </c>
-      <c r="I121">
-        <v>75.28466821000001</v>
-      </c>
-      <c r="J121" t="s">
-        <v>110</v>
-      </c>
-      <c r="K121">
-        <v>37</v>
-      </c>
-      <c r="L121" t="s">
-        <v>111</v>
-      </c>
-      <c r="M121" t="s">
-        <v>21</v>
-      </c>
-      <c r="N121" t="s">
-        <v>22</v>
-      </c>
-      <c r="O121" t="s">
-        <v>31</v>
-      </c>
-      <c r="P121">
-        <v>31.5547</v>
-      </c>
-      <c r="Q121">
-        <v>75.18429</v>
-      </c>
-      <c r="R121" t="s">
-        <v>112</v>
-      </c>
-      <c r="S121">
-        <v>90831</v>
-      </c>
-    </row>
-    <row r="122" spans="1:19">
-      <c r="A122" t="s">
-        <v>19</v>
-      </c>
-      <c r="B122" t="s">
-        <v>20</v>
-      </c>
-      <c r="C122" t="s">
-        <v>21</v>
-      </c>
-      <c r="D122" t="s">
-        <v>22</v>
-      </c>
-      <c r="E122" t="s">
-        <v>32</v>
-      </c>
-      <c r="F122">
-        <v>23</v>
-      </c>
-      <c r="G122" t="s">
-        <v>105</v>
-      </c>
-      <c r="H122">
-        <v>31.7398221</v>
-      </c>
-      <c r="I122">
-        <v>74.6072853</v>
-      </c>
-      <c r="J122" t="s">
-        <v>110</v>
-      </c>
-      <c r="K122">
-        <v>5</v>
-      </c>
-      <c r="L122" t="s">
-        <v>111</v>
-      </c>
-      <c r="M122" t="s">
-        <v>21</v>
-      </c>
-      <c r="N122" t="s">
-        <v>22</v>
-      </c>
-      <c r="O122" t="s">
-        <v>32</v>
-      </c>
-      <c r="P122">
-        <v>31.800077</v>
-      </c>
-      <c r="Q122">
-        <v>74.588493</v>
-      </c>
-      <c r="R122" t="s">
-        <v>112</v>
-      </c>
-      <c r="S122">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="123" spans="1:19">
-      <c r="A123" t="s">
-        <v>19</v>
-      </c>
-      <c r="B123" t="s">
-        <v>20</v>
-      </c>
-      <c r="C123" t="s">
-        <v>21</v>
-      </c>
-      <c r="D123" t="s">
-        <v>22</v>
-      </c>
-      <c r="E123" t="s">
-        <v>32</v>
-      </c>
-      <c r="F123">
-        <v>24</v>
-      </c>
-      <c r="G123" t="s">
-        <v>106</v>
-      </c>
-      <c r="H123">
-        <v>31.70149744</v>
-      </c>
-      <c r="I123">
-        <v>74.65969907</v>
-      </c>
-      <c r="J123" t="s">
-        <v>110</v>
-      </c>
-      <c r="K123">
-        <v>11</v>
-      </c>
-      <c r="L123" t="s">
-        <v>111</v>
-      </c>
-      <c r="M123" t="s">
-        <v>21</v>
-      </c>
-      <c r="N123" t="s">
-        <v>22</v>
-      </c>
-      <c r="O123" t="s">
-        <v>32</v>
-      </c>
-      <c r="P123">
-        <v>31.70219884</v>
-      </c>
-      <c r="Q123">
-        <v>74.68916134</v>
-      </c>
-      <c r="R123" t="s">
-        <v>112</v>
-      </c>
-      <c r="S123">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="124" spans="1:19">
-      <c r="A124" t="s">
-        <v>19</v>
-      </c>
-      <c r="B124" t="s">
-        <v>20</v>
-      </c>
-      <c r="C124" t="s">
-        <v>21</v>
-      </c>
-      <c r="D124" t="s">
-        <v>22</v>
-      </c>
-      <c r="E124" t="s">
-        <v>32</v>
-      </c>
-      <c r="F124">
-        <v>24</v>
-      </c>
-      <c r="G124" t="s">
-        <v>106</v>
-      </c>
-      <c r="H124">
-        <v>31.70149744</v>
-      </c>
-      <c r="I124">
-        <v>74.65969907</v>
-      </c>
-      <c r="J124" t="s">
-        <v>110</v>
-      </c>
-      <c r="K124">
-        <v>12</v>
-      </c>
-      <c r="L124" t="s">
-        <v>111</v>
-      </c>
-      <c r="M124" t="s">
-        <v>21</v>
-      </c>
-      <c r="N124" t="s">
-        <v>22</v>
-      </c>
-      <c r="O124" t="s">
-        <v>32</v>
-      </c>
-      <c r="P124">
-        <v>31.703294</v>
-      </c>
-      <c r="Q124">
-        <v>74.69096380000001</v>
-      </c>
-      <c r="R124" t="s">
-        <v>112</v>
-      </c>
-      <c r="S124">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="125" spans="1:19">
-      <c r="A125" t="s">
-        <v>19</v>
-      </c>
-      <c r="B125" t="s">
-        <v>20</v>
-      </c>
-      <c r="C125" t="s">
-        <v>21</v>
-      </c>
-      <c r="D125" t="s">
-        <v>22</v>
-      </c>
-      <c r="E125" t="s">
-        <v>33</v>
-      </c>
-      <c r="F125">
-        <v>36</v>
-      </c>
-      <c r="G125" t="s">
-        <v>107</v>
-      </c>
-      <c r="H125">
-        <v>31.5710787</v>
-      </c>
-      <c r="I125">
-        <v>75.0424861</v>
-      </c>
-      <c r="J125" t="s">
-        <v>110</v>
-      </c>
-      <c r="K125">
-        <v>13</v>
-      </c>
-      <c r="L125" t="s">
-        <v>111</v>
-      </c>
-      <c r="M125" t="s">
-        <v>21</v>
-      </c>
-      <c r="N125" t="s">
-        <v>22</v>
-      </c>
-      <c r="O125" t="s">
-        <v>33</v>
-      </c>
-      <c r="P125">
-        <v>31.56972149</v>
-      </c>
-      <c r="Q125">
-        <v>75.09414523</v>
-      </c>
-      <c r="R125" t="s">
-        <v>112</v>
-      </c>
-      <c r="S125">
-        <v>5511</v>
-      </c>
-    </row>
-    <row r="126" spans="1:19">
-      <c r="A126" t="s">
-        <v>19</v>
-      </c>
-      <c r="B126" t="s">
-        <v>20</v>
-      </c>
-      <c r="C126" t="s">
-        <v>21</v>
-      </c>
-      <c r="D126" t="s">
-        <v>22</v>
-      </c>
-      <c r="E126" t="s">
-        <v>33</v>
-      </c>
-      <c r="F126">
-        <v>36</v>
-      </c>
-      <c r="G126" t="s">
-        <v>107</v>
-      </c>
-      <c r="H126">
-        <v>31.5710787</v>
-      </c>
-      <c r="I126">
-        <v>75.0424861</v>
-      </c>
-      <c r="J126" t="s">
-        <v>110</v>
-      </c>
-      <c r="K126">
-        <v>14</v>
-      </c>
-      <c r="L126" t="s">
-        <v>111</v>
-      </c>
-      <c r="M126" t="s">
-        <v>21</v>
-      </c>
-      <c r="N126" t="s">
-        <v>22</v>
-      </c>
-      <c r="O126" t="s">
-        <v>33</v>
-      </c>
-      <c r="P126">
-        <v>31.45335</v>
-      </c>
-      <c r="Q126">
-        <v>74.46541999999999</v>
-      </c>
-      <c r="R126" t="s">
-        <v>112</v>
-      </c>
-      <c r="S126">
-        <v>70000</v>
-      </c>
-    </row>
-    <row r="127" spans="1:19">
-      <c r="A127" t="s">
-        <v>19</v>
-      </c>
-      <c r="B127" t="s">
-        <v>20</v>
-      </c>
-      <c r="C127" t="s">
-        <v>21</v>
-      </c>
-      <c r="D127" t="s">
-        <v>22</v>
-      </c>
-      <c r="E127" t="s">
-        <v>33</v>
-      </c>
-      <c r="F127">
-        <v>36</v>
-      </c>
-      <c r="G127" t="s">
-        <v>107</v>
-      </c>
-      <c r="H127">
-        <v>31.5710787</v>
-      </c>
-      <c r="I127">
-        <v>75.0424861</v>
-      </c>
-      <c r="J127" t="s">
-        <v>110</v>
-      </c>
-      <c r="K127">
-        <v>30</v>
-      </c>
-      <c r="L127" t="s">
-        <v>111</v>
-      </c>
-      <c r="M127" t="s">
-        <v>21</v>
-      </c>
-      <c r="N127" t="s">
-        <v>22</v>
-      </c>
-      <c r="O127" t="s">
-        <v>33</v>
-      </c>
-      <c r="P127">
-        <v>31.571434</v>
-      </c>
-      <c r="Q127">
-        <v>75.048013</v>
-      </c>
-      <c r="R127" t="s">
-        <v>112</v>
-      </c>
-      <c r="S127">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="128" spans="1:19">
-      <c r="A128" t="s">
-        <v>19</v>
-      </c>
-      <c r="B128" t="s">
-        <v>20</v>
-      </c>
-      <c r="C128" t="s">
-        <v>21</v>
-      </c>
-      <c r="D128" t="s">
-        <v>22</v>
-      </c>
-      <c r="E128" t="s">
-        <v>33</v>
-      </c>
-      <c r="F128">
-        <v>36</v>
-      </c>
-      <c r="G128" t="s">
-        <v>107</v>
-      </c>
-      <c r="H128">
-        <v>31.5710787</v>
-      </c>
-      <c r="I128">
-        <v>75.0424861</v>
-      </c>
-      <c r="J128" t="s">
-        <v>110</v>
-      </c>
-      <c r="K128">
-        <v>31</v>
-      </c>
-      <c r="L128" t="s">
-        <v>111</v>
-      </c>
-      <c r="M128" t="s">
-        <v>21</v>
-      </c>
-      <c r="N128" t="s">
-        <v>22</v>
-      </c>
-      <c r="O128" t="s">
-        <v>33</v>
-      </c>
-      <c r="P128">
-        <v>31.583519</v>
-      </c>
-      <c r="Q128">
-        <v>75.049741</v>
-      </c>
-      <c r="R128" t="s">
-        <v>112</v>
-      </c>
-      <c r="S128">
-        <v>10500</v>
-      </c>
-    </row>
-    <row r="129" spans="1:19">
-      <c r="A129" t="s">
-        <v>19</v>
-      </c>
-      <c r="B129" t="s">
-        <v>20</v>
-      </c>
-      <c r="C129" t="s">
-        <v>21</v>
-      </c>
-      <c r="D129" t="s">
-        <v>22</v>
-      </c>
-      <c r="E129" t="s">
-        <v>33</v>
-      </c>
-      <c r="F129">
-        <v>36</v>
-      </c>
-      <c r="G129" t="s">
-        <v>107</v>
-      </c>
-      <c r="H129">
-        <v>31.5710787</v>
-      </c>
-      <c r="I129">
-        <v>75.0424861</v>
-      </c>
-      <c r="J129" t="s">
-        <v>110</v>
-      </c>
-      <c r="K129">
-        <v>34</v>
-      </c>
-      <c r="L129" t="s">
-        <v>111</v>
-      </c>
-      <c r="M129" t="s">
-        <v>21</v>
-      </c>
-      <c r="N129" t="s">
-        <v>22</v>
-      </c>
-      <c r="O129" t="s">
-        <v>33</v>
-      </c>
-      <c r="P129">
-        <v>31.34177</v>
-      </c>
-      <c r="Q129">
-        <v>75.02247</v>
-      </c>
-      <c r="R129" t="s">
-        <v>112</v>
-      </c>
-      <c r="S129">
-        <v>5100</v>
-      </c>
-    </row>
-    <row r="130" spans="1:19">
-      <c r="A130" t="s">
-        <v>19</v>
-      </c>
-      <c r="B130" t="s">
-        <v>20</v>
-      </c>
-      <c r="C130" t="s">
-        <v>21</v>
-      </c>
-      <c r="D130" t="s">
-        <v>22</v>
-      </c>
-      <c r="E130" t="s">
-        <v>33</v>
-      </c>
-      <c r="F130">
-        <v>38</v>
-      </c>
-      <c r="G130" t="s">
-        <v>108</v>
-      </c>
-      <c r="H130">
-        <v>31.55596</v>
-      </c>
-      <c r="I130">
-        <v>75.1401267</v>
-      </c>
-      <c r="J130" t="s">
-        <v>110</v>
-      </c>
-      <c r="K130">
-        <v>13</v>
-      </c>
-      <c r="L130" t="s">
-        <v>111</v>
-      </c>
-      <c r="M130" t="s">
-        <v>21</v>
-      </c>
-      <c r="N130" t="s">
-        <v>22</v>
-      </c>
-      <c r="O130" t="s">
-        <v>33</v>
-      </c>
-      <c r="P130">
-        <v>31.56972149</v>
-      </c>
-      <c r="Q130">
-        <v>75.09414523</v>
-      </c>
-      <c r="R130" t="s">
-        <v>112</v>
-      </c>
-      <c r="S130">
-        <v>88347</v>
-      </c>
-    </row>
-    <row r="131" spans="1:19">
-      <c r="A131" t="s">
-        <v>19</v>
-      </c>
-      <c r="B131" t="s">
-        <v>20</v>
-      </c>
-      <c r="C131" t="s">
-        <v>21</v>
-      </c>
-      <c r="D131" t="s">
-        <v>22</v>
-      </c>
-      <c r="E131" t="s">
-        <v>33</v>
-      </c>
-      <c r="F131">
-        <v>40</v>
-      </c>
-      <c r="G131" t="s">
-        <v>109</v>
-      </c>
-      <c r="H131">
-        <v>31.592672</v>
-      </c>
-      <c r="I131">
-        <v>75.12929200000001</v>
-      </c>
-      <c r="J131" t="s">
-        <v>110</v>
-      </c>
-      <c r="K131">
-        <v>13</v>
-      </c>
-      <c r="L131" t="s">
-        <v>111</v>
-      </c>
-      <c r="M131" t="s">
-        <v>21</v>
-      </c>
-      <c r="N131" t="s">
-        <v>22</v>
-      </c>
-      <c r="O131" t="s">
-        <v>33</v>
-      </c>
-      <c r="P131">
-        <v>31.56972149</v>
-      </c>
-      <c r="Q131">
-        <v>75.09414523</v>
-      </c>
-      <c r="R131" t="s">
-        <v>112</v>
-      </c>
-      <c r="S131">
-        <v>11142</v>
+        <v>29640</v>
       </c>
     </row>
   </sheetData>
